--- a/5-DADOS/ouricuri/resina/Dados ouricuri (exemplo).xlsx
+++ b/5-DADOS/ouricuri/resina/Dados ouricuri (exemplo).xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10807"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/328c329cf2f6e6d0/Documentos/1 - ACADEMICO/20 - ARTIGOS/3 - ARTIGOS SUBMETIDOS/ARTIGO GEOTEXTIL OURICURI/4 - DADOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/328c329cf2f6e6d0/Documentos/1 - ACADEMICO/20 - ARTIGOS/2 - ARTIGOS PUBLICADOS/ARTIGO GEOTEXTIL OURICURI/4 - DADOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="511" documentId="13_ncr:1_{BE51082D-827B-4173-B308-A42363AA3CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87B73A73-A746-421F-A853-9371F9BB00E9}"/>
+  <xr:revisionPtr revIDLastSave="512" documentId="13_ncr:1_{BE51082D-827B-4173-B308-A42363AA3CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE7F1363-2F06-4F0C-9748-82BE34AE65D3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="782" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="782" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados gerais" sheetId="12" r:id="rId1"/>
-    <sheet name="Deformação" sheetId="11" state="hidden" r:id="rId2"/>
+    <sheet name="Deformação" sheetId="11" r:id="rId2"/>
     <sheet name="Gráfico deformação" sheetId="6" r:id="rId3"/>
     <sheet name="Planilha3" sheetId="15" r:id="rId4"/>
     <sheet name="Gráfico secante" sheetId="8" r:id="rId5"/>
@@ -1353,7 +1353,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2165,23 +2165,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2189,20 +2177,11 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2221,29 +2200,47 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2271,26 +2268,29 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -6237,25 +6237,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{403D1434-DB46-4AD1-991E-C8EB81A3A4D3}">
   <sheetPr filterMode="1"/>
   <dimension ref="B1:N79"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="0.609375" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.08984375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.64453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.578125" customWidth="1"/>
-    <col min="6" max="6" width="11.890625" customWidth="1"/>
-    <col min="7" max="7" width="12.9921875" customWidth="1"/>
-    <col min="8" max="8" width="12.74609375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.01171875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.4453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.59765625" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.09765625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.59765625" customWidth="1"/>
+    <col min="6" max="6" width="11.8984375" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="3" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:14" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:14" ht="3" customHeight="1"/>
+    <row r="2" spans="2:14" ht="43.2">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" ht="14.4">
       <c r="B3" t="s">
         <v>217</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>118.4698932923603</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:14" ht="14.4">
       <c r="B4" t="s">
         <v>217</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>97.344709846255313</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:14" ht="14.4">
       <c r="B5" t="s">
         <v>217</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>72.658585553313614</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14" ht="14.4">
       <c r="B6" t="s">
         <v>217</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>72.220425432865028</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14" ht="14.4">
       <c r="B7" t="s">
         <v>217</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>104.22046354182598</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:14" ht="14.4" hidden="1">
       <c r="B8" t="s">
         <v>217</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>45.372228970264985</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14" ht="14.4" hidden="1">
       <c r="B9" t="s">
         <v>217</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>22.107411234041738</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14" ht="14.4" hidden="1">
       <c r="B10" t="s">
         <v>217</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>11.833109230404176</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:14" ht="14.4" hidden="1">
       <c r="B11" t="s">
         <v>217</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>56.020099654006323</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" ht="14.4" hidden="1">
       <c r="B12" t="s">
         <v>217</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v>69.78132797858099</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:14" ht="14.4" hidden="1">
       <c r="B13" t="s">
         <v>217</v>
       </c>
@@ -6802,7 +6802,7 @@
         <v>200.69308544127995</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:14" ht="14.4" hidden="1">
       <c r="B14" t="s">
         <v>217</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>79.760776576033521</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:14" ht="14.4" hidden="1">
       <c r="B15" t="s">
         <v>217</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>115.14335872179907</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:14" ht="14.4" hidden="1">
       <c r="B16" t="s">
         <v>217</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>48.002357618623371</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:14" ht="14.4" hidden="1">
       <c r="B17" t="s">
         <v>217</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>178.54728802528089</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" ht="14.4" hidden="1">
       <c r="B18" t="s">
         <v>217</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>63.333333333333336</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:14" ht="14.4" hidden="1">
       <c r="B19" t="s">
         <v>217</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>148.62895368202973</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:14" ht="14.4" hidden="1">
       <c r="B20" t="s">
         <v>217</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>19.884771073987331</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:14" ht="14.4" hidden="1">
       <c r="B21" s="10" t="s">
         <v>17</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>181.77469424940048</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:14" ht="14.4" hidden="1">
       <c r="B22" s="10" t="s">
         <v>17</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>157.64214856859428</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:14" ht="14.4" hidden="1">
       <c r="B23" s="10" t="s">
         <v>17</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>86.708007870231157</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:14" ht="14.4" hidden="1">
       <c r="B24" s="10" t="s">
         <v>17</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>126.44282190496919</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:14" ht="14.4" hidden="1">
       <c r="B25" s="10" t="s">
         <v>17</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>165.93380492090034</v>
       </c>
     </row>
-    <row r="26" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:14" ht="14.4" hidden="1">
       <c r="B26" s="10" t="s">
         <v>17</v>
       </c>
@@ -7400,7 +7400,7 @@
         <v>146.97872539502461</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:14" ht="14.4" hidden="1">
       <c r="B27" s="10" t="s">
         <v>17</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>182.52952335574497</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" ht="14.4" hidden="1">
       <c r="B28" s="10" t="s">
         <v>17</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>348.90318314837418</v>
       </c>
     </row>
-    <row r="29" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" ht="14.4" hidden="1">
       <c r="B29" s="10" t="s">
         <v>17</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>127.62665186862796</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:14" ht="14.4" hidden="1">
       <c r="B30" s="10" t="s">
         <v>17</v>
       </c>
@@ -7584,7 +7584,7 @@
         <v>35.915447170559368</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" ht="14.4" hidden="1">
       <c r="B31" s="10" t="s">
         <v>17</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>393.2971172281346</v>
       </c>
     </row>
-    <row r="32" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:14" ht="14.4" hidden="1">
       <c r="B32" s="10" t="s">
         <v>17</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>105.71843711802842</v>
       </c>
     </row>
-    <row r="33" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" ht="14.4" hidden="1">
       <c r="B33" s="10" t="s">
         <v>17</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>85.64771813408673</v>
       </c>
     </row>
-    <row r="34" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" ht="14.4" hidden="1">
       <c r="B34" s="10" t="s">
         <v>17</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>112.77465692609297</v>
       </c>
     </row>
-    <row r="35" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:14" ht="14.4" hidden="1">
       <c r="B35" s="10" t="s">
         <v>17</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>105.12052640025678</v>
       </c>
     </row>
-    <row r="36" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:14" ht="14.4" hidden="1">
       <c r="B36" s="10" t="s">
         <v>17</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>64.502364650243521</v>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" ht="14.4" hidden="1">
       <c r="B37" s="10" t="s">
         <v>17</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>254.91711209574379</v>
       </c>
     </row>
-    <row r="38" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" ht="14.4" hidden="1">
       <c r="B38" s="10" t="s">
         <v>17</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>70.928388187544314</v>
       </c>
     </row>
-    <row r="39" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" ht="14.4" hidden="1">
       <c r="B39" s="10" t="s">
         <v>17</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>44.429241832990776</v>
       </c>
     </row>
-    <row r="40" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:14" ht="14.4" hidden="1">
       <c r="B40" s="10" t="s">
         <v>17</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>151.31077446495482</v>
       </c>
     </row>
-    <row r="41" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:14" ht="14.4" hidden="1">
       <c r="B41" s="10" t="s">
         <v>17</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>183.37056770513425</v>
       </c>
     </row>
-    <row r="42" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" ht="14.4" hidden="1">
       <c r="B42" s="10" t="s">
         <v>17</v>
       </c>
@@ -8136,7 +8136,7 @@
         <v>73.486417405042602</v>
       </c>
     </row>
-    <row r="43" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" ht="14.4" hidden="1">
       <c r="B43" s="10" t="s">
         <v>17</v>
       </c>
@@ -8182,7 +8182,7 @@
         <v>97.15339273727092</v>
       </c>
     </row>
-    <row r="44" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" ht="14.4" hidden="1">
       <c r="B44" s="10" t="s">
         <v>17</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>467.64818898176168</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" ht="14.4" hidden="1">
       <c r="B45" s="10" t="s">
         <v>17</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>1749.8594086156002</v>
       </c>
     </row>
-    <row r="46" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" ht="14.4" hidden="1">
       <c r="B46" s="10" t="s">
         <v>17</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>171.02674074074073</v>
       </c>
     </row>
-    <row r="47" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" ht="14.4" hidden="1">
       <c r="B47" s="10" t="s">
         <v>17</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>278.25053538229827</v>
       </c>
     </row>
-    <row r="48" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" ht="14.4" hidden="1">
       <c r="B48" s="10" t="s">
         <v>17</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>146.81105777777779</v>
       </c>
     </row>
-    <row r="49" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:14" ht="14.4" hidden="1">
       <c r="B49" s="10" t="s">
         <v>17</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>381.88224480416693</v>
       </c>
     </row>
-    <row r="50" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:14" ht="14.4" hidden="1">
       <c r="B50" s="10" t="s">
         <v>17</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>173.82974411485498</v>
       </c>
     </row>
-    <row r="51" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:14" ht="14.4" hidden="1">
       <c r="B51" s="10" t="s">
         <v>17</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>426.31666888859263</v>
       </c>
     </row>
-    <row r="52" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:14" ht="14.4" hidden="1">
       <c r="B52" s="10" t="s">
         <v>17</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>16.033884278522333</v>
       </c>
     </row>
-    <row r="53" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:14" ht="14.4" hidden="1">
       <c r="B53" s="10" t="s">
         <v>17</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>456.71355555555556</v>
       </c>
     </row>
-    <row r="54" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:14" ht="14.4" hidden="1">
       <c r="B54" s="10" t="s">
         <v>213</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>225.22286709178164</v>
       </c>
     </row>
-    <row r="55" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:14" ht="14.4" hidden="1">
       <c r="B55" s="10" t="s">
         <v>213</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>209.5517144704088</v>
       </c>
     </row>
-    <row r="56" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:14" ht="14.4" hidden="1">
       <c r="B56" s="10" t="s">
         <v>213</v>
       </c>
@@ -8780,7 +8780,7 @@
         <v>219.61018089037725</v>
       </c>
     </row>
-    <row r="57" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:14" ht="14.4" hidden="1">
       <c r="B57" s="10" t="s">
         <v>213</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>144.05793968253968</v>
       </c>
     </row>
-    <row r="58" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:14" ht="14.4" hidden="1">
       <c r="B58" s="10" t="s">
         <v>213</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>157.86264581542849</v>
       </c>
     </row>
-    <row r="59" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:14" ht="14.4" hidden="1">
       <c r="B59" s="10" t="s">
         <v>213</v>
       </c>
@@ -8918,7 +8918,7 @@
         <v>920.59362058865122</v>
       </c>
     </row>
-    <row r="60" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:14" ht="14.4" hidden="1">
       <c r="B60" s="10" t="s">
         <v>213</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>392.19035133758297</v>
       </c>
     </row>
-    <row r="61" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:14" ht="14.4" hidden="1">
       <c r="B61" s="10" t="s">
         <v>213</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>840.81534904996624</v>
       </c>
     </row>
-    <row r="62" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:14" ht="14.4" hidden="1">
       <c r="B62" s="10" t="s">
         <v>213</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>209.71130739740249</v>
       </c>
     </row>
-    <row r="63" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:14" ht="14.4" hidden="1">
       <c r="B63" s="10" t="s">
         <v>213</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>566.93625458274528</v>
       </c>
     </row>
-    <row r="64" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:14" ht="14.4" hidden="1">
       <c r="B64" s="10" t="s">
         <v>213</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>45.505075130227908</v>
       </c>
     </row>
-    <row r="65" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:14" ht="14.4" hidden="1">
       <c r="B65" s="10" t="s">
         <v>213</v>
       </c>
@@ -9194,7 +9194,7 @@
         <v>80.574576737855395</v>
       </c>
     </row>
-    <row r="66" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:14" ht="14.4" hidden="1">
       <c r="B66" s="10" t="s">
         <v>213</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>335.49496296296292</v>
       </c>
     </row>
-    <row r="67" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" ht="14.4" hidden="1">
       <c r="B67" s="10" t="s">
         <v>213</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>109.16768064417174</v>
       </c>
     </row>
-    <row r="68" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:14" ht="14.4" hidden="1">
       <c r="B68" s="10" t="s">
         <v>213</v>
       </c>
@@ -9332,7 +9332,7 @@
         <v>96.374121380612664</v>
       </c>
     </row>
-    <row r="69" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:14" ht="14.4" hidden="1">
       <c r="B69" s="10" t="s">
         <v>213</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>710.54680506618422</v>
       </c>
     </row>
-    <row r="70" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:14" ht="14.4" hidden="1">
       <c r="B70" s="10" t="s">
         <v>213</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>193.13276254347593</v>
       </c>
     </row>
-    <row r="71" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:14" ht="14.4" hidden="1">
       <c r="B71" s="10" t="s">
         <v>213</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>225.68808466143147</v>
       </c>
     </row>
-    <row r="72" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:14" ht="14.4" hidden="1">
       <c r="B72" s="10" t="s">
         <v>213</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>175.30939869281048</v>
       </c>
     </row>
-    <row r="73" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" ht="14.4" hidden="1">
       <c r="B73" s="10" t="s">
         <v>213</v>
       </c>
@@ -9562,7 +9562,7 @@
         <v>22.127653900791749</v>
       </c>
     </row>
-    <row r="74" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:14" ht="14.4" hidden="1">
       <c r="B74" s="10" t="s">
         <v>213</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>527.01876572838023</v>
       </c>
     </row>
-    <row r="75" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:14" ht="14.4" hidden="1">
       <c r="B75" s="10" t="s">
         <v>213</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>819.86385453202899</v>
       </c>
     </row>
-    <row r="76" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:14" ht="14.4" hidden="1">
       <c r="B76" s="10" t="s">
         <v>213</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>82.993879158838865</v>
       </c>
     </row>
-    <row r="77" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" ht="14.4" hidden="1">
       <c r="B77" s="10" t="s">
         <v>213</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>140.29092189944004</v>
       </c>
     </row>
-    <row r="78" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:14" ht="14.4" hidden="1">
       <c r="B78" s="10" t="s">
         <v>213</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>435.36551596824808</v>
       </c>
     </row>
-    <row r="79" spans="2:14" ht="15" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:14" ht="14.4" hidden="1">
       <c r="B79" s="10" t="s">
         <v>213</v>
       </c>
@@ -9859,15 +9859,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A9614D-9FF0-4FDB-8310-6F6FC8BD0285}">
   <dimension ref="B1:E99"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="0.609375" customWidth="1"/>
-    <col min="2" max="2" width="11.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.890625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.59765625" customWidth="1"/>
+    <col min="2" max="2" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="3.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:5" ht="3.75" customHeight="1"/>
+    <row r="2" spans="2:5">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:5">
       <c r="B3" t="s">
         <v>212</v>
       </c>
@@ -9895,7 +9895,7 @@
         <v>4.1447894736842104</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:5">
       <c r="B4" t="s">
         <v>212</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>4.1973210526315796</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
         <v>212</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>2.9605526315789477</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
         <v>212</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>3.1052789473684212</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
         <v>212</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>2.236857894736842</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
         <v>212</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>1.4342473684210526</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:5">
       <c r="B9" t="s">
         <v>212</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>2.9341894736842105</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:5">
       <c r="B10" t="s">
         <v>212</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>2.3289736842105264</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:5">
       <c r="B11" t="s">
         <v>212</v>
       </c>
@@ -10007,7 +10007,7 @@
         <v>3.4079315789473679</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:5">
       <c r="B12" t="s">
         <v>212</v>
       </c>
@@ -10021,7 +10021,7 @@
         <v>3.2763157894736841</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:5">
       <c r="B13" t="s">
         <v>212</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>0.71055263157894732</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:5">
       <c r="B14" t="s">
         <v>212</v>
       </c>
@@ -10049,7 +10049,7 @@
         <v>4.6973631578947366</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:5">
       <c r="B15" t="s">
         <v>212</v>
       </c>
@@ -10063,7 +10063,7 @@
         <v>1.5789736842105262</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:5">
       <c r="B16" t="s">
         <v>212</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>1.7368105263157894</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:5">
       <c r="B17" t="s">
         <v>212</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>0.22373157894736845</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:5">
       <c r="B18" t="s">
         <v>212</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>1.4605263157894737</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:5">
       <c r="B19" t="s">
         <v>212</v>
       </c>
@@ -10119,7 +10119,7 @@
         <v>2.2237210526315785</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
         <v>212</v>
       </c>
@@ -10133,7 +10133,7 @@
         <v>1.7236473684210527</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:5">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>3.5394631578947373</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:5">
       <c r="B22" t="s">
         <v>17</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>5.2631368421052631</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:5">
       <c r="B23" t="s">
         <v>17</v>
       </c>
@@ -10175,7 +10175,7 @@
         <v>5.4605052631578941</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:5">
       <c r="B24" t="s">
         <v>17</v>
       </c>
@@ -10189,7 +10189,7 @@
         <v>1.7894842105263158</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:5">
       <c r="B25" t="s">
         <v>17</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>3.4210684210526319</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:5">
       <c r="B26" t="s">
         <v>17</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>2.2500263157894738</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:5">
       <c r="B27" t="s">
         <v>17</v>
       </c>
@@ -10231,7 +10231,7 @@
         <v>1.7894842105263158</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:5">
       <c r="B28" t="s">
         <v>17</v>
       </c>
@@ -10245,7 +10245,7 @@
         <v>1.2895210526315788</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:5">
       <c r="B29" t="s">
         <v>17</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>1.8684315789473684</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:5">
       <c r="B30" t="s">
         <v>17</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>7.4473526315789478</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:5">
       <c r="B31" t="s">
         <v>17</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>1.6315315789473686</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:5">
       <c r="B32" t="s">
         <v>17</v>
       </c>
@@ -10301,7 +10301,7 @@
         <v>3.1447526315789474</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:5">
       <c r="B33" t="s">
         <v>17</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>1.2500157894736843</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:5">
       <c r="B34" t="s">
         <v>17</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>1.1973789473684211</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:5">
       <c r="B35" t="s">
         <v>17</v>
       </c>
@@ -10343,7 +10343,7 @@
         <v>0.71055263157894732</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:5">
       <c r="B36" t="s">
         <v>17</v>
       </c>
@@ -10357,7 +10357,7 @@
         <v>0.44737894736842104</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:5">
       <c r="B37" t="s">
         <v>17</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>1.1973473684210527</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:5">
       <c r="B38" t="s">
         <v>17</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>1.9736526315789475</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:5">
       <c r="B39" t="s">
         <v>17</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>4.0920947368421059</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:5">
       <c r="B40" t="s">
         <v>17</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>1.1447631578947368</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:5">
       <c r="B41" t="s">
         <v>17</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>0.3684578947368421</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:5">
       <c r="B42" t="s">
         <v>17</v>
       </c>
@@ -10441,7 +10441,7 @@
         <v>0.69735789473684207</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:5">
       <c r="B43" t="s">
         <v>17</v>
       </c>
@@ -10455,7 +10455,7 @@
         <v>0.76313684210526311</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:5">
       <c r="B44" t="s">
         <v>17</v>
       </c>
@@ -10469,7 +10469,7 @@
         <v>0.5131842105263158</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:5">
       <c r="B45" t="s">
         <v>17</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>0.10519473684210527</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:5">
       <c r="B46" t="s">
         <v>17</v>
       </c>
@@ -10497,7 +10497,7 @@
         <v>0.94736842105263164</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:5">
       <c r="B47" t="s">
         <v>17</v>
       </c>
@@ -10511,7 +10511,7 @@
         <v>0.22364736842105259</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:5">
       <c r="B48" t="s">
         <v>17</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>0.98684210526315785</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:5">
       <c r="B49" t="s">
         <v>17</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>0.61841052631578941</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:5">
       <c r="B50" t="s">
         <v>17</v>
       </c>
@@ -10553,7 +10553,7 @@
         <v>0.32895789473684212</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:5">
       <c r="B51" t="s">
         <v>17</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>0.19739473684210526</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:5">
       <c r="B52" t="s">
         <v>17</v>
       </c>
@@ -10581,7 +10581,7 @@
         <v>1.1447631578947368</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:5">
       <c r="B53" t="s">
         <v>17</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>0.15789473684210525</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:5">
       <c r="B54" t="s">
         <v>17</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:5">
       <c r="B55" t="s">
         <v>17</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:5">
       <c r="B56" t="s">
         <v>17</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:5">
       <c r="B57" t="s">
         <v>17</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:5">
       <c r="B58" t="s">
         <v>17</v>
       </c>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:5">
       <c r="B59" t="s">
         <v>17</v>
       </c>
@@ -10679,7 +10679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:5">
       <c r="B60" t="s">
         <v>213</v>
       </c>
@@ -10693,7 +10693,7 @@
         <v>2.0394894736842106</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:5">
       <c r="B61" t="s">
         <v>213</v>
       </c>
@@ -10707,7 +10707,7 @@
         <v>2.9473578947368422</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:5">
       <c r="B62" t="s">
         <v>213</v>
       </c>
@@ -10721,7 +10721,7 @@
         <v>3.2894789473684209</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:5">
       <c r="B63" t="s">
         <v>213</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>2.2105263157894739</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:5">
       <c r="B64" t="s">
         <v>213</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>3.2763421052631578</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:5">
       <c r="B65" t="s">
         <v>213</v>
       </c>
@@ -10763,7 +10763,7 @@
         <v>0.43423684210526314</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:5">
       <c r="B66" t="s">
         <v>213</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>2.2763631578947368</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:5">
       <c r="B67" t="s">
         <v>213</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>0.85527894736842103</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:5">
       <c r="B68" t="s">
         <v>213</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>4.0000052631578953</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:5">
       <c r="B69" t="s">
         <v>213</v>
       </c>
@@ -10819,7 +10819,7 @@
         <v>1.6183894736842106</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:5">
       <c r="B70" t="s">
         <v>213</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>4.0263421052631578</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:5">
       <c r="B71" t="s">
         <v>213</v>
       </c>
@@ -10847,7 +10847,7 @@
         <v>1.013121052631579</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:5">
       <c r="B72" t="s">
         <v>213</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>0.94736842105263164</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:5">
       <c r="B73" t="s">
         <v>213</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>1.8815947368421053</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:5">
       <c r="B74" t="s">
         <v>213</v>
       </c>
@@ -10889,7 +10889,7 @@
         <v>0.80269473684210535</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:5">
       <c r="B75" t="s">
         <v>213</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>0.27634210526315789</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:5">
       <c r="B76" t="s">
         <v>213</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>1.2368210526315788</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:5">
       <c r="B77" t="s">
         <v>213</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>0.49998947368421048</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:5">
       <c r="B78" t="s">
         <v>213</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>1.3421052631578947</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:5">
       <c r="B79" t="s">
         <v>213</v>
       </c>
@@ -10959,7 +10959,7 @@
         <v>0.72369473684210517</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:5">
       <c r="B80" t="s">
         <v>213</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>0.21053684210526313</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:5">
       <c r="B81" t="s">
         <v>213</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>0.34212631578947367</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:5">
       <c r="B82" t="s">
         <v>213</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>0.43423684210526314</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:5">
       <c r="B83" t="s">
         <v>213</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>0.88158947368421037</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:5">
       <c r="B84" t="s">
         <v>213</v>
       </c>
@@ -11029,7 +11029,7 @@
         <v>0.17106315789473683</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:5">
       <c r="B85" t="s">
         <v>213</v>
       </c>
@@ -11043,7 +11043,7 @@
         <v>0.23684210526315791</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:5">
       <c r="B86" t="s">
         <v>213</v>
       </c>
@@ -11057,7 +11057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:5">
       <c r="B87" t="s">
         <v>213</v>
       </c>
@@ -11071,7 +11071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:5">
       <c r="B88" t="s">
         <v>213</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:5">
       <c r="B89" t="s">
         <v>213</v>
       </c>
@@ -11099,7 +11099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:5">
       <c r="B90" t="s">
         <v>213</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:5">
       <c r="B91" t="s">
         <v>213</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:5">
       <c r="B92" t="s">
         <v>213</v>
       </c>
@@ -11141,7 +11141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:5">
       <c r="B93" t="s">
         <v>213</v>
       </c>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:5">
       <c r="B94" t="s">
         <v>213</v>
       </c>
@@ -11169,7 +11169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:5">
       <c r="B95" t="s">
         <v>213</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:5">
       <c r="B96" t="s">
         <v>213</v>
       </c>
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:5">
       <c r="B97" t="s">
         <v>213</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:5">
       <c r="B98" t="s">
         <v>213</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:5">
       <c r="B99" t="s">
         <v>213</v>
       </c>
@@ -11248,22 +11248,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D10ABD7D-C240-400D-A96E-C853E05A1EA0}">
   <dimension ref="B1:AA73"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="0.609375" customWidth="1"/>
-    <col min="2" max="2" width="12.13671875" customWidth="1"/>
-    <col min="4" max="4" width="18.51171875" customWidth="1"/>
+    <col min="1" max="1" width="0.59765625" customWidth="1"/>
+    <col min="2" max="2" width="12.09765625" customWidth="1"/>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="4.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="B2" s="116" t="s">
+    <row r="1" spans="2:27" ht="4.5" customHeight="1"/>
+    <row r="2" spans="2:27">
+      <c r="B2" s="105" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-    </row>
-    <row r="3" spans="2:27" x14ac:dyDescent="0.15">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+    </row>
+    <row r="3" spans="2:27">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -11273,18 +11273,18 @@
       <c r="D3" t="s">
         <v>214</v>
       </c>
-      <c r="T3" s="120" t="s">
+      <c r="T3" s="113" t="s">
         <v>222</v>
       </c>
-      <c r="U3" s="120"/>
-      <c r="V3" s="120"/>
-      <c r="W3" s="120"/>
-      <c r="X3" s="120"/>
-      <c r="Y3" s="120"/>
-      <c r="Z3" s="120"/>
+      <c r="U3" s="113"/>
+      <c r="V3" s="113"/>
+      <c r="W3" s="113"/>
+      <c r="X3" s="113"/>
+      <c r="Y3" s="113"/>
+      <c r="Z3" s="113"/>
       <c r="AA3" s="22"/>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:27">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -11296,20 +11296,20 @@
         <v>3.3289600000000003E-2</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="114" t="s">
         <v>223</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="V4" s="122"/>
-      <c r="W4" s="122"/>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="122"/>
-      <c r="Z4" s="122"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
       <c r="AA4" s="22"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:27">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -11321,24 +11321,24 @@
         <v>2.6842248120300748E-2</v>
       </c>
       <c r="E5" s="8"/>
-      <c r="T5" s="123" t="s">
+      <c r="T5" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="U5" s="123"/>
-      <c r="V5" s="123"/>
-      <c r="W5" s="106" t="s">
+      <c r="U5" s="116"/>
+      <c r="V5" s="116"/>
+      <c r="W5" s="118" t="s">
         <v>224</v>
       </c>
-      <c r="X5" s="108" t="s">
+      <c r="X5" s="120" t="s">
         <v>235</v>
       </c>
-      <c r="Y5" s="108" t="s">
+      <c r="Y5" s="120" t="s">
         <v>236</v>
       </c>
-      <c r="Z5" s="110"/>
+      <c r="Z5" s="122"/>
       <c r="AA5" s="22"/>
     </row>
-    <row r="6" spans="2:27" ht="21.75" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:27" ht="23.4">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -11350,11 +11350,11 @@
         <v>1.4912350877192981E-2</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="T6" s="124"/>
-      <c r="U6" s="124"/>
-      <c r="V6" s="124"/>
-      <c r="W6" s="107"/>
-      <c r="X6" s="109"/>
+      <c r="T6" s="117"/>
+      <c r="U6" s="117"/>
+      <c r="V6" s="117"/>
+      <c r="W6" s="119"/>
+      <c r="X6" s="121"/>
       <c r="Y6" s="23" t="s">
         <v>225</v>
       </c>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:27">
       <c r="B7" t="s">
         <v>220</v>
       </c>
@@ -11375,10 +11375,10 @@
         <v>3.8947315789473677E-2</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="T7" s="118" t="s">
+      <c r="T7" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="U7" s="119" t="s">
+      <c r="U7" s="112" t="s">
         <v>5</v>
       </c>
       <c r="V7" s="56" t="s">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="AA7" s="22"/>
     </row>
-    <row r="8" spans="2:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:27">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -11410,8 +11410,8 @@
         <v>2.7744428571428573E-2</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="T8" s="112"/>
-      <c r="U8" s="115"/>
+      <c r="T8" s="108"/>
+      <c r="U8" s="110"/>
       <c r="V8" s="43" t="s">
         <v>7</v>
       </c>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="AA8" s="22"/>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:27">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -11441,8 +11441,8 @@
         <v>1.5526315789473687E-2</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="T9" s="112"/>
-      <c r="U9" s="115"/>
+      <c r="T9" s="108"/>
+      <c r="U9" s="110"/>
       <c r="V9" s="43"/>
       <c r="W9" s="47"/>
       <c r="X9" s="48"/>
@@ -11450,7 +11450,7 @@
       <c r="Z9" s="49"/>
       <c r="AA9" s="22"/>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:27">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -11462,8 +11462,8 @@
         <v>6.4849473684210519E-3</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="T10" s="112"/>
-      <c r="U10" s="114"/>
+      <c r="T10" s="108"/>
+      <c r="U10" s="109"/>
       <c r="V10" s="50"/>
       <c r="W10" s="51"/>
       <c r="X10" s="52"/>
@@ -11471,7 +11471,7 @@
       <c r="Z10" s="53"/>
       <c r="AA10" s="22"/>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:27">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -11483,7 +11483,7 @@
         <v>5.2255864661654135E-3</v>
       </c>
       <c r="E11" s="8"/>
-      <c r="T11" s="112"/>
+      <c r="T11" s="108"/>
       <c r="U11" s="50"/>
       <c r="V11" s="50"/>
       <c r="W11" s="51"/>
@@ -11492,7 +11492,7 @@
       <c r="Z11" s="53"/>
       <c r="AA11" s="22"/>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:27">
       <c r="B12" s="2" t="s">
         <v>221</v>
       </c>
@@ -11504,8 +11504,8 @@
         <v>2.7526389473684212E-2</v>
       </c>
       <c r="E12" s="8"/>
-      <c r="T12" s="112"/>
-      <c r="U12" s="111" t="s">
+      <c r="T12" s="108"/>
+      <c r="U12" s="107" t="s">
         <v>6</v>
       </c>
       <c r="V12" s="25" t="s">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="AA12" s="22"/>
     </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:27">
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
@@ -11537,8 +11537,8 @@
         <v>2.0319624060150376E-2</v>
       </c>
       <c r="E13" s="8"/>
-      <c r="T13" s="112"/>
-      <c r="U13" s="112"/>
+      <c r="T13" s="108"/>
+      <c r="U13" s="108"/>
       <c r="V13" s="25" t="s">
         <v>7</v>
       </c>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="AA13" s="22"/>
     </row>
-    <row r="14" spans="2:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:27">
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
@@ -11568,8 +11568,8 @@
         <v>9.9813082706766924E-3</v>
       </c>
       <c r="E14" s="8"/>
-      <c r="T14" s="112"/>
-      <c r="U14" s="112"/>
+      <c r="T14" s="108"/>
+      <c r="U14" s="108"/>
       <c r="V14" s="25" t="s">
         <v>8</v>
       </c>
@@ -11581,7 +11581,7 @@
       <c r="Z14" s="31"/>
       <c r="AA14" s="22"/>
     </row>
-    <row r="15" spans="2:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:27">
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
@@ -11593,8 +11593,8 @@
         <v>4.2858421052631582E-3</v>
       </c>
       <c r="E15" s="8"/>
-      <c r="T15" s="112"/>
-      <c r="U15" s="111"/>
+      <c r="T15" s="108"/>
+      <c r="U15" s="107"/>
       <c r="V15" s="32" t="s">
         <v>227</v>
       </c>
@@ -11606,11 +11606,11 @@
       <c r="Z15" s="35"/>
       <c r="AA15" s="22"/>
     </row>
-    <row r="16" spans="2:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:27">
       <c r="B16" s="2"/>
       <c r="D16" s="8"/>
-      <c r="T16" s="112"/>
-      <c r="U16" s="111" t="s">
+      <c r="T16" s="108"/>
+      <c r="U16" s="107" t="s">
         <v>7</v>
       </c>
       <c r="V16" s="25" t="s">
@@ -11630,11 +11630,11 @@
       </c>
       <c r="AA16" s="22"/>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:27">
       <c r="B17" s="2"/>
       <c r="D17" s="8"/>
-      <c r="T17" s="112"/>
-      <c r="U17" s="112"/>
+      <c r="T17" s="108"/>
+      <c r="U17" s="108"/>
       <c r="V17" s="25" t="s">
         <v>6</v>
       </c>
@@ -11652,9 +11652,9 @@
       </c>
       <c r="AA17" s="22"/>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
+    <row r="18" spans="2:27">
+      <c r="T18" s="108"/>
+      <c r="U18" s="108"/>
       <c r="V18" s="25"/>
       <c r="W18" s="29"/>
       <c r="X18" s="30"/>
@@ -11662,9 +11662,9 @@
       <c r="Z18" s="31"/>
       <c r="AA18" s="22"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T19" s="112"/>
-      <c r="U19" s="111"/>
+    <row r="19" spans="2:27">
+      <c r="T19" s="108"/>
+      <c r="U19" s="107"/>
       <c r="V19" s="32"/>
       <c r="W19" s="33"/>
       <c r="X19" s="34"/>
@@ -11672,9 +11672,9 @@
       <c r="Z19" s="35"/>
       <c r="AA19" s="22"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T20" s="112"/>
-      <c r="U20" s="111"/>
+    <row r="20" spans="2:27">
+      <c r="T20" s="108"/>
+      <c r="U20" s="107"/>
       <c r="V20" s="25"/>
       <c r="W20" s="29"/>
       <c r="X20" s="30"/>
@@ -11682,9 +11682,9 @@
       <c r="Z20" s="31"/>
       <c r="AA20" s="22"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
+    <row r="21" spans="2:27">
+      <c r="T21" s="108"/>
+      <c r="U21" s="108"/>
       <c r="V21" s="25"/>
       <c r="W21" s="29"/>
       <c r="X21" s="30"/>
@@ -11692,9 +11692,9 @@
       <c r="Z21" s="31"/>
       <c r="AA21" s="22"/>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T22" s="112"/>
-      <c r="U22" s="112"/>
+    <row r="22" spans="2:27">
+      <c r="T22" s="108"/>
+      <c r="U22" s="108"/>
       <c r="V22" s="25"/>
       <c r="W22" s="29"/>
       <c r="X22" s="30"/>
@@ -11702,9 +11702,9 @@
       <c r="Z22" s="31"/>
       <c r="AA22" s="22"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T23" s="112"/>
-      <c r="U23" s="111"/>
+    <row r="23" spans="2:27">
+      <c r="T23" s="108"/>
+      <c r="U23" s="107"/>
       <c r="V23" s="32"/>
       <c r="W23" s="33"/>
       <c r="X23" s="34"/>
@@ -11712,9 +11712,9 @@
       <c r="Z23" s="35"/>
       <c r="AA23" s="22"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T24" s="112"/>
-      <c r="U24" s="111"/>
+    <row r="24" spans="2:27">
+      <c r="T24" s="108"/>
+      <c r="U24" s="107"/>
       <c r="V24" s="25"/>
       <c r="W24" s="29"/>
       <c r="X24" s="30"/>
@@ -11722,9 +11722,9 @@
       <c r="Z24" s="31"/>
       <c r="AA24" s="22"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T25" s="112"/>
-      <c r="U25" s="112"/>
+    <row r="25" spans="2:27">
+      <c r="T25" s="108"/>
+      <c r="U25" s="108"/>
       <c r="V25" s="25"/>
       <c r="W25" s="29"/>
       <c r="X25" s="30"/>
@@ -11732,9 +11732,9 @@
       <c r="Z25" s="31"/>
       <c r="AA25" s="22"/>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T26" s="112"/>
-      <c r="U26" s="112"/>
+    <row r="26" spans="2:27">
+      <c r="T26" s="108"/>
+      <c r="U26" s="108"/>
       <c r="V26" s="25"/>
       <c r="W26" s="29"/>
       <c r="X26" s="30"/>
@@ -11742,9 +11742,9 @@
       <c r="Z26" s="31"/>
       <c r="AA26" s="22"/>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T27" s="111"/>
-      <c r="U27" s="111"/>
+    <row r="27" spans="2:27">
+      <c r="T27" s="107"/>
+      <c r="U27" s="107"/>
       <c r="V27" s="32"/>
       <c r="W27" s="33"/>
       <c r="X27" s="34"/>
@@ -11752,11 +11752,11 @@
       <c r="Z27" s="35"/>
       <c r="AA27" s="22"/>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T28" s="111" t="s">
+    <row r="28" spans="2:27">
+      <c r="T28" s="107" t="s">
         <v>228</v>
       </c>
-      <c r="U28" s="114" t="s">
+      <c r="U28" s="109" t="s">
         <v>5</v>
       </c>
       <c r="V28" s="43" t="s">
@@ -11776,9 +11776,9 @@
       </c>
       <c r="AA28" s="22"/>
     </row>
-    <row r="29" spans="2:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T29" s="112"/>
-      <c r="U29" s="115"/>
+    <row r="29" spans="2:27">
+      <c r="T29" s="108"/>
+      <c r="U29" s="110"/>
       <c r="V29" s="43" t="s">
         <v>7</v>
       </c>
@@ -11796,9 +11796,9 @@
       </c>
       <c r="AA29" s="22"/>
     </row>
-    <row r="30" spans="2:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T30" s="112"/>
-      <c r="U30" s="115"/>
+    <row r="30" spans="2:27">
+      <c r="T30" s="108"/>
+      <c r="U30" s="110"/>
       <c r="V30" s="43" t="s">
         <v>8</v>
       </c>
@@ -11816,9 +11816,9 @@
       </c>
       <c r="AA30" s="22"/>
     </row>
-    <row r="31" spans="2:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T31" s="112"/>
-      <c r="U31" s="114"/>
+    <row r="31" spans="2:27">
+      <c r="T31" s="108"/>
+      <c r="U31" s="109"/>
       <c r="V31" s="50" t="s">
         <v>227</v>
       </c>
@@ -11836,9 +11836,9 @@
       </c>
       <c r="AA31" s="22"/>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="T32" s="112"/>
-      <c r="U32" s="111" t="s">
+    <row r="32" spans="2:27">
+      <c r="T32" s="108"/>
+      <c r="U32" s="107" t="s">
         <v>6</v>
       </c>
       <c r="V32" s="25" t="s">
@@ -11858,9 +11858,9 @@
       </c>
       <c r="AA32" s="22"/>
     </row>
-    <row r="33" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T33" s="112"/>
-      <c r="U33" s="112"/>
+    <row r="33" spans="20:27">
+      <c r="T33" s="108"/>
+      <c r="U33" s="108"/>
       <c r="V33" s="25" t="s">
         <v>7</v>
       </c>
@@ -11878,9 +11878,9 @@
       </c>
       <c r="AA33" s="22"/>
     </row>
-    <row r="34" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T34" s="112"/>
-      <c r="U34" s="112"/>
+    <row r="34" spans="20:27">
+      <c r="T34" s="108"/>
+      <c r="U34" s="108"/>
       <c r="V34" s="25" t="s">
         <v>8</v>
       </c>
@@ -11898,9 +11898,9 @@
       </c>
       <c r="AA34" s="22"/>
     </row>
-    <row r="35" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T35" s="112"/>
-      <c r="U35" s="111"/>
+    <row r="35" spans="20:27">
+      <c r="T35" s="108"/>
+      <c r="U35" s="107"/>
       <c r="V35" s="32" t="s">
         <v>227</v>
       </c>
@@ -11918,9 +11918,9 @@
       </c>
       <c r="AA35" s="22"/>
     </row>
-    <row r="36" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T36" s="112"/>
-      <c r="U36" s="111" t="s">
+    <row r="36" spans="20:27">
+      <c r="T36" s="108"/>
+      <c r="U36" s="107" t="s">
         <v>7</v>
       </c>
       <c r="V36" s="25" t="s">
@@ -11940,9 +11940,9 @@
       </c>
       <c r="AA36" s="22"/>
     </row>
-    <row r="37" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T37" s="112"/>
-      <c r="U37" s="112"/>
+    <row r="37" spans="20:27">
+      <c r="T37" s="108"/>
+      <c r="U37" s="108"/>
       <c r="V37" s="25" t="s">
         <v>6</v>
       </c>
@@ -11960,9 +11960,9 @@
       </c>
       <c r="AA37" s="22"/>
     </row>
-    <row r="38" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T38" s="112"/>
-      <c r="U38" s="112"/>
+    <row r="38" spans="20:27">
+      <c r="T38" s="108"/>
+      <c r="U38" s="108"/>
       <c r="V38" s="25" t="s">
         <v>8</v>
       </c>
@@ -11980,9 +11980,9 @@
       </c>
       <c r="AA38" s="22"/>
     </row>
-    <row r="39" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T39" s="112"/>
-      <c r="U39" s="111"/>
+    <row r="39" spans="20:27">
+      <c r="T39" s="108"/>
+      <c r="U39" s="107"/>
       <c r="V39" s="32" t="s">
         <v>227</v>
       </c>
@@ -12000,9 +12000,9 @@
       </c>
       <c r="AA39" s="22"/>
     </row>
-    <row r="40" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T40" s="112"/>
-      <c r="U40" s="111" t="s">
+    <row r="40" spans="20:27">
+      <c r="T40" s="108"/>
+      <c r="U40" s="107" t="s">
         <v>8</v>
       </c>
       <c r="V40" s="25" t="s">
@@ -12022,9 +12022,9 @@
       </c>
       <c r="AA40" s="22"/>
     </row>
-    <row r="41" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T41" s="112"/>
-      <c r="U41" s="112"/>
+    <row r="41" spans="20:27">
+      <c r="T41" s="108"/>
+      <c r="U41" s="108"/>
       <c r="V41" s="25" t="s">
         <v>6</v>
       </c>
@@ -12042,9 +12042,9 @@
       </c>
       <c r="AA41" s="22"/>
     </row>
-    <row r="42" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T42" s="112"/>
-      <c r="U42" s="112"/>
+    <row r="42" spans="20:27">
+      <c r="T42" s="108"/>
+      <c r="U42" s="108"/>
       <c r="V42" s="25" t="s">
         <v>7</v>
       </c>
@@ -12062,9 +12062,9 @@
       </c>
       <c r="AA42" s="22"/>
     </row>
-    <row r="43" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T43" s="112"/>
-      <c r="U43" s="111"/>
+    <row r="43" spans="20:27">
+      <c r="T43" s="108"/>
+      <c r="U43" s="107"/>
       <c r="V43" s="32" t="s">
         <v>227</v>
       </c>
@@ -12082,9 +12082,9 @@
       </c>
       <c r="AA43" s="22"/>
     </row>
-    <row r="44" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T44" s="112"/>
-      <c r="U44" s="111" t="s">
+    <row r="44" spans="20:27">
+      <c r="T44" s="108"/>
+      <c r="U44" s="107" t="s">
         <v>227</v>
       </c>
       <c r="V44" s="25" t="s">
@@ -12104,9 +12104,9 @@
       </c>
       <c r="AA44" s="22"/>
     </row>
-    <row r="45" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T45" s="112"/>
-      <c r="U45" s="112"/>
+    <row r="45" spans="20:27">
+      <c r="T45" s="108"/>
+      <c r="U45" s="108"/>
       <c r="V45" s="25" t="s">
         <v>6</v>
       </c>
@@ -12124,9 +12124,9 @@
       </c>
       <c r="AA45" s="22"/>
     </row>
-    <row r="46" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T46" s="112"/>
-      <c r="U46" s="112"/>
+    <row r="46" spans="20:27">
+      <c r="T46" s="108"/>
+      <c r="U46" s="108"/>
       <c r="V46" s="25" t="s">
         <v>7</v>
       </c>
@@ -12144,9 +12144,9 @@
       </c>
       <c r="AA46" s="22"/>
     </row>
-    <row r="47" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
+    <row r="47" spans="20:27">
+      <c r="T47" s="107"/>
+      <c r="U47" s="107"/>
       <c r="V47" s="32" t="s">
         <v>8</v>
       </c>
@@ -12164,11 +12164,11 @@
       </c>
       <c r="AA47" s="22"/>
     </row>
-    <row r="48" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T48" s="111" t="s">
+    <row r="48" spans="20:27">
+      <c r="T48" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="U48" s="114" t="s">
+      <c r="U48" s="109" t="s">
         <v>5</v>
       </c>
       <c r="V48" s="43" t="s">
@@ -12188,9 +12188,9 @@
       </c>
       <c r="AA48" s="22"/>
     </row>
-    <row r="49" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T49" s="112"/>
-      <c r="U49" s="115"/>
+    <row r="49" spans="20:27">
+      <c r="T49" s="108"/>
+      <c r="U49" s="110"/>
       <c r="V49" s="43" t="s">
         <v>7</v>
       </c>
@@ -12208,9 +12208,9 @@
       </c>
       <c r="AA49" s="22"/>
     </row>
-    <row r="50" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T50" s="112"/>
-      <c r="U50" s="115"/>
+    <row r="50" spans="20:27">
+      <c r="T50" s="108"/>
+      <c r="U50" s="110"/>
       <c r="V50" s="43" t="s">
         <v>8</v>
       </c>
@@ -12228,9 +12228,9 @@
       </c>
       <c r="AA50" s="22"/>
     </row>
-    <row r="51" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T51" s="112"/>
-      <c r="U51" s="114"/>
+    <row r="51" spans="20:27">
+      <c r="T51" s="108"/>
+      <c r="U51" s="109"/>
       <c r="V51" s="50" t="s">
         <v>227</v>
       </c>
@@ -12242,9 +12242,9 @@
       <c r="Z51" s="53"/>
       <c r="AA51" s="22"/>
     </row>
-    <row r="52" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T52" s="112"/>
-      <c r="U52" s="111" t="s">
+    <row r="52" spans="20:27">
+      <c r="T52" s="108"/>
+      <c r="U52" s="107" t="s">
         <v>6</v>
       </c>
       <c r="V52" s="25" t="s">
@@ -12264,9 +12264,9 @@
       </c>
       <c r="AA52" s="22"/>
     </row>
-    <row r="53" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T53" s="112"/>
-      <c r="U53" s="112"/>
+    <row r="53" spans="20:27">
+      <c r="T53" s="108"/>
+      <c r="U53" s="108"/>
       <c r="V53" s="25" t="s">
         <v>7</v>
       </c>
@@ -12284,9 +12284,9 @@
       </c>
       <c r="AA53" s="22"/>
     </row>
-    <row r="54" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T54" s="112"/>
-      <c r="U54" s="112"/>
+    <row r="54" spans="20:27">
+      <c r="T54" s="108"/>
+      <c r="U54" s="108"/>
       <c r="V54" s="25" t="s">
         <v>8</v>
       </c>
@@ -12304,9 +12304,9 @@
       </c>
       <c r="AA54" s="22"/>
     </row>
-    <row r="55" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T55" s="112"/>
-      <c r="U55" s="111"/>
+    <row r="55" spans="20:27">
+      <c r="T55" s="108"/>
+      <c r="U55" s="107"/>
       <c r="V55" s="32" t="s">
         <v>227</v>
       </c>
@@ -12318,9 +12318,9 @@
       <c r="Z55" s="35"/>
       <c r="AA55" s="22"/>
     </row>
-    <row r="56" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T56" s="112"/>
-      <c r="U56" s="111" t="s">
+    <row r="56" spans="20:27">
+      <c r="T56" s="108"/>
+      <c r="U56" s="107" t="s">
         <v>7</v>
       </c>
       <c r="V56" s="25" t="s">
@@ -12340,9 +12340,9 @@
       </c>
       <c r="AA56" s="22"/>
     </row>
-    <row r="57" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T57" s="112"/>
-      <c r="U57" s="112"/>
+    <row r="57" spans="20:27">
+      <c r="T57" s="108"/>
+      <c r="U57" s="108"/>
       <c r="V57" s="25" t="s">
         <v>6</v>
       </c>
@@ -12360,9 +12360,9 @@
       </c>
       <c r="AA57" s="22"/>
     </row>
-    <row r="58" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T58" s="112"/>
-      <c r="U58" s="112"/>
+    <row r="58" spans="20:27">
+      <c r="T58" s="108"/>
+      <c r="U58" s="108"/>
       <c r="V58" s="25" t="s">
         <v>8</v>
       </c>
@@ -12380,9 +12380,9 @@
       </c>
       <c r="AA58" s="22"/>
     </row>
-    <row r="59" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T59" s="112"/>
-      <c r="U59" s="111"/>
+    <row r="59" spans="20:27">
+      <c r="T59" s="108"/>
+      <c r="U59" s="107"/>
       <c r="V59" s="32" t="s">
         <v>227</v>
       </c>
@@ -12394,9 +12394,9 @@
       <c r="Z59" s="35"/>
       <c r="AA59" s="22"/>
     </row>
-    <row r="60" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T60" s="112"/>
-      <c r="U60" s="111" t="s">
+    <row r="60" spans="20:27">
+      <c r="T60" s="108"/>
+      <c r="U60" s="107" t="s">
         <v>8</v>
       </c>
       <c r="V60" s="25" t="s">
@@ -12416,9 +12416,9 @@
       </c>
       <c r="AA60" s="22"/>
     </row>
-    <row r="61" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T61" s="112"/>
-      <c r="U61" s="112"/>
+    <row r="61" spans="20:27">
+      <c r="T61" s="108"/>
+      <c r="U61" s="108"/>
       <c r="V61" s="25" t="s">
         <v>6</v>
       </c>
@@ -12436,9 +12436,9 @@
       </c>
       <c r="AA61" s="22"/>
     </row>
-    <row r="62" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T62" s="112"/>
-      <c r="U62" s="112"/>
+    <row r="62" spans="20:27">
+      <c r="T62" s="108"/>
+      <c r="U62" s="108"/>
       <c r="V62" s="25" t="s">
         <v>7</v>
       </c>
@@ -12456,9 +12456,9 @@
       </c>
       <c r="AA62" s="22"/>
     </row>
-    <row r="63" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T63" s="112"/>
-      <c r="U63" s="111"/>
+    <row r="63" spans="20:27">
+      <c r="T63" s="108"/>
+      <c r="U63" s="107"/>
       <c r="V63" s="32" t="s">
         <v>227</v>
       </c>
@@ -12470,9 +12470,9 @@
       <c r="Z63" s="35"/>
       <c r="AA63" s="22"/>
     </row>
-    <row r="64" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T64" s="112"/>
-      <c r="U64" s="111" t="s">
+    <row r="64" spans="20:27">
+      <c r="T64" s="108"/>
+      <c r="U64" s="107" t="s">
         <v>227</v>
       </c>
       <c r="V64" s="25" t="s">
@@ -12486,9 +12486,9 @@
       <c r="Z64" s="31"/>
       <c r="AA64" s="22"/>
     </row>
-    <row r="65" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T65" s="112"/>
-      <c r="U65" s="112"/>
+    <row r="65" spans="20:27">
+      <c r="T65" s="108"/>
+      <c r="U65" s="108"/>
       <c r="V65" s="25" t="s">
         <v>6</v>
       </c>
@@ -12500,9 +12500,9 @@
       <c r="Z65" s="31"/>
       <c r="AA65" s="22"/>
     </row>
-    <row r="66" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T66" s="112"/>
-      <c r="U66" s="112"/>
+    <row r="66" spans="20:27">
+      <c r="T66" s="108"/>
+      <c r="U66" s="108"/>
       <c r="V66" s="25" t="s">
         <v>7</v>
       </c>
@@ -12514,9 +12514,9 @@
       <c r="Z66" s="31"/>
       <c r="AA66" s="22"/>
     </row>
-    <row r="67" spans="20:27" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="T67" s="113"/>
-      <c r="U67" s="113"/>
+    <row r="67" spans="20:27">
+      <c r="T67" s="123"/>
+      <c r="U67" s="123"/>
       <c r="V67" s="39" t="s">
         <v>8</v>
       </c>
@@ -12528,71 +12528,85 @@
       <c r="Z67" s="42"/>
       <c r="AA67" s="22"/>
     </row>
-    <row r="68" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T68" s="105" t="s">
+    <row r="68" spans="20:27">
+      <c r="T68" s="124" t="s">
         <v>230</v>
       </c>
-      <c r="U68" s="105"/>
-      <c r="V68" s="105"/>
-      <c r="W68" s="105"/>
-      <c r="X68" s="105"/>
-      <c r="Y68" s="105"/>
-      <c r="Z68" s="105"/>
+      <c r="U68" s="124"/>
+      <c r="V68" s="124"/>
+      <c r="W68" s="124"/>
+      <c r="X68" s="124"/>
+      <c r="Y68" s="124"/>
+      <c r="Z68" s="124"/>
       <c r="AA68" s="22"/>
     </row>
-    <row r="69" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T69" s="105" t="s">
+    <row r="69" spans="20:27">
+      <c r="T69" s="124" t="s">
         <v>231</v>
       </c>
-      <c r="U69" s="105"/>
-      <c r="V69" s="105"/>
-      <c r="W69" s="105"/>
-      <c r="X69" s="105"/>
-      <c r="Y69" s="105"/>
-      <c r="Z69" s="105"/>
+      <c r="U69" s="124"/>
+      <c r="V69" s="124"/>
+      <c r="W69" s="124"/>
+      <c r="X69" s="124"/>
+      <c r="Y69" s="124"/>
+      <c r="Z69" s="124"/>
       <c r="AA69" s="22"/>
     </row>
-    <row r="70" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T70" s="105" t="s">
+    <row r="70" spans="20:27">
+      <c r="T70" s="124" t="s">
         <v>241</v>
       </c>
-      <c r="U70" s="105"/>
-      <c r="V70" s="105"/>
-      <c r="W70" s="105"/>
-      <c r="X70" s="105"/>
-      <c r="Y70" s="105"/>
-      <c r="Z70" s="105"/>
+      <c r="U70" s="124"/>
+      <c r="V70" s="124"/>
+      <c r="W70" s="124"/>
+      <c r="X70" s="124"/>
+      <c r="Y70" s="124"/>
+      <c r="Z70" s="124"/>
       <c r="AA70" s="22"/>
     </row>
-    <row r="71" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T71" s="105" t="s">
+    <row r="71" spans="20:27">
+      <c r="T71" s="124" t="s">
         <v>242</v>
       </c>
-      <c r="U71" s="105"/>
-      <c r="V71" s="105"/>
-      <c r="W71" s="105"/>
-      <c r="X71" s="105"/>
-      <c r="Y71" s="105"/>
-      <c r="Z71" s="105"/>
+      <c r="U71" s="124"/>
+      <c r="V71" s="124"/>
+      <c r="W71" s="124"/>
+      <c r="X71" s="124"/>
+      <c r="Y71" s="124"/>
+      <c r="Z71" s="124"/>
       <c r="AA71" s="22"/>
     </row>
-    <row r="72" spans="20:27" x14ac:dyDescent="0.15">
-      <c r="T72" s="105" t="s">
+    <row r="72" spans="20:27">
+      <c r="T72" s="124" t="s">
         <v>234</v>
       </c>
-      <c r="U72" s="105"/>
-      <c r="V72" s="105"/>
-      <c r="W72" s="105"/>
-      <c r="X72" s="105"/>
-      <c r="Y72" s="105"/>
-      <c r="Z72" s="105"/>
+      <c r="U72" s="124"/>
+      <c r="V72" s="124"/>
+      <c r="W72" s="124"/>
+      <c r="X72" s="124"/>
+      <c r="Y72" s="124"/>
+      <c r="Z72" s="124"/>
       <c r="AA72" s="22"/>
     </row>
-    <row r="73" spans="20:27" x14ac:dyDescent="0.15">
+    <row r="73" spans="20:27">
       <c r="Z73" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="T68:Z68"/>
+    <mergeCell ref="T69:Z69"/>
+    <mergeCell ref="T70:Z70"/>
+    <mergeCell ref="T71:Z71"/>
+    <mergeCell ref="T72:Z72"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="T48:T67"/>
+    <mergeCell ref="U48:U51"/>
+    <mergeCell ref="U52:U55"/>
+    <mergeCell ref="U56:U59"/>
+    <mergeCell ref="U60:U63"/>
+    <mergeCell ref="U64:U67"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="T28:T47"/>
     <mergeCell ref="U28:U31"/>
@@ -12609,20 +12623,6 @@
     <mergeCell ref="T3:Z3"/>
     <mergeCell ref="T4:Z4"/>
     <mergeCell ref="T5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="T48:T67"/>
-    <mergeCell ref="U48:U51"/>
-    <mergeCell ref="U52:U55"/>
-    <mergeCell ref="U56:U59"/>
-    <mergeCell ref="U60:U63"/>
-    <mergeCell ref="U64:U67"/>
-    <mergeCell ref="T68:Z68"/>
-    <mergeCell ref="T69:Z69"/>
-    <mergeCell ref="T70:Z70"/>
-    <mergeCell ref="T71:Z71"/>
-    <mergeCell ref="T72:Z72"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12633,17 +12633,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA7462-7C15-4F70-B2AA-718A60064C68}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="3" max="3" width="8.703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="39" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="41.4">
       <c r="A3" s="102" t="s">
         <v>289</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4">
       <c r="A4" s="103" t="s">
         <v>293</v>
       </c>
@@ -12671,7 +12671,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4">
       <c r="A5" s="103" t="s">
         <v>295</v>
       </c>
@@ -12685,7 +12685,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4">
       <c r="A6" s="103" t="s">
         <v>297</v>
       </c>
@@ -12699,7 +12699,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4">
       <c r="A7" s="103" t="s">
         <v>68</v>
       </c>
@@ -12713,7 +12713,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4">
       <c r="A8" s="103" t="s">
         <v>91</v>
       </c>
@@ -12727,7 +12727,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4">
       <c r="A9" s="103" t="s">
         <v>301</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4">
       <c r="A10" s="103" t="s">
         <v>219</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4">
       <c r="A11" s="103" t="s">
         <v>303</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4">
       <c r="A12" s="103" t="s">
         <v>305</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4">
       <c r="A13" s="103" t="s">
         <v>219</v>
       </c>
@@ -12797,7 +12797,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4">
       <c r="A14" s="103" t="s">
         <v>306</v>
       </c>
@@ -12811,7 +12811,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>308</v>
       </c>
@@ -12824,29 +12824,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E53A4BD-4FF5-4CA6-9580-C622DFB3A388}">
   <dimension ref="B1:AM212"/>
-  <sheetFormatPr defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.1" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="0.734375" customWidth="1"/>
+    <col min="1" max="1" width="0.69921875" customWidth="1"/>
     <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.03125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.8046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.94921875" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.8984375" customWidth="1"/>
     <col min="22" max="31" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:39" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:39" ht="4.5" customHeight="1">
       <c r="V1" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="116" t="s">
+    <row r="2" spans="2:39" ht="14.1" customHeight="1">
+      <c r="B2" s="105" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-    </row>
-    <row r="3" spans="2:39" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+    </row>
+    <row r="3" spans="2:39" ht="14.1" customHeight="1" thickBot="1">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -12856,20 +12856,20 @@
       <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="V3" s="149" t="s">
+      <c r="V3" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="W3" s="149"/>
-      <c r="X3" s="149"/>
-      <c r="Y3" s="149"/>
-      <c r="Z3" s="149"/>
-      <c r="AA3" s="149"/>
-      <c r="AB3" s="149"/>
-      <c r="AC3" s="149"/>
-      <c r="AD3" s="149"/>
-      <c r="AE3" s="149"/>
-    </row>
-    <row r="4" spans="2:39" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="W3" s="131"/>
+      <c r="X3" s="131"/>
+      <c r="Y3" s="131"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="131"/>
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+      <c r="AE3" s="131"/>
+    </row>
+    <row r="4" spans="2:39" ht="14.1" customHeight="1" thickBot="1">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -12884,30 +12884,30 @@
         <f>D4/100</f>
         <v>0.92982815533324059</v>
       </c>
-      <c r="V4" s="147"/>
-      <c r="W4" s="147"/>
-      <c r="X4" s="147"/>
-      <c r="Y4" s="147"/>
-      <c r="Z4" s="147"/>
-      <c r="AA4" s="148" t="s">
+      <c r="V4" s="129"/>
+      <c r="W4" s="129"/>
+      <c r="X4" s="129"/>
+      <c r="Y4" s="129"/>
+      <c r="Z4" s="129"/>
+      <c r="AA4" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="AB4" s="148"/>
+      <c r="AB4" s="130"/>
       <c r="AC4" s="19"/>
-      <c r="AD4" s="147"/>
-      <c r="AE4" s="147"/>
-      <c r="AF4" s="133" t="s">
+      <c r="AD4" s="129"/>
+      <c r="AE4" s="129"/>
+      <c r="AF4" s="132" t="s">
         <v>222</v>
       </c>
-      <c r="AG4" s="133"/>
-      <c r="AH4" s="133"/>
-      <c r="AI4" s="133"/>
-      <c r="AJ4" s="133"/>
-      <c r="AK4" s="133"/>
-      <c r="AL4" s="133"/>
+      <c r="AG4" s="132"/>
+      <c r="AH4" s="132"/>
+      <c r="AI4" s="132"/>
+      <c r="AJ4" s="132"/>
+      <c r="AK4" s="132"/>
+      <c r="AL4" s="132"/>
       <c r="AM4" s="60"/>
     </row>
-    <row r="5" spans="2:39" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:39" ht="14.1" customHeight="1" thickBot="1">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -12922,13 +12922,13 @@
         <f t="shared" ref="E5:E15" si="0">D5/100</f>
         <v>0.41022835413459646</v>
       </c>
-      <c r="V5" s="146"/>
-      <c r="W5" s="146"/>
+      <c r="V5" s="128"/>
+      <c r="W5" s="128"/>
       <c r="X5" s="18"/>
-      <c r="Y5" s="146" t="s">
+      <c r="Y5" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="Z5" s="146"/>
+      <c r="Z5" s="128"/>
       <c r="AA5" s="20" t="s">
         <v>27</v>
       </c>
@@ -12938,24 +12938,24 @@
       <c r="AC5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="AD5" s="146" t="s">
+      <c r="AD5" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="AE5" s="146"/>
-      <c r="AF5" s="134" t="s">
+      <c r="AE5" s="128"/>
+      <c r="AF5" s="133" t="s">
         <v>223</v>
       </c>
-      <c r="AG5" s="134" t="s">
+      <c r="AG5" s="133" t="s">
         <v>256</v>
       </c>
-      <c r="AH5" s="135"/>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="135"/>
-      <c r="AL5" s="135"/>
+      <c r="AH5" s="134"/>
+      <c r="AI5" s="134"/>
+      <c r="AJ5" s="134"/>
+      <c r="AK5" s="134"/>
+      <c r="AL5" s="134"/>
       <c r="AM5" s="60"/>
     </row>
-    <row r="6" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:39" ht="14.1" customHeight="1">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -12994,24 +12994,24 @@
         <v>1000</v>
       </c>
       <c r="AE6" s="3"/>
-      <c r="AF6" s="136" t="s">
+      <c r="AF6" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="AG6" s="136"/>
-      <c r="AH6" s="136"/>
-      <c r="AI6" s="138" t="s">
+      <c r="AG6" s="135"/>
+      <c r="AH6" s="135"/>
+      <c r="AI6" s="137" t="s">
         <v>224</v>
       </c>
-      <c r="AJ6" s="140" t="s">
+      <c r="AJ6" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="AK6" s="140" t="s">
+      <c r="AK6" s="139" t="s">
         <v>236</v>
       </c>
-      <c r="AL6" s="142"/>
+      <c r="AL6" s="141"/>
       <c r="AM6" s="60"/>
     </row>
-    <row r="7" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:39" ht="14.1" customHeight="1">
       <c r="B7" t="s">
         <v>19</v>
       </c>
@@ -13048,11 +13048,11 @@
         <v>1000</v>
       </c>
       <c r="AE7" s="3"/>
-      <c r="AF7" s="137"/>
-      <c r="AG7" s="137"/>
-      <c r="AH7" s="137"/>
-      <c r="AI7" s="139"/>
-      <c r="AJ7" s="141"/>
+      <c r="AF7" s="136"/>
+      <c r="AG7" s="136"/>
+      <c r="AH7" s="136"/>
+      <c r="AI7" s="138"/>
+      <c r="AJ7" s="140"/>
       <c r="AK7" s="62" t="s">
         <v>225</v>
       </c>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="AM7" s="60"/>
     </row>
-    <row r="8" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:39" ht="14.1" customHeight="1">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -13100,10 +13100,10 @@
       <c r="AE8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF8" s="131" t="s">
+      <c r="AF8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="AG8" s="132" t="s">
+      <c r="AG8" s="145" t="s">
         <v>5</v>
       </c>
       <c r="AH8" s="90" t="s">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="AM8" s="60"/>
     </row>
-    <row r="9" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:39" ht="14.1" customHeight="1">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -13162,8 +13162,8 @@
       <c r="AE9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF9" s="127"/>
-      <c r="AG9" s="130"/>
+      <c r="AF9" s="143"/>
+      <c r="AG9" s="146"/>
       <c r="AH9" s="81" t="s">
         <v>7</v>
       </c>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="AM9" s="60"/>
     </row>
-    <row r="10" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:39" ht="14.1" customHeight="1">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -13206,8 +13206,8 @@
       <c r="AC10" s="4"/>
       <c r="AD10" s="5"/>
       <c r="AE10" s="3"/>
-      <c r="AF10" s="127"/>
-      <c r="AG10" s="130"/>
+      <c r="AF10" s="143"/>
+      <c r="AG10" s="146"/>
       <c r="AH10" s="81"/>
       <c r="AI10" s="82"/>
       <c r="AJ10" s="83"/>
@@ -13215,7 +13215,7 @@
       <c r="AL10" s="84"/>
       <c r="AM10" s="60"/>
     </row>
-    <row r="11" spans="2:39" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:39" ht="13.95" customHeight="1">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -13254,8 +13254,8 @@
       <c r="AE11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF11" s="127"/>
-      <c r="AG11" s="130"/>
+      <c r="AF11" s="143"/>
+      <c r="AG11" s="146"/>
       <c r="AH11" s="81"/>
       <c r="AI11" s="85"/>
       <c r="AJ11" s="94"/>
@@ -13263,7 +13263,7 @@
       <c r="AL11" s="95"/>
       <c r="AM11" s="60"/>
     </row>
-    <row r="12" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:39" ht="14.1" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
@@ -13302,8 +13302,8 @@
       <c r="AE12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF12" s="127"/>
-      <c r="AG12" s="129"/>
+      <c r="AF12" s="143"/>
+      <c r="AG12" s="147"/>
       <c r="AH12" s="86"/>
       <c r="AI12" s="87"/>
       <c r="AJ12" s="96"/>
@@ -13311,7 +13311,7 @@
       <c r="AL12" s="97"/>
       <c r="AM12" s="60"/>
     </row>
-    <row r="13" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:39" ht="14.1" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
@@ -13348,8 +13348,8 @@
         <v>52</v>
       </c>
       <c r="AE13" s="3"/>
-      <c r="AF13" s="127"/>
-      <c r="AG13" s="126" t="s">
+      <c r="AF13" s="143"/>
+      <c r="AG13" s="144" t="s">
         <v>6</v>
       </c>
       <c r="AH13" s="64" t="s">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="AM13" s="60"/>
     </row>
-    <row r="14" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:39" ht="14.1" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
@@ -13408,8 +13408,8 @@
       <c r="AE14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF14" s="127"/>
-      <c r="AG14" s="127"/>
+      <c r="AF14" s="143"/>
+      <c r="AG14" s="143"/>
       <c r="AH14" s="64" t="s">
         <v>7</v>
       </c>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="AM14" s="60"/>
     </row>
-    <row r="15" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:39" ht="14.1" customHeight="1">
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
@@ -13466,8 +13466,8 @@
       <c r="AE15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF15" s="127"/>
-      <c r="AG15" s="127"/>
+      <c r="AF15" s="143"/>
+      <c r="AG15" s="143"/>
       <c r="AH15" s="64" t="s">
         <v>8</v>
       </c>
@@ -13479,7 +13479,7 @@
       <c r="AL15" s="70"/>
       <c r="AM15" s="60"/>
     </row>
-    <row r="16" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:39" ht="14.1" customHeight="1">
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3" t="s">
@@ -13504,8 +13504,8 @@
       <c r="AE16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF16" s="127"/>
-      <c r="AG16" s="126"/>
+      <c r="AF16" s="143"/>
+      <c r="AG16" s="144"/>
       <c r="AH16" s="71" t="s">
         <v>227</v>
       </c>
@@ -13517,7 +13517,7 @@
       <c r="AL16" s="74"/>
       <c r="AM16" s="60"/>
     </row>
-    <row r="17" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="6:39" ht="14.1" customHeight="1">
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3" t="s">
@@ -13542,8 +13542,8 @@
       <c r="AE17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF17" s="127"/>
-      <c r="AG17" s="126" t="s">
+      <c r="AF17" s="143"/>
+      <c r="AG17" s="144" t="s">
         <v>7</v>
       </c>
       <c r="AH17" s="64" t="s">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="AM17" s="60"/>
     </row>
-    <row r="18" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="6:39" ht="14.1" customHeight="1">
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3" t="s">
@@ -13588,8 +13588,8 @@
       <c r="AE18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF18" s="127"/>
-      <c r="AG18" s="127"/>
+      <c r="AF18" s="143"/>
+      <c r="AG18" s="143"/>
       <c r="AH18" s="64" t="s">
         <v>6</v>
       </c>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="AM18" s="60"/>
     </row>
-    <row r="19" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="6:39" ht="14.1" customHeight="1">
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3" t="s">
@@ -13632,8 +13632,8 @@
       <c r="AE19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF19" s="127"/>
-      <c r="AG19" s="127"/>
+      <c r="AF19" s="143"/>
+      <c r="AG19" s="143"/>
       <c r="AH19" s="64"/>
       <c r="AI19" s="68"/>
       <c r="AJ19" s="69"/>
@@ -13641,7 +13641,7 @@
       <c r="AL19" s="70"/>
       <c r="AM19" s="60"/>
     </row>
-    <row r="20" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="6:39" ht="14.1" customHeight="1">
       <c r="V20" s="3" t="s">
         <v>32</v>
       </c>
@@ -13666,8 +13666,8 @@
         <v>1000</v>
       </c>
       <c r="AE20" s="3"/>
-      <c r="AF20" s="127"/>
-      <c r="AG20" s="126"/>
+      <c r="AF20" s="143"/>
+      <c r="AG20" s="144"/>
       <c r="AH20" s="71"/>
       <c r="AI20" s="72"/>
       <c r="AJ20" s="73"/>
@@ -13675,7 +13675,7 @@
       <c r="AL20" s="74"/>
       <c r="AM20" s="60"/>
     </row>
-    <row r="21" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="6:39" ht="14.1" customHeight="1">
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3" t="s">
@@ -13698,8 +13698,8 @@
         <v>63</v>
       </c>
       <c r="AE21" s="3"/>
-      <c r="AF21" s="127"/>
-      <c r="AG21" s="126" t="s">
+      <c r="AF21" s="143"/>
+      <c r="AG21" s="144" t="s">
         <v>8</v>
       </c>
       <c r="AH21" s="64"/>
@@ -13709,7 +13709,7 @@
       <c r="AL21" s="70"/>
       <c r="AM21" s="60"/>
     </row>
-    <row r="22" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="6:39" ht="14.1" customHeight="1">
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3" t="s">
@@ -13732,8 +13732,8 @@
         <v>64</v>
       </c>
       <c r="AE22" s="3"/>
-      <c r="AF22" s="127"/>
-      <c r="AG22" s="127"/>
+      <c r="AF22" s="143"/>
+      <c r="AG22" s="143"/>
       <c r="AH22" s="64"/>
       <c r="AI22" s="68"/>
       <c r="AJ22" s="69"/>
@@ -13741,7 +13741,7 @@
       <c r="AL22" s="70"/>
       <c r="AM22" s="60"/>
     </row>
-    <row r="23" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="6:39" ht="14.1" customHeight="1">
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3" t="s">
@@ -13764,8 +13764,8 @@
         <v>1000</v>
       </c>
       <c r="AE23" s="3"/>
-      <c r="AF23" s="127"/>
-      <c r="AG23" s="127"/>
+      <c r="AF23" s="143"/>
+      <c r="AG23" s="143"/>
       <c r="AH23" s="64"/>
       <c r="AI23" s="68"/>
       <c r="AJ23" s="69"/>
@@ -13773,7 +13773,7 @@
       <c r="AL23" s="70"/>
       <c r="AM23" s="60"/>
     </row>
-    <row r="24" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="6:39" ht="14.1" customHeight="1">
       <c r="F24" s="21"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -13799,8 +13799,8 @@
       <c r="AE24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF24" s="127"/>
-      <c r="AG24" s="126"/>
+      <c r="AF24" s="143"/>
+      <c r="AG24" s="144"/>
       <c r="AH24" s="71"/>
       <c r="AI24" s="72"/>
       <c r="AJ24" s="73"/>
@@ -13808,7 +13808,7 @@
       <c r="AL24" s="74"/>
       <c r="AM24" s="60"/>
     </row>
-    <row r="25" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="6:39" ht="14.1" customHeight="1">
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3" t="s">
@@ -13833,8 +13833,8 @@
       <c r="AE25" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF25" s="127"/>
-      <c r="AG25" s="126" t="s">
+      <c r="AF25" s="143"/>
+      <c r="AG25" s="144" t="s">
         <v>227</v>
       </c>
       <c r="AH25" s="64"/>
@@ -13844,7 +13844,7 @@
       <c r="AL25" s="70"/>
       <c r="AM25" s="60"/>
     </row>
-    <row r="26" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="6:39" ht="14.1" customHeight="1">
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3" t="s">
@@ -13869,8 +13869,8 @@
       <c r="AE26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF26" s="127"/>
-      <c r="AG26" s="127"/>
+      <c r="AF26" s="143"/>
+      <c r="AG26" s="143"/>
       <c r="AH26" s="64"/>
       <c r="AI26" s="68"/>
       <c r="AJ26" s="69"/>
@@ -13878,7 +13878,7 @@
       <c r="AL26" s="70"/>
       <c r="AM26" s="60"/>
     </row>
-    <row r="27" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="6:39" ht="14.1" customHeight="1">
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3" t="s">
@@ -13903,8 +13903,8 @@
       <c r="AE27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF27" s="127"/>
-      <c r="AG27" s="127"/>
+      <c r="AF27" s="143"/>
+      <c r="AG27" s="143"/>
       <c r="AH27" s="64"/>
       <c r="AI27" s="68"/>
       <c r="AJ27" s="69"/>
@@ -13912,7 +13912,7 @@
       <c r="AL27" s="70"/>
       <c r="AM27" s="60"/>
     </row>
-    <row r="28" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="6:39" ht="14.1" customHeight="1">
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3" t="s">
@@ -13937,8 +13937,8 @@
       <c r="AE28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF28" s="126"/>
-      <c r="AG28" s="126"/>
+      <c r="AF28" s="144"/>
+      <c r="AG28" s="144"/>
       <c r="AH28" s="71"/>
       <c r="AI28" s="72"/>
       <c r="AJ28" s="73"/>
@@ -13946,7 +13946,7 @@
       <c r="AL28" s="74"/>
       <c r="AM28" s="60"/>
     </row>
-    <row r="29" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="6:39" ht="14.1" customHeight="1">
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3" t="s">
@@ -13971,10 +13971,10 @@
       <c r="AE29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF29" s="126" t="s">
+      <c r="AF29" s="144" t="s">
         <v>228</v>
       </c>
-      <c r="AG29" s="129" t="s">
+      <c r="AG29" s="147" t="s">
         <v>5</v>
       </c>
       <c r="AH29" s="81" t="s">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="AM29" s="60"/>
     </row>
-    <row r="30" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="6:39" ht="14.1" customHeight="1">
       <c r="P30" s="21"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -14018,8 +14018,8 @@
         <v>67</v>
       </c>
       <c r="AD30" s="3"/>
-      <c r="AF30" s="127"/>
-      <c r="AG30" s="130"/>
+      <c r="AF30" s="143"/>
+      <c r="AG30" s="146"/>
       <c r="AH30" s="81" t="s">
         <v>7</v>
       </c>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="AM30" s="60"/>
     </row>
-    <row r="31" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="6:39" ht="14.1" customHeight="1">
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="s">
@@ -14062,8 +14062,8 @@
       <c r="AD31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF31" s="127"/>
-      <c r="AG31" s="130"/>
+      <c r="AF31" s="143"/>
+      <c r="AG31" s="146"/>
       <c r="AH31" s="81" t="s">
         <v>8</v>
       </c>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="AM31" s="60"/>
     </row>
-    <row r="32" spans="6:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="6:39" ht="14.1" customHeight="1">
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="s">
@@ -14106,8 +14106,8 @@
       <c r="AD32" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF32" s="127"/>
-      <c r="AG32" s="129"/>
+      <c r="AF32" s="143"/>
+      <c r="AG32" s="147"/>
       <c r="AH32" s="86" t="s">
         <v>227</v>
       </c>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="AM32" s="60"/>
     </row>
-    <row r="33" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="21:39" ht="14.1" customHeight="1">
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="s">
@@ -14148,8 +14148,8 @@
         <v>67</v>
       </c>
       <c r="AD33" s="3"/>
-      <c r="AF33" s="127"/>
-      <c r="AG33" s="126" t="s">
+      <c r="AF33" s="143"/>
+      <c r="AG33" s="144" t="s">
         <v>6</v>
       </c>
       <c r="AH33" s="64" t="s">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="AM33" s="60"/>
     </row>
-    <row r="34" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="21:39" ht="14.1" customHeight="1">
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
@@ -14194,8 +14194,8 @@
       <c r="AD34" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF34" s="127"/>
-      <c r="AG34" s="127"/>
+      <c r="AF34" s="143"/>
+      <c r="AG34" s="143"/>
       <c r="AH34" s="64" t="s">
         <v>7</v>
       </c>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="AM34" s="60"/>
     </row>
-    <row r="35" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="21:39" ht="14.1" customHeight="1">
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
@@ -14238,8 +14238,8 @@
       <c r="AD35" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF35" s="127"/>
-      <c r="AG35" s="127"/>
+      <c r="AF35" s="143"/>
+      <c r="AG35" s="143"/>
       <c r="AH35" s="64" t="s">
         <v>8</v>
       </c>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="AM35" s="60"/>
     </row>
-    <row r="36" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="21:39" ht="14.1" customHeight="1">
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
@@ -14282,8 +14282,8 @@
       <c r="AD36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF36" s="127"/>
-      <c r="AG36" s="126"/>
+      <c r="AF36" s="143"/>
+      <c r="AG36" s="144"/>
       <c r="AH36" s="71" t="s">
         <v>227</v>
       </c>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="AM36" s="60"/>
     </row>
-    <row r="37" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="21:39" ht="14.1" customHeight="1">
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="s">
@@ -14326,8 +14326,8 @@
       <c r="AD37" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF37" s="127"/>
-      <c r="AG37" s="126" t="s">
+      <c r="AF37" s="143"/>
+      <c r="AG37" s="144" t="s">
         <v>7</v>
       </c>
       <c r="AH37" s="64" t="s">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="AM37" s="60"/>
     </row>
-    <row r="38" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="21:39" ht="14.1" customHeight="1">
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="s">
@@ -14372,8 +14372,8 @@
       <c r="AD38" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF38" s="127"/>
-      <c r="AG38" s="127"/>
+      <c r="AF38" s="143"/>
+      <c r="AG38" s="143"/>
       <c r="AH38" s="64" t="s">
         <v>6</v>
       </c>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="AM38" s="60"/>
     </row>
-    <row r="39" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="21:39" ht="14.1" customHeight="1">
       <c r="U39" s="3" t="s">
         <v>33</v>
       </c>
@@ -14416,8 +14416,8 @@
         <v>63</v>
       </c>
       <c r="AD39" s="3"/>
-      <c r="AF39" s="127"/>
-      <c r="AG39" s="127"/>
+      <c r="AF39" s="143"/>
+      <c r="AG39" s="143"/>
       <c r="AH39" s="64" t="s">
         <v>8</v>
       </c>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="AM39" s="60"/>
     </row>
-    <row r="40" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="21:39" ht="14.1" customHeight="1">
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="s">
@@ -14458,8 +14458,8 @@
         <v>38</v>
       </c>
       <c r="AD40" s="3"/>
-      <c r="AF40" s="127"/>
-      <c r="AG40" s="126"/>
+      <c r="AF40" s="143"/>
+      <c r="AG40" s="144"/>
       <c r="AH40" s="71" t="s">
         <v>227</v>
       </c>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="AM40" s="60"/>
     </row>
-    <row r="41" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="21:39" ht="14.1" customHeight="1">
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="s">
@@ -14500,8 +14500,8 @@
         <v>1000</v>
       </c>
       <c r="AD41" s="3"/>
-      <c r="AF41" s="127"/>
-      <c r="AG41" s="126" t="s">
+      <c r="AF41" s="143"/>
+      <c r="AG41" s="144" t="s">
         <v>8</v>
       </c>
       <c r="AH41" s="64" t="s">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="AM41" s="60"/>
     </row>
-    <row r="42" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="21:39" ht="14.1" customHeight="1">
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
@@ -14546,8 +14546,8 @@
       <c r="AD42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF42" s="127"/>
-      <c r="AG42" s="127"/>
+      <c r="AF42" s="143"/>
+      <c r="AG42" s="143"/>
       <c r="AH42" s="64" t="s">
         <v>6</v>
       </c>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="AM42" s="60"/>
     </row>
-    <row r="43" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="21:39" ht="14.1" customHeight="1">
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
@@ -14590,8 +14590,8 @@
       <c r="AD43" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF43" s="127"/>
-      <c r="AG43" s="127"/>
+      <c r="AF43" s="143"/>
+      <c r="AG43" s="143"/>
       <c r="AH43" s="64" t="s">
         <v>7</v>
       </c>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="AM43" s="60"/>
     </row>
-    <row r="44" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="21:39" ht="14.1" customHeight="1">
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="s">
@@ -14634,8 +14634,8 @@
       <c r="AD44" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF44" s="127"/>
-      <c r="AG44" s="126"/>
+      <c r="AF44" s="143"/>
+      <c r="AG44" s="144"/>
       <c r="AH44" s="71" t="s">
         <v>227</v>
       </c>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="AM44" s="60"/>
     </row>
-    <row r="45" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="21:39" ht="14.1" customHeight="1">
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="s">
@@ -14678,8 +14678,8 @@
       <c r="AD45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF45" s="127"/>
-      <c r="AG45" s="126" t="s">
+      <c r="AF45" s="143"/>
+      <c r="AG45" s="144" t="s">
         <v>227</v>
       </c>
       <c r="AH45" s="64" t="s">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="AM45" s="60"/>
     </row>
-    <row r="46" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="21:39" ht="14.1" customHeight="1">
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="s">
@@ -14724,8 +14724,8 @@
       <c r="AD46" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF46" s="127"/>
-      <c r="AG46" s="127"/>
+      <c r="AF46" s="143"/>
+      <c r="AG46" s="143"/>
       <c r="AH46" s="64" t="s">
         <v>6</v>
       </c>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="AM46" s="60"/>
     </row>
-    <row r="47" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="21:39" ht="14.1" customHeight="1">
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
@@ -14768,8 +14768,8 @@
       <c r="AD47" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF47" s="127"/>
-      <c r="AG47" s="127"/>
+      <c r="AF47" s="143"/>
+      <c r="AG47" s="143"/>
       <c r="AH47" s="64" t="s">
         <v>7</v>
       </c>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="AM47" s="60"/>
     </row>
-    <row r="48" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="21:39" ht="14.1" customHeight="1">
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="s">
@@ -14810,8 +14810,8 @@
         <v>67</v>
       </c>
       <c r="AD48" s="3"/>
-      <c r="AF48" s="126"/>
-      <c r="AG48" s="126"/>
+      <c r="AF48" s="144"/>
+      <c r="AG48" s="144"/>
       <c r="AH48" s="71" t="s">
         <v>8</v>
       </c>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="AM48" s="60"/>
     </row>
-    <row r="49" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="21:39" ht="14.1" customHeight="1">
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="s">
@@ -14854,10 +14854,10 @@
       <c r="AD49" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF49" s="126" t="s">
+      <c r="AF49" s="144" t="s">
         <v>229</v>
       </c>
-      <c r="AG49" s="129" t="s">
+      <c r="AG49" s="147" t="s">
         <v>5</v>
       </c>
       <c r="AH49" s="81" t="s">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="AM49" s="60"/>
     </row>
-    <row r="50" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="21:39" ht="14.1" customHeight="1">
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="s">
@@ -14902,8 +14902,8 @@
       <c r="AD50" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF50" s="127"/>
-      <c r="AG50" s="130"/>
+      <c r="AF50" s="143"/>
+      <c r="AG50" s="146"/>
       <c r="AH50" s="81" t="s">
         <v>7</v>
       </c>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="AM50" s="60"/>
     </row>
-    <row r="51" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="21:39" ht="14.1" customHeight="1">
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="s">
@@ -14944,8 +14944,8 @@
         <v>67</v>
       </c>
       <c r="AD51" s="3"/>
-      <c r="AF51" s="127"/>
-      <c r="AG51" s="130"/>
+      <c r="AF51" s="143"/>
+      <c r="AG51" s="146"/>
       <c r="AH51" s="81" t="s">
         <v>8</v>
       </c>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AM51" s="60"/>
     </row>
-    <row r="52" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="21:39" ht="14.1" customHeight="1">
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="s">
@@ -14988,8 +14988,8 @@
       <c r="AD52" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF52" s="127"/>
-      <c r="AG52" s="129"/>
+      <c r="AF52" s="143"/>
+      <c r="AG52" s="147"/>
       <c r="AH52" s="86" t="s">
         <v>227</v>
       </c>
@@ -15001,7 +15001,7 @@
       <c r="AL52" s="97"/>
       <c r="AM52" s="60"/>
     </row>
-    <row r="53" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="21:39" ht="14.1" customHeight="1">
       <c r="U53" s="3"/>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="s">
@@ -15026,8 +15026,8 @@
       <c r="AD53" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF53" s="127"/>
-      <c r="AG53" s="126" t="s">
+      <c r="AF53" s="143"/>
+      <c r="AG53" s="144" t="s">
         <v>6</v>
       </c>
       <c r="AH53" s="64" t="s">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="AM53" s="60"/>
     </row>
-    <row r="54" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="21:39" ht="14.1" customHeight="1">
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="s">
@@ -15072,8 +15072,8 @@
       <c r="AD54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF54" s="127"/>
-      <c r="AG54" s="127"/>
+      <c r="AF54" s="143"/>
+      <c r="AG54" s="143"/>
       <c r="AH54" s="64" t="s">
         <v>7</v>
       </c>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="AM54" s="60"/>
     </row>
-    <row r="55" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="21:39" ht="14.1" customHeight="1">
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="s">
@@ -15116,8 +15116,8 @@
       <c r="AD55" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF55" s="127"/>
-      <c r="AG55" s="127"/>
+      <c r="AF55" s="143"/>
+      <c r="AG55" s="143"/>
       <c r="AH55" s="64" t="s">
         <v>8</v>
       </c>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="AM55" s="60"/>
     </row>
-    <row r="56" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="21:39" ht="14.1" customHeight="1">
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="s">
@@ -15160,8 +15160,8 @@
       <c r="AD56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AF56" s="127"/>
-      <c r="AG56" s="126"/>
+      <c r="AF56" s="143"/>
+      <c r="AG56" s="144"/>
       <c r="AH56" s="71" t="s">
         <v>227</v>
       </c>
@@ -15173,7 +15173,7 @@
       <c r="AL56" s="74"/>
       <c r="AM56" s="60"/>
     </row>
-    <row r="57" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="21:39" ht="14.1" customHeight="1">
       <c r="U57" s="3" t="s">
         <v>34</v>
       </c>
@@ -15198,8 +15198,8 @@
         <v>1000</v>
       </c>
       <c r="AD57" s="3"/>
-      <c r="AF57" s="127"/>
-      <c r="AG57" s="126" t="s">
+      <c r="AF57" s="143"/>
+      <c r="AG57" s="144" t="s">
         <v>7</v>
       </c>
       <c r="AH57" s="64" t="s">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AM57" s="60"/>
     </row>
-    <row r="58" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="21:39" ht="14.1" customHeight="1">
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="s">
@@ -15242,8 +15242,8 @@
         <v>1000</v>
       </c>
       <c r="AD58" s="3"/>
-      <c r="AF58" s="127"/>
-      <c r="AG58" s="127"/>
+      <c r="AF58" s="143"/>
+      <c r="AG58" s="143"/>
       <c r="AH58" s="64" t="s">
         <v>6</v>
       </c>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="AM58" s="60"/>
     </row>
-    <row r="59" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="21:39" ht="14.1" customHeight="1">
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="s">
@@ -15284,8 +15284,8 @@
         <v>72</v>
       </c>
       <c r="AD59" s="3"/>
-      <c r="AF59" s="127"/>
-      <c r="AG59" s="127"/>
+      <c r="AF59" s="143"/>
+      <c r="AG59" s="143"/>
       <c r="AH59" s="64" t="s">
         <v>8</v>
       </c>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="AM59" s="60"/>
     </row>
-    <row r="60" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="21:39" ht="14.1" customHeight="1">
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="s">
@@ -15326,8 +15326,8 @@
         <v>67</v>
       </c>
       <c r="AD60" s="3"/>
-      <c r="AF60" s="127"/>
-      <c r="AG60" s="126"/>
+      <c r="AF60" s="143"/>
+      <c r="AG60" s="144"/>
       <c r="AH60" s="71" t="s">
         <v>227</v>
       </c>
@@ -15339,7 +15339,7 @@
       <c r="AL60" s="74"/>
       <c r="AM60" s="60"/>
     </row>
-    <row r="61" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="21:39" ht="14.1" customHeight="1">
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="s">
@@ -15364,8 +15364,8 @@
       <c r="AD61" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AF61" s="127"/>
-      <c r="AG61" s="126" t="s">
+      <c r="AF61" s="143"/>
+      <c r="AG61" s="144" t="s">
         <v>8</v>
       </c>
       <c r="AH61" s="64" t="s">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AM61" s="60"/>
     </row>
-    <row r="62" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="21:39" ht="14.1" customHeight="1">
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="s">
@@ -15408,8 +15408,8 @@
         <v>1000</v>
       </c>
       <c r="AD62" s="3"/>
-      <c r="AF62" s="127"/>
-      <c r="AG62" s="127"/>
+      <c r="AF62" s="143"/>
+      <c r="AG62" s="143"/>
       <c r="AH62" s="64" t="s">
         <v>6</v>
       </c>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="AM62" s="60"/>
     </row>
-    <row r="63" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="21:39" ht="14.1" customHeight="1">
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="s">
@@ -15450,8 +15450,8 @@
         <v>1000</v>
       </c>
       <c r="AD63" s="3"/>
-      <c r="AF63" s="127"/>
-      <c r="AG63" s="127"/>
+      <c r="AF63" s="143"/>
+      <c r="AG63" s="143"/>
       <c r="AH63" s="64" t="s">
         <v>7</v>
       </c>
@@ -15469,7 +15469,7 @@
       </c>
       <c r="AM63" s="60"/>
     </row>
-    <row r="64" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="21:39" ht="14.1" customHeight="1">
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="s">
@@ -15492,8 +15492,8 @@
         <v>1000</v>
       </c>
       <c r="AD64" s="3"/>
-      <c r="AF64" s="127"/>
-      <c r="AG64" s="126"/>
+      <c r="AF64" s="143"/>
+      <c r="AG64" s="144"/>
       <c r="AH64" s="71" t="s">
         <v>227</v>
       </c>
@@ -15505,7 +15505,7 @@
       <c r="AL64" s="74"/>
       <c r="AM64" s="60"/>
     </row>
-    <row r="65" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="21:39" ht="14.1" customHeight="1">
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3" t="s">
@@ -15528,8 +15528,8 @@
         <v>1000</v>
       </c>
       <c r="AD65" s="3"/>
-      <c r="AF65" s="127"/>
-      <c r="AG65" s="126" t="s">
+      <c r="AF65" s="143"/>
+      <c r="AG65" s="144" t="s">
         <v>227</v>
       </c>
       <c r="AH65" s="64" t="s">
@@ -15543,7 +15543,7 @@
       <c r="AL65" s="70"/>
       <c r="AM65" s="60"/>
     </row>
-    <row r="66" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="21:39" ht="14.1" customHeight="1">
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
       <c r="W66" s="3" t="s">
@@ -15566,8 +15566,8 @@
         <v>1000</v>
       </c>
       <c r="AD66" s="3"/>
-      <c r="AF66" s="127"/>
-      <c r="AG66" s="127"/>
+      <c r="AF66" s="143"/>
+      <c r="AG66" s="143"/>
       <c r="AH66" s="64" t="s">
         <v>6</v>
       </c>
@@ -15579,7 +15579,7 @@
       <c r="AL66" s="70"/>
       <c r="AM66" s="60"/>
     </row>
-    <row r="67" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="21:39" ht="14.1" customHeight="1">
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3" t="s">
@@ -15602,8 +15602,8 @@
         <v>1000</v>
       </c>
       <c r="AD67" s="3"/>
-      <c r="AF67" s="127"/>
-      <c r="AG67" s="127"/>
+      <c r="AF67" s="143"/>
+      <c r="AG67" s="143"/>
       <c r="AH67" s="64" t="s">
         <v>7</v>
       </c>
@@ -15615,7 +15615,7 @@
       <c r="AL67" s="70"/>
       <c r="AM67" s="60"/>
     </row>
-    <row r="68" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="21:39" ht="14.1" customHeight="1">
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="s">
@@ -15638,8 +15638,8 @@
         <v>1000</v>
       </c>
       <c r="AD68" s="3"/>
-      <c r="AF68" s="128"/>
-      <c r="AG68" s="128"/>
+      <c r="AF68" s="148"/>
+      <c r="AG68" s="148"/>
       <c r="AH68" s="61" t="s">
         <v>8</v>
       </c>
@@ -15651,7 +15651,7 @@
       <c r="AL68" s="80"/>
       <c r="AM68" s="60"/>
     </row>
-    <row r="69" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="21:39" ht="14.1" customHeight="1">
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3" t="s">
@@ -15674,18 +15674,18 @@
         <v>84</v>
       </c>
       <c r="AD69" s="3"/>
-      <c r="AF69" s="125" t="s">
+      <c r="AF69" s="149" t="s">
         <v>230</v>
       </c>
-      <c r="AG69" s="125"/>
-      <c r="AH69" s="125"/>
-      <c r="AI69" s="125"/>
-      <c r="AJ69" s="125"/>
-      <c r="AK69" s="125"/>
-      <c r="AL69" s="125"/>
+      <c r="AG69" s="149"/>
+      <c r="AH69" s="149"/>
+      <c r="AI69" s="149"/>
+      <c r="AJ69" s="149"/>
+      <c r="AK69" s="149"/>
+      <c r="AL69" s="149"/>
       <c r="AM69" s="60"/>
     </row>
-    <row r="70" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="21:39" ht="14.1" customHeight="1">
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
       <c r="W70" s="3" t="s">
@@ -15708,18 +15708,18 @@
         <v>1000</v>
       </c>
       <c r="AD70" s="3"/>
-      <c r="AF70" s="125" t="s">
+      <c r="AF70" s="149" t="s">
         <v>231</v>
       </c>
-      <c r="AG70" s="125"/>
-      <c r="AH70" s="125"/>
-      <c r="AI70" s="125"/>
-      <c r="AJ70" s="125"/>
-      <c r="AK70" s="125"/>
-      <c r="AL70" s="125"/>
+      <c r="AG70" s="149"/>
+      <c r="AH70" s="149"/>
+      <c r="AI70" s="149"/>
+      <c r="AJ70" s="149"/>
+      <c r="AK70" s="149"/>
+      <c r="AL70" s="149"/>
       <c r="AM70" s="60"/>
     </row>
-    <row r="71" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="21:39" ht="14.1" customHeight="1">
       <c r="U71" s="3"/>
       <c r="V71" s="3"/>
       <c r="W71" s="3" t="s">
@@ -15742,18 +15742,18 @@
         <v>1000</v>
       </c>
       <c r="AD71" s="3"/>
-      <c r="AF71" s="125" t="s">
+      <c r="AF71" s="149" t="s">
         <v>232</v>
       </c>
-      <c r="AG71" s="125"/>
-      <c r="AH71" s="125"/>
-      <c r="AI71" s="125"/>
-      <c r="AJ71" s="125"/>
-      <c r="AK71" s="125"/>
-      <c r="AL71" s="125"/>
+      <c r="AG71" s="149"/>
+      <c r="AH71" s="149"/>
+      <c r="AI71" s="149"/>
+      <c r="AJ71" s="149"/>
+      <c r="AK71" s="149"/>
+      <c r="AL71" s="149"/>
       <c r="AM71" s="60"/>
     </row>
-    <row r="72" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="21:39" ht="14.1" customHeight="1">
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
       <c r="W72" s="3" t="s">
@@ -15776,18 +15776,18 @@
         <v>1000</v>
       </c>
       <c r="AD72" s="3"/>
-      <c r="AF72" s="125" t="s">
+      <c r="AF72" s="149" t="s">
         <v>233</v>
       </c>
-      <c r="AG72" s="125"/>
-      <c r="AH72" s="125"/>
-      <c r="AI72" s="125"/>
-      <c r="AJ72" s="125"/>
-      <c r="AK72" s="125"/>
-      <c r="AL72" s="125"/>
+      <c r="AG72" s="149"/>
+      <c r="AH72" s="149"/>
+      <c r="AI72" s="149"/>
+      <c r="AJ72" s="149"/>
+      <c r="AK72" s="149"/>
+      <c r="AL72" s="149"/>
       <c r="AM72" s="60"/>
     </row>
-    <row r="73" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="21:39" ht="14.1" customHeight="1">
       <c r="U73" s="3"/>
       <c r="V73" s="3"/>
       <c r="W73" s="3" t="s">
@@ -15812,18 +15812,18 @@
       <c r="AD73" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF73" s="125" t="s">
+      <c r="AF73" s="149" t="s">
         <v>234</v>
       </c>
-      <c r="AG73" s="125"/>
-      <c r="AH73" s="125"/>
-      <c r="AI73" s="125"/>
-      <c r="AJ73" s="125"/>
-      <c r="AK73" s="125"/>
-      <c r="AL73" s="125"/>
+      <c r="AG73" s="149"/>
+      <c r="AH73" s="149"/>
+      <c r="AI73" s="149"/>
+      <c r="AJ73" s="149"/>
+      <c r="AK73" s="149"/>
+      <c r="AL73" s="149"/>
       <c r="AM73" s="60"/>
     </row>
-    <row r="74" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="21:39" ht="14.1" customHeight="1">
       <c r="U74" s="3" t="s">
         <v>37</v>
       </c>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="AD74" s="3"/>
     </row>
-    <row r="75" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="21:39" ht="14.1" customHeight="1">
       <c r="U75" s="3"/>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="s">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="AD75" s="3"/>
     </row>
-    <row r="76" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="21:39" ht="14.1" customHeight="1">
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
       <c r="W76" s="3" t="s">
@@ -15899,7 +15899,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="21:39" ht="14.1" customHeight="1">
       <c r="U77" s="3"/>
       <c r="V77" s="3"/>
       <c r="W77" s="3" t="s">
@@ -15925,7 +15925,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="21:39" ht="14.1" customHeight="1">
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
       <c r="W78" s="3" t="s">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="AD78" s="3"/>
     </row>
-    <row r="79" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="21:39" ht="14.1" customHeight="1">
       <c r="U79" s="3"/>
       <c r="V79" s="3"/>
       <c r="W79" s="3" t="s">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="AD79" s="3"/>
     </row>
-    <row r="80" spans="21:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="21:39" ht="14.1" customHeight="1">
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
       <c r="W80" s="3" t="s">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="AD80" s="3"/>
     </row>
-    <row r="81" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="21:30" ht="14.1" customHeight="1">
       <c r="U81" s="3"/>
       <c r="V81" s="3"/>
       <c r="W81" s="3" t="s">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="AD81" s="3"/>
     </row>
-    <row r="82" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="21:30" ht="14.1" customHeight="1">
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3" t="s">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="AD82" s="3"/>
     </row>
-    <row r="83" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="21:30" ht="14.1" customHeight="1">
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
       <c r="W83" s="3" t="s">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="AD83" s="3"/>
     </row>
-    <row r="84" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="21:30" ht="14.1" customHeight="1">
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
       <c r="W84" s="3" t="s">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="AD84" s="3"/>
     </row>
-    <row r="85" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="21:30" ht="14.1" customHeight="1">
       <c r="U85" s="3"/>
       <c r="V85" s="3"/>
       <c r="W85" s="3" t="s">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="AD85" s="3"/>
     </row>
-    <row r="86" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="21:30" ht="14.1" customHeight="1">
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
       <c r="W86" s="3" t="s">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="AD86" s="3"/>
     </row>
-    <row r="87" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="21:30" ht="14.1" customHeight="1">
       <c r="U87" s="3"/>
       <c r="V87" s="3"/>
       <c r="W87" s="3" t="s">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="AD87" s="3"/>
     </row>
-    <row r="88" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="21:30" ht="14.1" customHeight="1">
       <c r="U88" s="3"/>
       <c r="V88" s="3"/>
       <c r="W88" s="3" t="s">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="AD88" s="3"/>
     </row>
-    <row r="89" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="21:30" ht="14.1" customHeight="1">
       <c r="U89" s="3"/>
       <c r="V89" s="3"/>
       <c r="W89" s="3" t="s">
@@ -16215,7 +16215,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="21:30" ht="14.1" customHeight="1">
       <c r="U90" s="3" t="s">
         <v>39</v>
       </c>
@@ -16243,7 +16243,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="91" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="21:30" ht="14.1" customHeight="1">
       <c r="U91" s="3"/>
       <c r="V91" s="3"/>
       <c r="W91" s="3" t="s">
@@ -16269,7 +16269,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="21:30" ht="14.1" customHeight="1">
       <c r="U92" s="3"/>
       <c r="V92" s="3"/>
       <c r="W92" s="3" t="s">
@@ -16295,7 +16295,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="21:30" ht="14.1" customHeight="1">
       <c r="U93" s="3"/>
       <c r="V93" s="3"/>
       <c r="W93" s="3" t="s">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="AD93" s="3"/>
     </row>
-    <row r="94" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="21:30" ht="14.1" customHeight="1">
       <c r="U94" s="3"/>
       <c r="V94" s="3"/>
       <c r="W94" s="3" t="s">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="AD94" s="3"/>
     </row>
-    <row r="95" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="21:30" ht="14.1" customHeight="1">
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3" t="s">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="AD95" s="3"/>
     </row>
-    <row r="96" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="21:30" ht="14.1" customHeight="1">
       <c r="U96" s="3"/>
       <c r="V96" s="3"/>
       <c r="W96" s="3" t="s">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="AD96" s="3"/>
     </row>
-    <row r="97" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="21:30" ht="14.1" customHeight="1">
       <c r="U97" s="3"/>
       <c r="V97" s="3"/>
       <c r="W97" s="3" t="s">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="AD97" s="3"/>
     </row>
-    <row r="98" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="21:30" ht="14.1" customHeight="1">
       <c r="U98" s="3"/>
       <c r="V98" s="3"/>
       <c r="W98" s="3" t="s">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="AD98" s="3"/>
     </row>
-    <row r="99" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="21:30" ht="14.1" customHeight="1">
       <c r="U99" s="3"/>
       <c r="V99" s="3"/>
       <c r="W99" s="3" t="s">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="AD99" s="3"/>
     </row>
-    <row r="100" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="21:30" ht="14.1" customHeight="1">
       <c r="U100" s="3"/>
       <c r="V100" s="3"/>
       <c r="W100" s="3" t="s">
@@ -16489,7 +16489,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="101" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="21:30" ht="14.1" customHeight="1">
       <c r="U101" s="3"/>
       <c r="V101" s="3"/>
       <c r="W101" s="3" t="s">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="AD101" s="3"/>
     </row>
-    <row r="102" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="21:30" ht="14.1" customHeight="1">
       <c r="U102" s="3"/>
       <c r="V102" s="3"/>
       <c r="W102" s="3" t="s">
@@ -16539,7 +16539,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="21:30" ht="14.1" customHeight="1">
       <c r="U103" s="3"/>
       <c r="V103" s="3"/>
       <c r="W103" s="3" t="s">
@@ -16565,7 +16565,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="104" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="21:30" ht="14.1" customHeight="1">
       <c r="U104" s="3"/>
       <c r="V104" s="3"/>
       <c r="W104" s="3" t="s">
@@ -16591,7 +16591,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="21:30" ht="14.1" customHeight="1">
       <c r="U105" s="3" t="s">
         <v>40</v>
       </c>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="AD105" s="3"/>
     </row>
-    <row r="106" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="21:30" ht="14.1" customHeight="1">
       <c r="U106" s="3"/>
       <c r="V106" s="3"/>
       <c r="W106" s="3" t="s">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="AD106" s="3"/>
     </row>
-    <row r="107" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="21:30" ht="14.1" customHeight="1">
       <c r="U107" s="3"/>
       <c r="V107" s="3"/>
       <c r="W107" s="3" t="s">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="AD107" s="3"/>
     </row>
-    <row r="108" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="21:30" ht="14.1" customHeight="1">
       <c r="U108" s="3"/>
       <c r="V108" s="3"/>
       <c r="W108" s="3" t="s">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="AD108" s="3"/>
     </row>
-    <row r="109" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="21:30" ht="14.1" customHeight="1">
       <c r="U109" s="3"/>
       <c r="V109" s="3"/>
       <c r="W109" s="3" t="s">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AD109" s="3"/>
     </row>
-    <row r="110" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="21:30" ht="14.1" customHeight="1">
       <c r="U110" s="3"/>
       <c r="V110" s="3"/>
       <c r="W110" s="3" t="s">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="AD110" s="3"/>
     </row>
-    <row r="111" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="21:30" ht="14.1" customHeight="1">
       <c r="U111" s="3"/>
       <c r="V111" s="3"/>
       <c r="W111" s="3" t="s">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="AD111" s="3"/>
     </row>
-    <row r="112" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="21:30" ht="14.1" customHeight="1">
       <c r="U112" s="3"/>
       <c r="V112" s="3"/>
       <c r="W112" s="3" t="s">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="AD112" s="3"/>
     </row>
-    <row r="113" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="21:30" ht="14.1" customHeight="1">
       <c r="U113" s="3"/>
       <c r="V113" s="3"/>
       <c r="W113" s="3" t="s">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="AD113" s="3"/>
     </row>
-    <row r="114" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="21:30" ht="14.1" customHeight="1">
       <c r="U114" s="3"/>
       <c r="V114" s="3"/>
       <c r="W114" s="3" t="s">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="AD114" s="3"/>
     </row>
-    <row r="115" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="21:30" ht="14.1" customHeight="1">
       <c r="U115" s="3"/>
       <c r="V115" s="3"/>
       <c r="W115" s="3" t="s">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="AD115" s="3"/>
     </row>
-    <row r="116" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="21:30" ht="14.1" customHeight="1">
       <c r="U116" s="3"/>
       <c r="V116" s="3"/>
       <c r="W116" s="3" t="s">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="AD116" s="3"/>
     </row>
-    <row r="117" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="21:30" ht="14.1" customHeight="1">
       <c r="U117" s="3"/>
       <c r="V117" s="3"/>
       <c r="W117" s="3" t="s">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="AD117" s="3"/>
     </row>
-    <row r="118" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="21:30" ht="14.1" customHeight="1">
       <c r="U118" s="3"/>
       <c r="V118" s="3"/>
       <c r="W118" s="3" t="s">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="AD118" s="3"/>
     </row>
-    <row r="119" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="21:30" ht="14.1" customHeight="1">
       <c r="U119" s="3" t="s">
         <v>43</v>
       </c>
@@ -16955,7 +16955,7 @@
       </c>
       <c r="AD119" s="3"/>
     </row>
-    <row r="120" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="21:30" ht="14.1" customHeight="1">
       <c r="U120" s="3"/>
       <c r="V120" s="3"/>
       <c r="W120" s="3" t="s">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="AD120" s="3"/>
     </row>
-    <row r="121" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="21:30" ht="14.1" customHeight="1">
       <c r="U121" s="3"/>
       <c r="V121" s="3"/>
       <c r="W121" s="3" t="s">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="AD121" s="3"/>
     </row>
-    <row r="122" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="21:30" ht="14.1" customHeight="1">
       <c r="U122" s="3"/>
       <c r="V122" s="3"/>
       <c r="W122" s="3" t="s">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="AD122" s="3"/>
     </row>
-    <row r="123" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="21:30" ht="14.1" customHeight="1">
       <c r="U123" s="3"/>
       <c r="V123" s="3"/>
       <c r="W123" s="3" t="s">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="AD123" s="3"/>
     </row>
-    <row r="124" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="21:30" ht="14.1" customHeight="1">
       <c r="U124" s="3"/>
       <c r="V124" s="3"/>
       <c r="W124" s="3" t="s">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="AD124" s="3"/>
     </row>
-    <row r="125" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="21:30" ht="14.1" customHeight="1">
       <c r="U125" s="3"/>
       <c r="V125" s="3"/>
       <c r="W125" s="3" t="s">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="AD125" s="3"/>
     </row>
-    <row r="126" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="21:30" ht="14.1" customHeight="1">
       <c r="U126" s="3"/>
       <c r="V126" s="3"/>
       <c r="W126" s="3" t="s">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="AD126" s="3"/>
     </row>
-    <row r="127" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="21:30" ht="14.1" customHeight="1">
       <c r="U127" s="3"/>
       <c r="V127" s="3"/>
       <c r="W127" s="3" t="s">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="AD127" s="3"/>
     </row>
-    <row r="128" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="21:30" ht="14.1" customHeight="1">
       <c r="U128" s="3"/>
       <c r="V128" s="3"/>
       <c r="W128" s="3" t="s">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AD128" s="3"/>
     </row>
-    <row r="129" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="21:30" ht="14.1" customHeight="1">
       <c r="U129" s="3"/>
       <c r="V129" s="3"/>
       <c r="W129" s="3" t="s">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="AD129" s="3"/>
     </row>
-    <row r="130" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="21:30" ht="14.1" customHeight="1">
       <c r="U130" s="3"/>
       <c r="V130" s="3"/>
       <c r="W130" s="3" t="s">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="AD130" s="3"/>
     </row>
-    <row r="131" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="21:30" ht="14.1" customHeight="1">
       <c r="U131" s="3"/>
       <c r="V131" s="3"/>
       <c r="W131" s="3" t="s">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="AD131" s="3"/>
     </row>
-    <row r="132" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="21:30" ht="14.1" customHeight="1">
       <c r="U132" s="3" t="s">
         <v>44</v>
       </c>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="AD132" s="3"/>
     </row>
-    <row r="133" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="21:30" ht="14.1" customHeight="1">
       <c r="U133" s="3"/>
       <c r="V133" s="3"/>
       <c r="W133" s="3" t="s">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="AD133" s="3"/>
     </row>
-    <row r="134" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="21:30" ht="14.1" customHeight="1">
       <c r="U134" s="3"/>
       <c r="V134" s="3"/>
       <c r="W134" s="3" t="s">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="AD134" s="3"/>
     </row>
-    <row r="135" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="21:30" ht="14.1" customHeight="1">
       <c r="U135" s="3"/>
       <c r="V135" s="3"/>
       <c r="W135" s="3" t="s">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="AD135" s="3"/>
     </row>
-    <row r="136" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="21:30" ht="14.1" customHeight="1">
       <c r="U136" s="3"/>
       <c r="V136" s="3"/>
       <c r="W136" s="3" t="s">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AD136" s="3"/>
     </row>
-    <row r="137" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="21:30" ht="14.1" customHeight="1">
       <c r="U137" s="3"/>
       <c r="V137" s="3"/>
       <c r="W137" s="3" t="s">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="AD137" s="3"/>
     </row>
-    <row r="138" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="21:30" ht="14.1" customHeight="1">
       <c r="U138" s="3"/>
       <c r="V138" s="3"/>
       <c r="W138" s="3" t="s">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="AD138" s="3"/>
     </row>
-    <row r="139" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="21:30" ht="14.1" customHeight="1">
       <c r="U139" s="3"/>
       <c r="V139" s="3"/>
       <c r="W139" s="3" t="s">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="AD139" s="3"/>
     </row>
-    <row r="140" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="21:30" ht="14.1" customHeight="1">
       <c r="U140" s="3"/>
       <c r="V140" s="3"/>
       <c r="W140" s="3" t="s">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="AD140" s="3"/>
     </row>
-    <row r="141" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="21:30" ht="14.1" customHeight="1">
       <c r="U141" s="3"/>
       <c r="V141" s="3"/>
       <c r="W141" s="3" t="s">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="AD141" s="3"/>
     </row>
-    <row r="142" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="21:30" ht="14.1" customHeight="1">
       <c r="U142" s="3"/>
       <c r="V142" s="3"/>
       <c r="W142" s="3" t="s">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="AD142" s="3"/>
     </row>
-    <row r="143" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="21:30" ht="14.1" customHeight="1">
       <c r="U143" s="3"/>
       <c r="V143" s="3"/>
       <c r="W143" s="3" t="s">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="AD143" s="3"/>
     </row>
-    <row r="144" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="21:30" ht="14.1" customHeight="1">
       <c r="U144" s="3" t="s">
         <v>45</v>
       </c>
@@ -17559,7 +17559,7 @@
       </c>
       <c r="AD144" s="3"/>
     </row>
-    <row r="145" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="21:30" ht="14.1" customHeight="1">
       <c r="U145" s="3"/>
       <c r="V145" s="3"/>
       <c r="W145" s="3" t="s">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="AD145" s="3"/>
     </row>
-    <row r="146" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="21:30" ht="14.1" customHeight="1">
       <c r="U146" s="3"/>
       <c r="V146" s="3"/>
       <c r="W146" s="3" t="s">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="AD146" s="3"/>
     </row>
-    <row r="147" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="21:30" ht="14.1" customHeight="1">
       <c r="U147" s="3"/>
       <c r="V147" s="3"/>
       <c r="W147" s="3" t="s">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AD147" s="3"/>
     </row>
-    <row r="148" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="21:30" ht="14.1" customHeight="1">
       <c r="U148" s="3"/>
       <c r="V148" s="3"/>
       <c r="W148" s="3" t="s">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AD148" s="3"/>
     </row>
-    <row r="149" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="21:30" ht="14.1" customHeight="1">
       <c r="U149" s="3"/>
       <c r="V149" s="3"/>
       <c r="W149" s="3" t="s">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="AD149" s="3"/>
     </row>
-    <row r="150" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="21:30" ht="14.1" customHeight="1">
       <c r="U150" s="3"/>
       <c r="V150" s="3"/>
       <c r="W150" s="3" t="s">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="AD150" s="3"/>
     </row>
-    <row r="151" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="21:30" ht="14.1" customHeight="1">
       <c r="U151" s="3"/>
       <c r="V151" s="3"/>
       <c r="W151" s="3" t="s">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="AD151" s="3"/>
     </row>
-    <row r="152" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="21:30" ht="14.1" customHeight="1">
       <c r="U152" s="3"/>
       <c r="V152" s="3"/>
       <c r="W152" s="3" t="s">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="AD152" s="3"/>
     </row>
-    <row r="153" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="21:30" ht="14.1" customHeight="1">
       <c r="U153" s="3"/>
       <c r="V153" s="3"/>
       <c r="W153" s="3" t="s">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="AD153" s="3"/>
     </row>
-    <row r="154" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="21:30" ht="14.1" customHeight="1">
       <c r="U154" s="3"/>
       <c r="V154" s="3"/>
       <c r="W154" s="3" t="s">
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AD154" s="3"/>
     </row>
-    <row r="155" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="21:30" ht="14.1" customHeight="1">
       <c r="U155" s="3" t="s">
         <v>48</v>
       </c>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="AD155" s="3"/>
     </row>
-    <row r="156" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="21:30" ht="14.1" customHeight="1">
       <c r="U156" s="3"/>
       <c r="V156" s="3"/>
       <c r="W156" s="3" t="s">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="AD156" s="3"/>
     </row>
-    <row r="157" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="21:30" ht="14.1" customHeight="1">
       <c r="U157" s="3"/>
       <c r="V157" s="3"/>
       <c r="W157" s="3" t="s">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="AD157" s="3"/>
     </row>
-    <row r="158" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="21:30" ht="14.1" customHeight="1">
       <c r="U158" s="3"/>
       <c r="V158" s="3"/>
       <c r="W158" s="3" t="s">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="AD158" s="3"/>
     </row>
-    <row r="159" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="21:30" ht="14.1" customHeight="1">
       <c r="U159" s="3"/>
       <c r="V159" s="3"/>
       <c r="W159" s="3" t="s">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="AD159" s="3"/>
     </row>
-    <row r="160" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="21:30" ht="14.1" customHeight="1">
       <c r="U160" s="3"/>
       <c r="V160" s="3"/>
       <c r="W160" s="3" t="s">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="AD160" s="3"/>
     </row>
-    <row r="161" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="21:30" ht="14.1" customHeight="1">
       <c r="U161" s="3"/>
       <c r="V161" s="3"/>
       <c r="W161" s="3" t="s">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="AD161" s="3"/>
     </row>
-    <row r="162" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="21:30" ht="14.1" customHeight="1">
       <c r="U162" s="3"/>
       <c r="V162" s="3"/>
       <c r="W162" s="3" t="s">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="AD162" s="3"/>
     </row>
-    <row r="163" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="21:30" ht="14.1" customHeight="1">
       <c r="U163" s="3"/>
       <c r="V163" s="3"/>
       <c r="W163" s="3" t="s">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AD163" s="3"/>
     </row>
-    <row r="164" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="21:30" ht="14.1" customHeight="1">
       <c r="U164" s="3"/>
       <c r="V164" s="3"/>
       <c r="W164" s="3" t="s">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="AD164" s="3"/>
     </row>
-    <row r="165" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="21:30" ht="14.1" customHeight="1">
       <c r="U165" s="3" t="s">
         <v>49</v>
       </c>
@@ -18067,7 +18067,7 @@
       </c>
       <c r="AD165" s="3"/>
     </row>
-    <row r="166" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="21:30" ht="14.1" customHeight="1">
       <c r="U166" s="3"/>
       <c r="V166" s="3"/>
       <c r="W166" s="3" t="s">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="AD166" s="3"/>
     </row>
-    <row r="167" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="21:30" ht="14.1" customHeight="1">
       <c r="U167" s="3"/>
       <c r="V167" s="3"/>
       <c r="W167" s="3" t="s">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="AD167" s="3"/>
     </row>
-    <row r="168" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="21:30" ht="14.1" customHeight="1">
       <c r="U168" s="3"/>
       <c r="V168" s="3"/>
       <c r="W168" s="3" t="s">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="AD168" s="3"/>
     </row>
-    <row r="169" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="21:30" ht="14.1" customHeight="1">
       <c r="U169" s="3"/>
       <c r="V169" s="3"/>
       <c r="W169" s="3" t="s">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="AD169" s="3"/>
     </row>
-    <row r="170" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="21:30" ht="14.1" customHeight="1">
       <c r="U170" s="3"/>
       <c r="V170" s="3"/>
       <c r="W170" s="3" t="s">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="AD170" s="3"/>
     </row>
-    <row r="171" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="21:30" ht="14.1" customHeight="1">
       <c r="U171" s="3"/>
       <c r="V171" s="3"/>
       <c r="W171" s="3" t="s">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="AD171" s="3"/>
     </row>
-    <row r="172" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="21:30" ht="14.1" customHeight="1">
       <c r="U172" s="3"/>
       <c r="V172" s="3"/>
       <c r="W172" s="3" t="s">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="AD172" s="3"/>
     </row>
-    <row r="173" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="21:30" ht="14.1" customHeight="1">
       <c r="U173" s="3"/>
       <c r="V173" s="3"/>
       <c r="W173" s="3" t="s">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="AD173" s="3"/>
     </row>
-    <row r="174" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="21:30" ht="14.1" customHeight="1">
       <c r="U174" s="3" t="s">
         <v>50</v>
       </c>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="AD174" s="3"/>
     </row>
-    <row r="175" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="21:30" ht="14.1" customHeight="1">
       <c r="U175" s="3"/>
       <c r="V175" s="3"/>
       <c r="W175" s="3" t="s">
@@ -18309,7 +18309,7 @@
       </c>
       <c r="AD175" s="3"/>
     </row>
-    <row r="176" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="21:30" ht="14.1" customHeight="1">
       <c r="U176" s="3"/>
       <c r="V176" s="3"/>
       <c r="W176" s="3" t="s">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="AD176" s="3"/>
     </row>
-    <row r="177" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="21:30" ht="14.1" customHeight="1">
       <c r="U177" s="3"/>
       <c r="V177" s="3"/>
       <c r="W177" s="3" t="s">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="AD177" s="3"/>
     </row>
-    <row r="178" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="21:30" ht="14.1" customHeight="1">
       <c r="U178" s="3"/>
       <c r="V178" s="3"/>
       <c r="W178" s="3" t="s">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="AD178" s="3"/>
     </row>
-    <row r="179" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="21:30" ht="14.1" customHeight="1">
       <c r="U179" s="3"/>
       <c r="V179" s="3"/>
       <c r="W179" s="3" t="s">
@@ -18405,7 +18405,7 @@
       </c>
       <c r="AD179" s="3"/>
     </row>
-    <row r="180" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="21:30" ht="14.1" customHeight="1">
       <c r="U180" s="3"/>
       <c r="V180" s="3"/>
       <c r="W180" s="3" t="s">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="AD180" s="3"/>
     </row>
-    <row r="181" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="21:30" ht="14.1" customHeight="1">
       <c r="U181" s="3"/>
       <c r="V181" s="3"/>
       <c r="W181" s="3" t="s">
@@ -18455,7 +18455,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="182" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="21:30" ht="14.1" customHeight="1">
       <c r="U182" s="3" t="s">
         <v>53</v>
       </c>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="AD182" s="3"/>
     </row>
-    <row r="183" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="21:30" ht="14.1" customHeight="1">
       <c r="U183" s="3"/>
       <c r="V183" s="3"/>
       <c r="W183" s="3" t="s">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="AD183" s="3"/>
     </row>
-    <row r="184" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="21:30" ht="14.1" customHeight="1">
       <c r="U184" s="3"/>
       <c r="V184" s="3"/>
       <c r="W184" s="3" t="s">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="AD184" s="3"/>
     </row>
-    <row r="185" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="21:30" ht="14.1" customHeight="1">
       <c r="U185" s="3"/>
       <c r="V185" s="3"/>
       <c r="W185" s="3" t="s">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="AD185" s="3"/>
     </row>
-    <row r="186" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="21:30" ht="14.1" customHeight="1">
       <c r="U186" s="3"/>
       <c r="V186" s="3"/>
       <c r="W186" s="3" t="s">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="AD186" s="3"/>
     </row>
-    <row r="187" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="21:30" ht="14.1" customHeight="1">
       <c r="U187" s="3"/>
       <c r="V187" s="3"/>
       <c r="W187" s="3" t="s">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="AD187" s="3"/>
     </row>
-    <row r="188" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="21:30" ht="14.1" customHeight="1">
       <c r="U188" s="3"/>
       <c r="V188" s="3"/>
       <c r="W188" s="3" t="s">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="AD188" s="3"/>
     </row>
-    <row r="189" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="21:30" ht="14.1" customHeight="1">
       <c r="U189" s="3" t="s">
         <v>54</v>
       </c>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="AD189" s="3"/>
     </row>
-    <row r="190" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="21:30" ht="14.1" customHeight="1">
       <c r="U190" s="3"/>
       <c r="V190" s="3"/>
       <c r="W190" s="3" t="s">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="AD190" s="3"/>
     </row>
-    <row r="191" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="21:30" ht="14.1" customHeight="1">
       <c r="U191" s="3"/>
       <c r="V191" s="3"/>
       <c r="W191" s="3" t="s">
@@ -18699,7 +18699,7 @@
       </c>
       <c r="AD191" s="3"/>
     </row>
-    <row r="192" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="21:30" ht="14.1" customHeight="1">
       <c r="U192" s="3"/>
       <c r="V192" s="3"/>
       <c r="W192" s="3" t="s">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="AD192" s="3"/>
     </row>
-    <row r="193" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="21:30" ht="14.1" customHeight="1">
       <c r="U193" s="3"/>
       <c r="V193" s="3"/>
       <c r="W193" s="3" t="s">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="AD193" s="3"/>
     </row>
-    <row r="194" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="21:30" ht="14.1" customHeight="1">
       <c r="U194" s="3"/>
       <c r="V194" s="3"/>
       <c r="W194" s="3" t="s">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="AD194" s="3"/>
     </row>
-    <row r="195" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="21:30" ht="14.1" customHeight="1">
       <c r="U195" s="3" t="s">
         <v>55</v>
       </c>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="AD195" s="3"/>
     </row>
-    <row r="196" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="21:30" ht="14.1" customHeight="1">
       <c r="U196" s="3"/>
       <c r="V196" s="3"/>
       <c r="W196" s="3" t="s">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="AD196" s="3"/>
     </row>
-    <row r="197" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="21:30" ht="14.1" customHeight="1">
       <c r="U197" s="3"/>
       <c r="V197" s="3"/>
       <c r="W197" s="3" t="s">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="AD197" s="3"/>
     </row>
-    <row r="198" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="21:30" ht="14.1" customHeight="1">
       <c r="U198" s="3"/>
       <c r="V198" s="3"/>
       <c r="W198" s="3" t="s">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="AD198" s="3"/>
     </row>
-    <row r="199" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="21:30" ht="14.1" customHeight="1">
       <c r="U199" s="3"/>
       <c r="V199" s="3"/>
       <c r="W199" s="3" t="s">
@@ -18895,7 +18895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="200" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="21:30" ht="14.1" customHeight="1">
       <c r="U200" s="3" t="s">
         <v>56</v>
       </c>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="AD200" s="3"/>
     </row>
-    <row r="201" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="21:30" ht="14.1" customHeight="1">
       <c r="U201" s="3"/>
       <c r="V201" s="3"/>
       <c r="W201" s="3" t="s">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="AD201" s="3"/>
     </row>
-    <row r="202" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="21:30" ht="14.1" customHeight="1">
       <c r="U202" s="3"/>
       <c r="V202" s="3"/>
       <c r="W202" s="3" t="s">
@@ -18969,7 +18969,7 @@
       </c>
       <c r="AD202" s="3"/>
     </row>
-    <row r="203" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="21:30" ht="14.1" customHeight="1">
       <c r="U203" s="3"/>
       <c r="V203" s="3"/>
       <c r="W203" s="3" t="s">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AD203" s="3"/>
     </row>
-    <row r="204" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="21:30" ht="14.1" customHeight="1">
       <c r="U204" s="3" t="s">
         <v>57</v>
       </c>
@@ -19019,7 +19019,7 @@
       </c>
       <c r="AD204" s="3"/>
     </row>
-    <row r="205" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="21:30" ht="14.1" customHeight="1">
       <c r="U205" s="3"/>
       <c r="V205" s="3"/>
       <c r="W205" s="3" t="s">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="AD205" s="3"/>
     </row>
-    <row r="206" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="21:30" ht="14.1" customHeight="1">
       <c r="U206" s="3"/>
       <c r="V206" s="3"/>
       <c r="W206" s="3" t="s">
@@ -19067,7 +19067,7 @@
       </c>
       <c r="AD206" s="3"/>
     </row>
-    <row r="207" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="21:30" ht="14.1" customHeight="1">
       <c r="U207" s="3" t="s">
         <v>58</v>
       </c>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="AD207" s="3"/>
     </row>
-    <row r="208" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="21:30" ht="14.1" customHeight="1">
       <c r="U208" s="3"/>
       <c r="V208" s="3"/>
       <c r="W208" s="3" t="s">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="AD208" s="3"/>
     </row>
-    <row r="209" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="21:30" ht="14.1" customHeight="1">
       <c r="U209" s="3" t="s">
         <v>59</v>
       </c>
@@ -19143,48 +19143,77 @@
       </c>
       <c r="AD209" s="3"/>
     </row>
-    <row r="210" spans="21:30" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="U210" s="143"/>
-      <c r="V210" s="143"/>
-      <c r="W210" s="143"/>
-      <c r="X210" s="143"/>
-      <c r="Y210" s="143"/>
-      <c r="Z210" s="143"/>
-      <c r="AA210" s="143"/>
-      <c r="AB210" s="143"/>
-      <c r="AC210" s="143"/>
-      <c r="AD210" s="143"/>
-    </row>
-    <row r="211" spans="21:30" ht="14.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="U211" s="144" t="s">
+    <row r="210" spans="21:30" ht="14.1" customHeight="1" thickBot="1">
+      <c r="U210" s="125"/>
+      <c r="V210" s="125"/>
+      <c r="W210" s="125"/>
+      <c r="X210" s="125"/>
+      <c r="Y210" s="125"/>
+      <c r="Z210" s="125"/>
+      <c r="AA210" s="125"/>
+      <c r="AB210" s="125"/>
+      <c r="AC210" s="125"/>
+      <c r="AD210" s="125"/>
+    </row>
+    <row r="211" spans="21:30" ht="14.1" customHeight="1" thickTop="1">
+      <c r="U211" s="126" t="s">
         <v>209</v>
       </c>
-      <c r="V211" s="144"/>
-      <c r="W211" s="144"/>
-      <c r="X211" s="144"/>
-      <c r="Y211" s="144"/>
-      <c r="Z211" s="144"/>
-      <c r="AA211" s="144"/>
-      <c r="AB211" s="144"/>
-      <c r="AC211" s="144"/>
-      <c r="AD211" s="144"/>
-    </row>
-    <row r="212" spans="21:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="U212" s="145" t="s">
+      <c r="V211" s="126"/>
+      <c r="W211" s="126"/>
+      <c r="X211" s="126"/>
+      <c r="Y211" s="126"/>
+      <c r="Z211" s="126"/>
+      <c r="AA211" s="126"/>
+      <c r="AB211" s="126"/>
+      <c r="AC211" s="126"/>
+      <c r="AD211" s="126"/>
+    </row>
+    <row r="212" spans="21:30" ht="14.1" customHeight="1">
+      <c r="U212" s="127" t="s">
         <v>210</v>
       </c>
-      <c r="V212" s="145"/>
-      <c r="W212" s="145"/>
-      <c r="X212" s="145"/>
-      <c r="Y212" s="145"/>
-      <c r="Z212" s="145"/>
-      <c r="AA212" s="145"/>
-      <c r="AB212" s="145"/>
-      <c r="AC212" s="145"/>
-      <c r="AD212" s="145"/>
+      <c r="V212" s="127"/>
+      <c r="W212" s="127"/>
+      <c r="X212" s="127"/>
+      <c r="Y212" s="127"/>
+      <c r="Z212" s="127"/>
+      <c r="AA212" s="127"/>
+      <c r="AB212" s="127"/>
+      <c r="AC212" s="127"/>
+      <c r="AD212" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="AF69:AL69"/>
+    <mergeCell ref="AF70:AL70"/>
+    <mergeCell ref="AF71:AL71"/>
+    <mergeCell ref="AF72:AL72"/>
+    <mergeCell ref="AF73:AL73"/>
+    <mergeCell ref="AF49:AF68"/>
+    <mergeCell ref="AG49:AG52"/>
+    <mergeCell ref="AG53:AG56"/>
+    <mergeCell ref="AG57:AG60"/>
+    <mergeCell ref="AG61:AG64"/>
+    <mergeCell ref="AG65:AG68"/>
+    <mergeCell ref="AF29:AF48"/>
+    <mergeCell ref="AG29:AG32"/>
+    <mergeCell ref="AG33:AG36"/>
+    <mergeCell ref="AG37:AG40"/>
+    <mergeCell ref="AG41:AG44"/>
+    <mergeCell ref="AG45:AG48"/>
+    <mergeCell ref="AF8:AF28"/>
+    <mergeCell ref="AG8:AG12"/>
+    <mergeCell ref="AG13:AG16"/>
+    <mergeCell ref="AG17:AG20"/>
+    <mergeCell ref="AG21:AG24"/>
+    <mergeCell ref="AG25:AG28"/>
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AF5:AL5"/>
+    <mergeCell ref="AF6:AH7"/>
+    <mergeCell ref="AI6:AI7"/>
+    <mergeCell ref="AJ6:AJ7"/>
+    <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="U210:AD210"/>
     <mergeCell ref="U211:AD211"/>
@@ -19196,35 +19225,6 @@
     <mergeCell ref="V4:Z4"/>
     <mergeCell ref="V3:AE3"/>
     <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="AF4:AL4"/>
-    <mergeCell ref="AF5:AL5"/>
-    <mergeCell ref="AF6:AH7"/>
-    <mergeCell ref="AI6:AI7"/>
-    <mergeCell ref="AJ6:AJ7"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AF8:AF28"/>
-    <mergeCell ref="AG8:AG12"/>
-    <mergeCell ref="AG13:AG16"/>
-    <mergeCell ref="AG17:AG20"/>
-    <mergeCell ref="AG21:AG24"/>
-    <mergeCell ref="AG25:AG28"/>
-    <mergeCell ref="AF29:AF48"/>
-    <mergeCell ref="AG29:AG32"/>
-    <mergeCell ref="AG33:AG36"/>
-    <mergeCell ref="AG37:AG40"/>
-    <mergeCell ref="AG41:AG44"/>
-    <mergeCell ref="AG45:AG48"/>
-    <mergeCell ref="AF49:AF68"/>
-    <mergeCell ref="AG49:AG52"/>
-    <mergeCell ref="AG53:AG56"/>
-    <mergeCell ref="AG57:AG60"/>
-    <mergeCell ref="AG61:AG64"/>
-    <mergeCell ref="AG65:AG68"/>
-    <mergeCell ref="AF69:AL69"/>
-    <mergeCell ref="AF70:AL70"/>
-    <mergeCell ref="AF71:AL71"/>
-    <mergeCell ref="AF72:AL72"/>
-    <mergeCell ref="AF73:AL73"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -19234,28 +19234,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C45BFD-4947-4D82-8D2A-A68E35221B7F}">
   <dimension ref="B1:AL212"/>
-  <sheetFormatPr defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.1" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="0.734375" customWidth="1"/>
+    <col min="1" max="1" width="0.69921875" customWidth="1"/>
     <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.03125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.94921875" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.8984375" customWidth="1"/>
     <col min="21" max="30" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:38" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:38" ht="4.5" customHeight="1">
       <c r="U1" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="116" t="s">
+    <row r="2" spans="2:38" ht="14.1" customHeight="1">
+      <c r="B2" s="105" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-    </row>
-    <row r="3" spans="2:38" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+    </row>
+    <row r="3" spans="2:38" ht="14.1" customHeight="1" thickBot="1">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -19265,20 +19265,20 @@
       <c r="D3" t="s">
         <v>270</v>
       </c>
-      <c r="U3" s="149" t="s">
+      <c r="U3" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="149"/>
-      <c r="W3" s="149"/>
-      <c r="X3" s="149"/>
-      <c r="Y3" s="149"/>
-      <c r="Z3" s="149"/>
-      <c r="AA3" s="149"/>
-      <c r="AB3" s="149"/>
-      <c r="AC3" s="149"/>
-      <c r="AD3" s="149"/>
-    </row>
-    <row r="4" spans="2:38" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="V3" s="131"/>
+      <c r="W3" s="131"/>
+      <c r="X3" s="131"/>
+      <c r="Y3" s="131"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="131"/>
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+    </row>
+    <row r="4" spans="2:38" ht="14.1" customHeight="1" thickBot="1">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -19289,30 +19289,30 @@
         <f>AVERAGE('Dados gerais'!K3:K7)</f>
         <v>3.1442405333333334</v>
       </c>
-      <c r="U4" s="147"/>
-      <c r="V4" s="147"/>
-      <c r="W4" s="147"/>
-      <c r="X4" s="147"/>
-      <c r="Y4" s="147"/>
-      <c r="Z4" s="148" t="s">
+      <c r="U4" s="129"/>
+      <c r="V4" s="129"/>
+      <c r="W4" s="129"/>
+      <c r="X4" s="129"/>
+      <c r="Y4" s="129"/>
+      <c r="Z4" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="AA4" s="148"/>
+      <c r="AA4" s="130"/>
       <c r="AB4" s="19"/>
-      <c r="AC4" s="147"/>
-      <c r="AD4" s="147"/>
-      <c r="AE4" s="133" t="s">
+      <c r="AC4" s="129"/>
+      <c r="AD4" s="129"/>
+      <c r="AE4" s="132" t="s">
         <v>222</v>
       </c>
-      <c r="AF4" s="133"/>
-      <c r="AG4" s="133"/>
-      <c r="AH4" s="133"/>
-      <c r="AI4" s="133"/>
-      <c r="AJ4" s="133"/>
-      <c r="AK4" s="133"/>
+      <c r="AF4" s="132"/>
+      <c r="AG4" s="132"/>
+      <c r="AH4" s="132"/>
+      <c r="AI4" s="132"/>
+      <c r="AJ4" s="132"/>
+      <c r="AK4" s="132"/>
       <c r="AL4" s="60"/>
     </row>
-    <row r="5" spans="2:38" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:38" ht="14.1" customHeight="1" thickBot="1">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -19323,13 +19323,13 @@
         <f>AVERAGE('Dados gerais'!K8:K14)</f>
         <v>1.5632971428571429</v>
       </c>
-      <c r="U5" s="146"/>
-      <c r="V5" s="146"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="128"/>
       <c r="W5" s="18"/>
-      <c r="X5" s="146" t="s">
+      <c r="X5" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="Y5" s="146"/>
+      <c r="Y5" s="128"/>
       <c r="Z5" s="20" t="s">
         <v>27</v>
       </c>
@@ -19339,24 +19339,24 @@
       <c r="AB5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="AC5" s="146" t="s">
+      <c r="AC5" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="AD5" s="146"/>
-      <c r="AE5" s="134" t="s">
+      <c r="AD5" s="128"/>
+      <c r="AE5" s="133" t="s">
         <v>223</v>
       </c>
-      <c r="AF5" s="134" t="s">
+      <c r="AF5" s="133" t="s">
         <v>256</v>
       </c>
-      <c r="AG5" s="135"/>
-      <c r="AH5" s="135"/>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="135"/>
+      <c r="AG5" s="134"/>
+      <c r="AH5" s="134"/>
+      <c r="AI5" s="134"/>
+      <c r="AJ5" s="134"/>
+      <c r="AK5" s="134"/>
       <c r="AL5" s="60"/>
     </row>
-    <row r="6" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:38" ht="14.1" customHeight="1">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -19391,24 +19391,24 @@
         <v>1000</v>
       </c>
       <c r="AD6" s="3"/>
-      <c r="AE6" s="136" t="s">
+      <c r="AE6" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="AF6" s="136"/>
-      <c r="AG6" s="136"/>
-      <c r="AH6" s="138" t="s">
+      <c r="AF6" s="135"/>
+      <c r="AG6" s="135"/>
+      <c r="AH6" s="137" t="s">
         <v>224</v>
       </c>
-      <c r="AI6" s="140" t="s">
+      <c r="AI6" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="AJ6" s="140" t="s">
+      <c r="AJ6" s="139" t="s">
         <v>236</v>
       </c>
-      <c r="AK6" s="142"/>
+      <c r="AK6" s="141"/>
       <c r="AL6" s="60"/>
     </row>
-    <row r="7" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:38" ht="14.1" customHeight="1">
       <c r="B7" t="s">
         <v>19</v>
       </c>
@@ -19441,11 +19441,11 @@
         <v>1000</v>
       </c>
       <c r="AD7" s="3"/>
-      <c r="AE7" s="137"/>
-      <c r="AF7" s="137"/>
-      <c r="AG7" s="137"/>
-      <c r="AH7" s="139"/>
-      <c r="AI7" s="141"/>
+      <c r="AE7" s="136"/>
+      <c r="AF7" s="136"/>
+      <c r="AG7" s="136"/>
+      <c r="AH7" s="138"/>
+      <c r="AI7" s="140"/>
       <c r="AJ7" s="62" t="s">
         <v>225</v>
       </c>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="AL7" s="60"/>
     </row>
-    <row r="8" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:38" ht="14.1" customHeight="1">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -19489,10 +19489,10 @@
       <c r="AD8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE8" s="131" t="s">
+      <c r="AE8" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="AF8" s="132" t="s">
+      <c r="AF8" s="145" t="s">
         <v>5</v>
       </c>
       <c r="AG8" s="90" t="s">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="AL8" s="60"/>
     </row>
-    <row r="9" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:38" ht="14.1" customHeight="1">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -19547,8 +19547,8 @@
       <c r="AD9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE9" s="127"/>
-      <c r="AF9" s="130"/>
+      <c r="AE9" s="143"/>
+      <c r="AF9" s="146"/>
       <c r="AG9" s="81" t="s">
         <v>7</v>
       </c>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="AL9" s="60"/>
     </row>
-    <row r="10" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:38" ht="14.1" customHeight="1">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -19587,8 +19587,8 @@
       <c r="AB10" s="4"/>
       <c r="AC10" s="5"/>
       <c r="AD10" s="3"/>
-      <c r="AE10" s="127"/>
-      <c r="AF10" s="130"/>
+      <c r="AE10" s="143"/>
+      <c r="AF10" s="146"/>
       <c r="AG10" s="81"/>
       <c r="AH10" s="82"/>
       <c r="AI10" s="83"/>
@@ -19596,7 +19596,7 @@
       <c r="AK10" s="84"/>
       <c r="AL10" s="60"/>
     </row>
-    <row r="11" spans="2:38" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:38" ht="13.95" customHeight="1">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -19631,8 +19631,8 @@
       <c r="AD11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE11" s="127"/>
-      <c r="AF11" s="130"/>
+      <c r="AE11" s="143"/>
+      <c r="AF11" s="146"/>
       <c r="AG11" s="81"/>
       <c r="AH11" s="85"/>
       <c r="AI11" s="94"/>
@@ -19640,7 +19640,7 @@
       <c r="AK11" s="95"/>
       <c r="AL11" s="60"/>
     </row>
-    <row r="12" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:38" ht="14.1" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
@@ -19675,8 +19675,8 @@
       <c r="AD12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AE12" s="127"/>
-      <c r="AF12" s="129"/>
+      <c r="AE12" s="143"/>
+      <c r="AF12" s="147"/>
       <c r="AG12" s="86"/>
       <c r="AH12" s="87"/>
       <c r="AI12" s="96"/>
@@ -19684,7 +19684,7 @@
       <c r="AK12" s="97"/>
       <c r="AL12" s="60"/>
     </row>
-    <row r="13" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:38" ht="14.1" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
@@ -19717,8 +19717,8 @@
         <v>52</v>
       </c>
       <c r="AD13" s="3"/>
-      <c r="AE13" s="127"/>
-      <c r="AF13" s="126" t="s">
+      <c r="AE13" s="143"/>
+      <c r="AF13" s="144" t="s">
         <v>6</v>
       </c>
       <c r="AG13" s="64" t="s">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="AL13" s="60"/>
     </row>
-    <row r="14" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:38" ht="14.1" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
@@ -19773,8 +19773,8 @@
       <c r="AD14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE14" s="127"/>
-      <c r="AF14" s="127"/>
+      <c r="AE14" s="143"/>
+      <c r="AF14" s="143"/>
       <c r="AG14" s="64" t="s">
         <v>7</v>
       </c>
@@ -19792,7 +19792,7 @@
       </c>
       <c r="AL14" s="60"/>
     </row>
-    <row r="15" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:38" ht="14.1" customHeight="1">
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
@@ -19827,8 +19827,8 @@
       <c r="AD15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE15" s="127"/>
-      <c r="AF15" s="127"/>
+      <c r="AE15" s="143"/>
+      <c r="AF15" s="143"/>
       <c r="AG15" s="64" t="s">
         <v>8</v>
       </c>
@@ -19840,7 +19840,7 @@
       <c r="AK15" s="70"/>
       <c r="AL15" s="60"/>
     </row>
-    <row r="16" spans="2:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:38" ht="14.1" customHeight="1">
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
@@ -19865,8 +19865,8 @@
       <c r="AD16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE16" s="127"/>
-      <c r="AF16" s="126"/>
+      <c r="AE16" s="143"/>
+      <c r="AF16" s="144"/>
       <c r="AG16" s="71" t="s">
         <v>227</v>
       </c>
@@ -19878,7 +19878,7 @@
       <c r="AK16" s="74"/>
       <c r="AL16" s="60"/>
     </row>
-    <row r="17" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="5:38" ht="14.1" customHeight="1">
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
@@ -19903,8 +19903,8 @@
       <c r="AD17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE17" s="127"/>
-      <c r="AF17" s="126" t="s">
+      <c r="AE17" s="143"/>
+      <c r="AF17" s="144" t="s">
         <v>7</v>
       </c>
       <c r="AG17" s="64" t="s">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="AL17" s="60"/>
     </row>
-    <row r="18" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="5:38" ht="14.1" customHeight="1">
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="s">
@@ -19949,8 +19949,8 @@
       <c r="AD18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE18" s="127"/>
-      <c r="AF18" s="127"/>
+      <c r="AE18" s="143"/>
+      <c r="AF18" s="143"/>
       <c r="AG18" s="64" t="s">
         <v>6</v>
       </c>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="AL18" s="60"/>
     </row>
-    <row r="19" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="5:38" ht="14.1" customHeight="1">
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="s">
@@ -19993,8 +19993,8 @@
       <c r="AD19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE19" s="127"/>
-      <c r="AF19" s="127"/>
+      <c r="AE19" s="143"/>
+      <c r="AF19" s="143"/>
       <c r="AG19" s="64"/>
       <c r="AH19" s="68"/>
       <c r="AI19" s="69"/>
@@ -20002,7 +20002,7 @@
       <c r="AK19" s="70"/>
       <c r="AL19" s="60"/>
     </row>
-    <row r="20" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="5:38" ht="14.1" customHeight="1">
       <c r="U20" s="3" t="s">
         <v>32</v>
       </c>
@@ -20027,8 +20027,8 @@
         <v>1000</v>
       </c>
       <c r="AD20" s="3"/>
-      <c r="AE20" s="127"/>
-      <c r="AF20" s="126"/>
+      <c r="AE20" s="143"/>
+      <c r="AF20" s="144"/>
       <c r="AG20" s="71"/>
       <c r="AH20" s="72"/>
       <c r="AI20" s="73"/>
@@ -20036,7 +20036,7 @@
       <c r="AK20" s="74"/>
       <c r="AL20" s="60"/>
     </row>
-    <row r="21" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="5:38" ht="14.1" customHeight="1">
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="s">
@@ -20059,8 +20059,8 @@
         <v>63</v>
       </c>
       <c r="AD21" s="3"/>
-      <c r="AE21" s="127"/>
-      <c r="AF21" s="126" t="s">
+      <c r="AE21" s="143"/>
+      <c r="AF21" s="144" t="s">
         <v>8</v>
       </c>
       <c r="AG21" s="64"/>
@@ -20070,7 +20070,7 @@
       <c r="AK21" s="70"/>
       <c r="AL21" s="60"/>
     </row>
-    <row r="22" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="5:38" ht="14.1" customHeight="1">
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
@@ -20093,8 +20093,8 @@
         <v>64</v>
       </c>
       <c r="AD22" s="3"/>
-      <c r="AE22" s="127"/>
-      <c r="AF22" s="127"/>
+      <c r="AE22" s="143"/>
+      <c r="AF22" s="143"/>
       <c r="AG22" s="64"/>
       <c r="AH22" s="68"/>
       <c r="AI22" s="69"/>
@@ -20102,7 +20102,7 @@
       <c r="AK22" s="70"/>
       <c r="AL22" s="60"/>
     </row>
-    <row r="23" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="5:38" ht="14.1" customHeight="1">
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
@@ -20125,8 +20125,8 @@
         <v>1000</v>
       </c>
       <c r="AD23" s="3"/>
-      <c r="AE23" s="127"/>
-      <c r="AF23" s="127"/>
+      <c r="AE23" s="143"/>
+      <c r="AF23" s="143"/>
       <c r="AG23" s="64"/>
       <c r="AH23" s="68"/>
       <c r="AI23" s="69"/>
@@ -20134,7 +20134,7 @@
       <c r="AK23" s="70"/>
       <c r="AL23" s="60"/>
     </row>
-    <row r="24" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="5:38" ht="14.1" customHeight="1">
       <c r="E24" s="21"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -20160,8 +20160,8 @@
       <c r="AD24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE24" s="127"/>
-      <c r="AF24" s="126"/>
+      <c r="AE24" s="143"/>
+      <c r="AF24" s="144"/>
       <c r="AG24" s="71"/>
       <c r="AH24" s="72"/>
       <c r="AI24" s="73"/>
@@ -20169,7 +20169,7 @@
       <c r="AK24" s="74"/>
       <c r="AL24" s="60"/>
     </row>
-    <row r="25" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="5:38" ht="14.1" customHeight="1">
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
@@ -20194,8 +20194,8 @@
       <c r="AD25" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE25" s="127"/>
-      <c r="AF25" s="126" t="s">
+      <c r="AE25" s="143"/>
+      <c r="AF25" s="144" t="s">
         <v>227</v>
       </c>
       <c r="AG25" s="64"/>
@@ -20205,7 +20205,7 @@
       <c r="AK25" s="70"/>
       <c r="AL25" s="60"/>
     </row>
-    <row r="26" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="5:38" ht="14.1" customHeight="1">
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="s">
@@ -20230,8 +20230,8 @@
       <c r="AD26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE26" s="127"/>
-      <c r="AF26" s="127"/>
+      <c r="AE26" s="143"/>
+      <c r="AF26" s="143"/>
       <c r="AG26" s="64"/>
       <c r="AH26" s="68"/>
       <c r="AI26" s="69"/>
@@ -20239,7 +20239,7 @@
       <c r="AK26" s="70"/>
       <c r="AL26" s="60"/>
     </row>
-    <row r="27" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="5:38" ht="14.1" customHeight="1">
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="s">
@@ -20264,8 +20264,8 @@
       <c r="AD27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AE27" s="127"/>
-      <c r="AF27" s="127"/>
+      <c r="AE27" s="143"/>
+      <c r="AF27" s="143"/>
       <c r="AG27" s="64"/>
       <c r="AH27" s="68"/>
       <c r="AI27" s="69"/>
@@ -20273,7 +20273,7 @@
       <c r="AK27" s="70"/>
       <c r="AL27" s="60"/>
     </row>
-    <row r="28" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="5:38" ht="14.1" customHeight="1">
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="s">
@@ -20298,8 +20298,8 @@
       <c r="AD28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE28" s="126"/>
-      <c r="AF28" s="126"/>
+      <c r="AE28" s="144"/>
+      <c r="AF28" s="144"/>
       <c r="AG28" s="71"/>
       <c r="AH28" s="72"/>
       <c r="AI28" s="73"/>
@@ -20307,7 +20307,7 @@
       <c r="AK28" s="74"/>
       <c r="AL28" s="60"/>
     </row>
-    <row r="29" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="5:38" ht="14.1" customHeight="1">
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="s">
@@ -20332,10 +20332,10 @@
       <c r="AD29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AE29" s="126" t="s">
+      <c r="AE29" s="144" t="s">
         <v>228</v>
       </c>
-      <c r="AF29" s="129" t="s">
+      <c r="AF29" s="147" t="s">
         <v>5</v>
       </c>
       <c r="AG29" s="81" t="s">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="AL29" s="60"/>
     </row>
-    <row r="30" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="5:38" ht="14.1" customHeight="1">
       <c r="O30" s="21"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -20379,8 +20379,8 @@
         <v>67</v>
       </c>
       <c r="AC30" s="3"/>
-      <c r="AE30" s="127"/>
-      <c r="AF30" s="130"/>
+      <c r="AE30" s="143"/>
+      <c r="AF30" s="146"/>
       <c r="AG30" s="81" t="s">
         <v>7</v>
       </c>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="AL30" s="60"/>
     </row>
-    <row r="31" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="5:38" ht="14.1" customHeight="1">
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3" t="s">
@@ -20423,8 +20423,8 @@
       <c r="AC31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE31" s="127"/>
-      <c r="AF31" s="130"/>
+      <c r="AE31" s="143"/>
+      <c r="AF31" s="146"/>
       <c r="AG31" s="81" t="s">
         <v>8</v>
       </c>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="AL31" s="60"/>
     </row>
-    <row r="32" spans="5:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="5:38" ht="14.1" customHeight="1">
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3" t="s">
@@ -20467,8 +20467,8 @@
       <c r="AC32" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE32" s="127"/>
-      <c r="AF32" s="129"/>
+      <c r="AE32" s="143"/>
+      <c r="AF32" s="147"/>
       <c r="AG32" s="86" t="s">
         <v>227</v>
       </c>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="AL32" s="60"/>
     </row>
-    <row r="33" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="20:38" ht="14.1" customHeight="1">
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
@@ -20509,8 +20509,8 @@
         <v>67</v>
       </c>
       <c r="AC33" s="3"/>
-      <c r="AE33" s="127"/>
-      <c r="AF33" s="126" t="s">
+      <c r="AE33" s="143"/>
+      <c r="AF33" s="144" t="s">
         <v>6</v>
       </c>
       <c r="AG33" s="64" t="s">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="AL33" s="60"/>
     </row>
-    <row r="34" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="20:38" ht="14.1" customHeight="1">
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
@@ -20555,8 +20555,8 @@
       <c r="AC34" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE34" s="127"/>
-      <c r="AF34" s="127"/>
+      <c r="AE34" s="143"/>
+      <c r="AF34" s="143"/>
       <c r="AG34" s="64" t="s">
         <v>7</v>
       </c>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="AL34" s="60"/>
     </row>
-    <row r="35" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="20:38" ht="14.1" customHeight="1">
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
@@ -20599,8 +20599,8 @@
       <c r="AC35" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE35" s="127"/>
-      <c r="AF35" s="127"/>
+      <c r="AE35" s="143"/>
+      <c r="AF35" s="143"/>
       <c r="AG35" s="64" t="s">
         <v>8</v>
       </c>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AL35" s="60"/>
     </row>
-    <row r="36" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="20:38" ht="14.1" customHeight="1">
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3" t="s">
@@ -20643,8 +20643,8 @@
       <c r="AC36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE36" s="127"/>
-      <c r="AF36" s="126"/>
+      <c r="AE36" s="143"/>
+      <c r="AF36" s="144"/>
       <c r="AG36" s="71" t="s">
         <v>227</v>
       </c>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="AL36" s="60"/>
     </row>
-    <row r="37" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="20:38" ht="14.1" customHeight="1">
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3" t="s">
@@ -20687,8 +20687,8 @@
       <c r="AC37" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE37" s="127"/>
-      <c r="AF37" s="126" t="s">
+      <c r="AE37" s="143"/>
+      <c r="AF37" s="144" t="s">
         <v>7</v>
       </c>
       <c r="AG37" s="64" t="s">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AL37" s="60"/>
     </row>
-    <row r="38" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="20:38" ht="14.1" customHeight="1">
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
@@ -20733,8 +20733,8 @@
       <c r="AC38" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE38" s="127"/>
-      <c r="AF38" s="127"/>
+      <c r="AE38" s="143"/>
+      <c r="AF38" s="143"/>
       <c r="AG38" s="64" t="s">
         <v>6</v>
       </c>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="AL38" s="60"/>
     </row>
-    <row r="39" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="20:38" ht="14.1" customHeight="1">
       <c r="T39" s="3" t="s">
         <v>33</v>
       </c>
@@ -20777,8 +20777,8 @@
         <v>63</v>
       </c>
       <c r="AC39" s="3"/>
-      <c r="AE39" s="127"/>
-      <c r="AF39" s="127"/>
+      <c r="AE39" s="143"/>
+      <c r="AF39" s="143"/>
       <c r="AG39" s="64" t="s">
         <v>8</v>
       </c>
@@ -20796,7 +20796,7 @@
       </c>
       <c r="AL39" s="60"/>
     </row>
-    <row r="40" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="20:38" ht="14.1" customHeight="1">
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3" t="s">
@@ -20819,8 +20819,8 @@
         <v>38</v>
       </c>
       <c r="AC40" s="3"/>
-      <c r="AE40" s="127"/>
-      <c r="AF40" s="126"/>
+      <c r="AE40" s="143"/>
+      <c r="AF40" s="144"/>
       <c r="AG40" s="71" t="s">
         <v>227</v>
       </c>
@@ -20838,7 +20838,7 @@
       </c>
       <c r="AL40" s="60"/>
     </row>
-    <row r="41" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="20:38" ht="14.1" customHeight="1">
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3" t="s">
@@ -20861,8 +20861,8 @@
         <v>1000</v>
       </c>
       <c r="AC41" s="3"/>
-      <c r="AE41" s="127"/>
-      <c r="AF41" s="126" t="s">
+      <c r="AE41" s="143"/>
+      <c r="AF41" s="144" t="s">
         <v>8</v>
       </c>
       <c r="AG41" s="64" t="s">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="AL41" s="60"/>
     </row>
-    <row r="42" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="20:38" ht="14.1" customHeight="1">
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
@@ -20907,8 +20907,8 @@
       <c r="AC42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE42" s="127"/>
-      <c r="AF42" s="127"/>
+      <c r="AE42" s="143"/>
+      <c r="AF42" s="143"/>
       <c r="AG42" s="64" t="s">
         <v>6</v>
       </c>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="AL42" s="60"/>
     </row>
-    <row r="43" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="20:38" ht="14.1" customHeight="1">
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
@@ -20951,8 +20951,8 @@
       <c r="AC43" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE43" s="127"/>
-      <c r="AF43" s="127"/>
+      <c r="AE43" s="143"/>
+      <c r="AF43" s="143"/>
       <c r="AG43" s="64" t="s">
         <v>7</v>
       </c>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="AL43" s="60"/>
     </row>
-    <row r="44" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="20:38" ht="14.1" customHeight="1">
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
@@ -20995,8 +20995,8 @@
       <c r="AC44" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE44" s="127"/>
-      <c r="AF44" s="126"/>
+      <c r="AE44" s="143"/>
+      <c r="AF44" s="144"/>
       <c r="AG44" s="71" t="s">
         <v>227</v>
       </c>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="AL44" s="60"/>
     </row>
-    <row r="45" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="20:38" ht="14.1" customHeight="1">
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
       <c r="V45" s="3" t="s">
@@ -21039,8 +21039,8 @@
       <c r="AC45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AE45" s="127"/>
-      <c r="AF45" s="126" t="s">
+      <c r="AE45" s="143"/>
+      <c r="AF45" s="144" t="s">
         <v>227</v>
       </c>
       <c r="AG45" s="64" t="s">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="AL45" s="60"/>
     </row>
-    <row r="46" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="20:38" ht="14.1" customHeight="1">
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3" t="s">
@@ -21085,8 +21085,8 @@
       <c r="AC46" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE46" s="127"/>
-      <c r="AF46" s="127"/>
+      <c r="AE46" s="143"/>
+      <c r="AF46" s="143"/>
       <c r="AG46" s="64" t="s">
         <v>6</v>
       </c>
@@ -21104,7 +21104,7 @@
       </c>
       <c r="AL46" s="60"/>
     </row>
-    <row r="47" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="20:38" ht="14.1" customHeight="1">
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
@@ -21129,8 +21129,8 @@
       <c r="AC47" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AE47" s="127"/>
-      <c r="AF47" s="127"/>
+      <c r="AE47" s="143"/>
+      <c r="AF47" s="143"/>
       <c r="AG47" s="64" t="s">
         <v>7</v>
       </c>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="AL47" s="60"/>
     </row>
-    <row r="48" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="20:38" ht="14.1" customHeight="1">
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
@@ -21171,8 +21171,8 @@
         <v>67</v>
       </c>
       <c r="AC48" s="3"/>
-      <c r="AE48" s="126"/>
-      <c r="AF48" s="126"/>
+      <c r="AE48" s="144"/>
+      <c r="AF48" s="144"/>
       <c r="AG48" s="71" t="s">
         <v>8</v>
       </c>
@@ -21190,7 +21190,7 @@
       </c>
       <c r="AL48" s="60"/>
     </row>
-    <row r="49" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="20:38" ht="14.1" customHeight="1">
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
@@ -21215,10 +21215,10 @@
       <c r="AC49" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE49" s="126" t="s">
+      <c r="AE49" s="144" t="s">
         <v>229</v>
       </c>
-      <c r="AF49" s="129" t="s">
+      <c r="AF49" s="147" t="s">
         <v>5</v>
       </c>
       <c r="AG49" s="81" t="s">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="AL49" s="60"/>
     </row>
-    <row r="50" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="20:38" ht="14.1" customHeight="1">
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
@@ -21263,8 +21263,8 @@
       <c r="AC50" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE50" s="127"/>
-      <c r="AF50" s="130"/>
+      <c r="AE50" s="143"/>
+      <c r="AF50" s="146"/>
       <c r="AG50" s="81" t="s">
         <v>7</v>
       </c>
@@ -21282,7 +21282,7 @@
       </c>
       <c r="AL50" s="60"/>
     </row>
-    <row r="51" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="20:38" ht="14.1" customHeight="1">
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
@@ -21305,8 +21305,8 @@
         <v>67</v>
       </c>
       <c r="AC51" s="3"/>
-      <c r="AE51" s="127"/>
-      <c r="AF51" s="130"/>
+      <c r="AE51" s="143"/>
+      <c r="AF51" s="146"/>
       <c r="AG51" s="81" t="s">
         <v>8</v>
       </c>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="AL51" s="60"/>
     </row>
-    <row r="52" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="20:38" ht="14.1" customHeight="1">
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
@@ -21349,8 +21349,8 @@
       <c r="AC52" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE52" s="127"/>
-      <c r="AF52" s="129"/>
+      <c r="AE52" s="143"/>
+      <c r="AF52" s="147"/>
       <c r="AG52" s="86" t="s">
         <v>227</v>
       </c>
@@ -21362,7 +21362,7 @@
       <c r="AK52" s="97"/>
       <c r="AL52" s="60"/>
     </row>
-    <row r="53" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="20:38" ht="14.1" customHeight="1">
       <c r="T53" s="3"/>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
@@ -21387,8 +21387,8 @@
       <c r="AC53" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE53" s="127"/>
-      <c r="AF53" s="126" t="s">
+      <c r="AE53" s="143"/>
+      <c r="AF53" s="144" t="s">
         <v>6</v>
       </c>
       <c r="AG53" s="64" t="s">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="AL53" s="60"/>
     </row>
-    <row r="54" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="20:38" ht="14.1" customHeight="1">
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
@@ -21433,8 +21433,8 @@
       <c r="AC54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE54" s="127"/>
-      <c r="AF54" s="127"/>
+      <c r="AE54" s="143"/>
+      <c r="AF54" s="143"/>
       <c r="AG54" s="64" t="s">
         <v>7</v>
       </c>
@@ -21452,7 +21452,7 @@
       </c>
       <c r="AL54" s="60"/>
     </row>
-    <row r="55" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="20:38" ht="14.1" customHeight="1">
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
@@ -21477,8 +21477,8 @@
       <c r="AC55" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE55" s="127"/>
-      <c r="AF55" s="127"/>
+      <c r="AE55" s="143"/>
+      <c r="AF55" s="143"/>
       <c r="AG55" s="64" t="s">
         <v>8</v>
       </c>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="AL55" s="60"/>
     </row>
-    <row r="56" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="20:38" ht="14.1" customHeight="1">
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3" t="s">
@@ -21521,8 +21521,8 @@
       <c r="AC56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AE56" s="127"/>
-      <c r="AF56" s="126"/>
+      <c r="AE56" s="143"/>
+      <c r="AF56" s="144"/>
       <c r="AG56" s="71" t="s">
         <v>227</v>
       </c>
@@ -21534,7 +21534,7 @@
       <c r="AK56" s="74"/>
       <c r="AL56" s="60"/>
     </row>
-    <row r="57" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="20:38" ht="14.1" customHeight="1">
       <c r="T57" s="3" t="s">
         <v>34</v>
       </c>
@@ -21559,8 +21559,8 @@
         <v>1000</v>
       </c>
       <c r="AC57" s="3"/>
-      <c r="AE57" s="127"/>
-      <c r="AF57" s="126" t="s">
+      <c r="AE57" s="143"/>
+      <c r="AF57" s="144" t="s">
         <v>7</v>
       </c>
       <c r="AG57" s="64" t="s">
@@ -21580,7 +21580,7 @@
       </c>
       <c r="AL57" s="60"/>
     </row>
-    <row r="58" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="20:38" ht="14.1" customHeight="1">
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3" t="s">
@@ -21603,8 +21603,8 @@
         <v>1000</v>
       </c>
       <c r="AC58" s="3"/>
-      <c r="AE58" s="127"/>
-      <c r="AF58" s="127"/>
+      <c r="AE58" s="143"/>
+      <c r="AF58" s="143"/>
       <c r="AG58" s="64" t="s">
         <v>6</v>
       </c>
@@ -21622,7 +21622,7 @@
       </c>
       <c r="AL58" s="60"/>
     </row>
-    <row r="59" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="20:38" ht="14.1" customHeight="1">
       <c r="T59" s="3"/>
       <c r="U59" s="3"/>
       <c r="V59" s="3" t="s">
@@ -21645,8 +21645,8 @@
         <v>72</v>
       </c>
       <c r="AC59" s="3"/>
-      <c r="AE59" s="127"/>
-      <c r="AF59" s="127"/>
+      <c r="AE59" s="143"/>
+      <c r="AF59" s="143"/>
       <c r="AG59" s="64" t="s">
         <v>8</v>
       </c>
@@ -21664,7 +21664,7 @@
       </c>
       <c r="AL59" s="60"/>
     </row>
-    <row r="60" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="20:38" ht="14.1" customHeight="1">
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3" t="s">
@@ -21687,8 +21687,8 @@
         <v>67</v>
       </c>
       <c r="AC60" s="3"/>
-      <c r="AE60" s="127"/>
-      <c r="AF60" s="126"/>
+      <c r="AE60" s="143"/>
+      <c r="AF60" s="144"/>
       <c r="AG60" s="71" t="s">
         <v>227</v>
       </c>
@@ -21700,7 +21700,7 @@
       <c r="AK60" s="74"/>
       <c r="AL60" s="60"/>
     </row>
-    <row r="61" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="20:38" ht="14.1" customHeight="1">
       <c r="T61" s="3"/>
       <c r="U61" s="3"/>
       <c r="V61" s="3" t="s">
@@ -21725,8 +21725,8 @@
       <c r="AC61" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AE61" s="127"/>
-      <c r="AF61" s="126" t="s">
+      <c r="AE61" s="143"/>
+      <c r="AF61" s="144" t="s">
         <v>8</v>
       </c>
       <c r="AG61" s="64" t="s">
@@ -21746,7 +21746,7 @@
       </c>
       <c r="AL61" s="60"/>
     </row>
-    <row r="62" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="20:38" ht="14.1" customHeight="1">
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3" t="s">
@@ -21769,8 +21769,8 @@
         <v>1000</v>
       </c>
       <c r="AC62" s="3"/>
-      <c r="AE62" s="127"/>
-      <c r="AF62" s="127"/>
+      <c r="AE62" s="143"/>
+      <c r="AF62" s="143"/>
       <c r="AG62" s="64" t="s">
         <v>6</v>
       </c>
@@ -21788,7 +21788,7 @@
       </c>
       <c r="AL62" s="60"/>
     </row>
-    <row r="63" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="20:38" ht="14.1" customHeight="1">
       <c r="T63" s="3"/>
       <c r="U63" s="3"/>
       <c r="V63" s="3" t="s">
@@ -21811,8 +21811,8 @@
         <v>1000</v>
       </c>
       <c r="AC63" s="3"/>
-      <c r="AE63" s="127"/>
-      <c r="AF63" s="127"/>
+      <c r="AE63" s="143"/>
+      <c r="AF63" s="143"/>
       <c r="AG63" s="64" t="s">
         <v>7</v>
       </c>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AL63" s="60"/>
     </row>
-    <row r="64" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="20:38" ht="14.1" customHeight="1">
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3" t="s">
@@ -21853,8 +21853,8 @@
         <v>1000</v>
       </c>
       <c r="AC64" s="3"/>
-      <c r="AE64" s="127"/>
-      <c r="AF64" s="126"/>
+      <c r="AE64" s="143"/>
+      <c r="AF64" s="144"/>
       <c r="AG64" s="71" t="s">
         <v>227</v>
       </c>
@@ -21866,7 +21866,7 @@
       <c r="AK64" s="74"/>
       <c r="AL64" s="60"/>
     </row>
-    <row r="65" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="20:38" ht="14.1" customHeight="1">
       <c r="T65" s="3"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3" t="s">
@@ -21889,8 +21889,8 @@
         <v>1000</v>
       </c>
       <c r="AC65" s="3"/>
-      <c r="AE65" s="127"/>
-      <c r="AF65" s="126" t="s">
+      <c r="AE65" s="143"/>
+      <c r="AF65" s="144" t="s">
         <v>227</v>
       </c>
       <c r="AG65" s="64" t="s">
@@ -21904,7 +21904,7 @@
       <c r="AK65" s="70"/>
       <c r="AL65" s="60"/>
     </row>
-    <row r="66" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="20:38" ht="14.1" customHeight="1">
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3" t="s">
@@ -21927,8 +21927,8 @@
         <v>1000</v>
       </c>
       <c r="AC66" s="3"/>
-      <c r="AE66" s="127"/>
-      <c r="AF66" s="127"/>
+      <c r="AE66" s="143"/>
+      <c r="AF66" s="143"/>
       <c r="AG66" s="64" t="s">
         <v>6</v>
       </c>
@@ -21940,7 +21940,7 @@
       <c r="AK66" s="70"/>
       <c r="AL66" s="60"/>
     </row>
-    <row r="67" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="20:38" ht="14.1" customHeight="1">
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3" t="s">
@@ -21963,8 +21963,8 @@
         <v>1000</v>
       </c>
       <c r="AC67" s="3"/>
-      <c r="AE67" s="127"/>
-      <c r="AF67" s="127"/>
+      <c r="AE67" s="143"/>
+      <c r="AF67" s="143"/>
       <c r="AG67" s="64" t="s">
         <v>7</v>
       </c>
@@ -21976,7 +21976,7 @@
       <c r="AK67" s="70"/>
       <c r="AL67" s="60"/>
     </row>
-    <row r="68" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="20:38" ht="14.1" customHeight="1">
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="3" t="s">
@@ -21999,8 +21999,8 @@
         <v>1000</v>
       </c>
       <c r="AC68" s="3"/>
-      <c r="AE68" s="128"/>
-      <c r="AF68" s="128"/>
+      <c r="AE68" s="148"/>
+      <c r="AF68" s="148"/>
       <c r="AG68" s="61" t="s">
         <v>8</v>
       </c>
@@ -22012,7 +22012,7 @@
       <c r="AK68" s="80"/>
       <c r="AL68" s="60"/>
     </row>
-    <row r="69" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="20:38" ht="14.1" customHeight="1">
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3" t="s">
@@ -22035,18 +22035,18 @@
         <v>84</v>
       </c>
       <c r="AC69" s="3"/>
-      <c r="AE69" s="125" t="s">
+      <c r="AE69" s="149" t="s">
         <v>230</v>
       </c>
-      <c r="AF69" s="125"/>
-      <c r="AG69" s="125"/>
-      <c r="AH69" s="125"/>
-      <c r="AI69" s="125"/>
-      <c r="AJ69" s="125"/>
-      <c r="AK69" s="125"/>
+      <c r="AF69" s="149"/>
+      <c r="AG69" s="149"/>
+      <c r="AH69" s="149"/>
+      <c r="AI69" s="149"/>
+      <c r="AJ69" s="149"/>
+      <c r="AK69" s="149"/>
       <c r="AL69" s="60"/>
     </row>
-    <row r="70" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="20:38" ht="14.1" customHeight="1">
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="3" t="s">
@@ -22069,18 +22069,18 @@
         <v>1000</v>
       </c>
       <c r="AC70" s="3"/>
-      <c r="AE70" s="125" t="s">
+      <c r="AE70" s="149" t="s">
         <v>231</v>
       </c>
-      <c r="AF70" s="125"/>
-      <c r="AG70" s="125"/>
-      <c r="AH70" s="125"/>
-      <c r="AI70" s="125"/>
-      <c r="AJ70" s="125"/>
-      <c r="AK70" s="125"/>
+      <c r="AF70" s="149"/>
+      <c r="AG70" s="149"/>
+      <c r="AH70" s="149"/>
+      <c r="AI70" s="149"/>
+      <c r="AJ70" s="149"/>
+      <c r="AK70" s="149"/>
       <c r="AL70" s="60"/>
     </row>
-    <row r="71" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="20:38" ht="14.1" customHeight="1">
       <c r="T71" s="3"/>
       <c r="U71" s="3"/>
       <c r="V71" s="3" t="s">
@@ -22103,18 +22103,18 @@
         <v>1000</v>
       </c>
       <c r="AC71" s="3"/>
-      <c r="AE71" s="125" t="s">
+      <c r="AE71" s="149" t="s">
         <v>232</v>
       </c>
-      <c r="AF71" s="125"/>
-      <c r="AG71" s="125"/>
-      <c r="AH71" s="125"/>
-      <c r="AI71" s="125"/>
-      <c r="AJ71" s="125"/>
-      <c r="AK71" s="125"/>
+      <c r="AF71" s="149"/>
+      <c r="AG71" s="149"/>
+      <c r="AH71" s="149"/>
+      <c r="AI71" s="149"/>
+      <c r="AJ71" s="149"/>
+      <c r="AK71" s="149"/>
       <c r="AL71" s="60"/>
     </row>
-    <row r="72" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="20:38" ht="14.1" customHeight="1">
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3" t="s">
@@ -22137,18 +22137,18 @@
         <v>1000</v>
       </c>
       <c r="AC72" s="3"/>
-      <c r="AE72" s="125" t="s">
+      <c r="AE72" s="149" t="s">
         <v>233</v>
       </c>
-      <c r="AF72" s="125"/>
-      <c r="AG72" s="125"/>
-      <c r="AH72" s="125"/>
-      <c r="AI72" s="125"/>
-      <c r="AJ72" s="125"/>
-      <c r="AK72" s="125"/>
+      <c r="AF72" s="149"/>
+      <c r="AG72" s="149"/>
+      <c r="AH72" s="149"/>
+      <c r="AI72" s="149"/>
+      <c r="AJ72" s="149"/>
+      <c r="AK72" s="149"/>
       <c r="AL72" s="60"/>
     </row>
-    <row r="73" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="20:38" ht="14.1" customHeight="1">
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
       <c r="V73" s="3" t="s">
@@ -22173,18 +22173,18 @@
       <c r="AC73" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AE73" s="125" t="s">
+      <c r="AE73" s="149" t="s">
         <v>234</v>
       </c>
-      <c r="AF73" s="125"/>
-      <c r="AG73" s="125"/>
-      <c r="AH73" s="125"/>
-      <c r="AI73" s="125"/>
-      <c r="AJ73" s="125"/>
-      <c r="AK73" s="125"/>
+      <c r="AF73" s="149"/>
+      <c r="AG73" s="149"/>
+      <c r="AH73" s="149"/>
+      <c r="AI73" s="149"/>
+      <c r="AJ73" s="149"/>
+      <c r="AK73" s="149"/>
       <c r="AL73" s="60"/>
     </row>
-    <row r="74" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="20:38" ht="14.1" customHeight="1">
       <c r="T74" s="3" t="s">
         <v>37</v>
       </c>
@@ -22210,7 +22210,7 @@
       </c>
       <c r="AC74" s="3"/>
     </row>
-    <row r="75" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="20:38" ht="14.1" customHeight="1">
       <c r="T75" s="3"/>
       <c r="U75" s="3"/>
       <c r="V75" s="3" t="s">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AC75" s="3"/>
     </row>
-    <row r="76" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="20:38" ht="14.1" customHeight="1">
       <c r="T76" s="3"/>
       <c r="U76" s="3"/>
       <c r="V76" s="3" t="s">
@@ -22260,7 +22260,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="20:38" ht="14.1" customHeight="1">
       <c r="T77" s="3"/>
       <c r="U77" s="3"/>
       <c r="V77" s="3" t="s">
@@ -22286,7 +22286,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="20:38" ht="14.1" customHeight="1">
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
       <c r="V78" s="3" t="s">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="AC78" s="3"/>
     </row>
-    <row r="79" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="20:38" ht="14.1" customHeight="1">
       <c r="T79" s="3"/>
       <c r="U79" s="3"/>
       <c r="V79" s="3" t="s">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="AC79" s="3"/>
     </row>
-    <row r="80" spans="20:38" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="20:38" ht="14.1" customHeight="1">
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="3" t="s">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="AC80" s="3"/>
     </row>
-    <row r="81" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="20:29" ht="14.1" customHeight="1">
       <c r="T81" s="3"/>
       <c r="U81" s="3"/>
       <c r="V81" s="3" t="s">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="AC81" s="3"/>
     </row>
-    <row r="82" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="20:29" ht="14.1" customHeight="1">
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3" t="s">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="AC82" s="3"/>
     </row>
-    <row r="83" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="20:29" ht="14.1" customHeight="1">
       <c r="T83" s="3"/>
       <c r="U83" s="3"/>
       <c r="V83" s="3" t="s">
@@ -22430,7 +22430,7 @@
       </c>
       <c r="AC83" s="3"/>
     </row>
-    <row r="84" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="20:29" ht="14.1" customHeight="1">
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
       <c r="V84" s="3" t="s">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="AC84" s="3"/>
     </row>
-    <row r="85" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="20:29" ht="14.1" customHeight="1">
       <c r="T85" s="3"/>
       <c r="U85" s="3"/>
       <c r="V85" s="3" t="s">
@@ -22478,7 +22478,7 @@
       </c>
       <c r="AC85" s="3"/>
     </row>
-    <row r="86" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="20:29" ht="14.1" customHeight="1">
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="3" t="s">
@@ -22502,7 +22502,7 @@
       </c>
       <c r="AC86" s="3"/>
     </row>
-    <row r="87" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="20:29" ht="14.1" customHeight="1">
       <c r="T87" s="3"/>
       <c r="U87" s="3"/>
       <c r="V87" s="3" t="s">
@@ -22526,7 +22526,7 @@
       </c>
       <c r="AC87" s="3"/>
     </row>
-    <row r="88" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="20:29" ht="14.1" customHeight="1">
       <c r="T88" s="3"/>
       <c r="U88" s="3"/>
       <c r="V88" s="3" t="s">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="AC88" s="3"/>
     </row>
-    <row r="89" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="20:29" ht="14.1" customHeight="1">
       <c r="T89" s="3"/>
       <c r="U89" s="3"/>
       <c r="V89" s="3" t="s">
@@ -22576,7 +22576,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="20:29" ht="14.1" customHeight="1">
       <c r="T90" s="3" t="s">
         <v>39</v>
       </c>
@@ -22604,7 +22604,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="91" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="20:29" ht="14.1" customHeight="1">
       <c r="T91" s="3"/>
       <c r="U91" s="3"/>
       <c r="V91" s="3" t="s">
@@ -22630,7 +22630,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="20:29" ht="14.1" customHeight="1">
       <c r="T92" s="3"/>
       <c r="U92" s="3"/>
       <c r="V92" s="3" t="s">
@@ -22656,7 +22656,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="20:29" ht="14.1" customHeight="1">
       <c r="T93" s="3"/>
       <c r="U93" s="3"/>
       <c r="V93" s="3" t="s">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="AC93" s="3"/>
     </row>
-    <row r="94" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="20:29" ht="14.1" customHeight="1">
       <c r="T94" s="3"/>
       <c r="U94" s="3"/>
       <c r="V94" s="3" t="s">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="AC94" s="3"/>
     </row>
-    <row r="95" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="20:29" ht="14.1" customHeight="1">
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3" t="s">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="AC95" s="3"/>
     </row>
-    <row r="96" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="20:29" ht="14.1" customHeight="1">
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
       <c r="V96" s="3" t="s">
@@ -22752,7 +22752,7 @@
       </c>
       <c r="AC96" s="3"/>
     </row>
-    <row r="97" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="20:29" ht="14.1" customHeight="1">
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
       <c r="V97" s="3" t="s">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="AC97" s="3"/>
     </row>
-    <row r="98" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="20:29" ht="14.1" customHeight="1">
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3" t="s">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="AC98" s="3"/>
     </row>
-    <row r="99" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="20:29" ht="14.1" customHeight="1">
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
       <c r="V99" s="3" t="s">
@@ -22824,7 +22824,7 @@
       </c>
       <c r="AC99" s="3"/>
     </row>
-    <row r="100" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="20:29" ht="14.1" customHeight="1">
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="3" t="s">
@@ -22850,7 +22850,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="101" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="20:29" ht="14.1" customHeight="1">
       <c r="T101" s="3"/>
       <c r="U101" s="3"/>
       <c r="V101" s="3" t="s">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="AC101" s="3"/>
     </row>
-    <row r="102" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="20:29" ht="14.1" customHeight="1">
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
       <c r="V102" s="3" t="s">
@@ -22900,7 +22900,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="20:29" ht="14.1" customHeight="1">
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
       <c r="V103" s="3" t="s">
@@ -22926,7 +22926,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="104" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="20:29" ht="14.1" customHeight="1">
       <c r="T104" s="3"/>
       <c r="U104" s="3"/>
       <c r="V104" s="3" t="s">
@@ -22952,7 +22952,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="20:29" ht="14.1" customHeight="1">
       <c r="T105" s="3" t="s">
         <v>40</v>
       </c>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="AC105" s="3"/>
     </row>
-    <row r="106" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="20:29" ht="14.1" customHeight="1">
       <c r="T106" s="3"/>
       <c r="U106" s="3"/>
       <c r="V106" s="3" t="s">
@@ -23002,7 +23002,7 @@
       </c>
       <c r="AC106" s="3"/>
     </row>
-    <row r="107" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="20:29" ht="14.1" customHeight="1">
       <c r="T107" s="3"/>
       <c r="U107" s="3"/>
       <c r="V107" s="3" t="s">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="AC107" s="3"/>
     </row>
-    <row r="108" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="20:29" ht="14.1" customHeight="1">
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
       <c r="V108" s="3" t="s">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="AC108" s="3"/>
     </row>
-    <row r="109" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="20:29" ht="14.1" customHeight="1">
       <c r="T109" s="3"/>
       <c r="U109" s="3"/>
       <c r="V109" s="3" t="s">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="AC109" s="3"/>
     </row>
-    <row r="110" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="20:29" ht="14.1" customHeight="1">
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
       <c r="V110" s="3" t="s">
@@ -23098,7 +23098,7 @@
       </c>
       <c r="AC110" s="3"/>
     </row>
-    <row r="111" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="20:29" ht="14.1" customHeight="1">
       <c r="T111" s="3"/>
       <c r="U111" s="3"/>
       <c r="V111" s="3" t="s">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="AC111" s="3"/>
     </row>
-    <row r="112" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="20:29" ht="14.1" customHeight="1">
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
       <c r="V112" s="3" t="s">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="AC112" s="3"/>
     </row>
-    <row r="113" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="20:29" ht="14.1" customHeight="1">
       <c r="T113" s="3"/>
       <c r="U113" s="3"/>
       <c r="V113" s="3" t="s">
@@ -23170,7 +23170,7 @@
       </c>
       <c r="AC113" s="3"/>
     </row>
-    <row r="114" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="20:29" ht="14.1" customHeight="1">
       <c r="T114" s="3"/>
       <c r="U114" s="3"/>
       <c r="V114" s="3" t="s">
@@ -23194,7 +23194,7 @@
       </c>
       <c r="AC114" s="3"/>
     </row>
-    <row r="115" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="20:29" ht="14.1" customHeight="1">
       <c r="T115" s="3"/>
       <c r="U115" s="3"/>
       <c r="V115" s="3" t="s">
@@ -23218,7 +23218,7 @@
       </c>
       <c r="AC115" s="3"/>
     </row>
-    <row r="116" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="20:29" ht="14.1" customHeight="1">
       <c r="T116" s="3"/>
       <c r="U116" s="3"/>
       <c r="V116" s="3" t="s">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="AC116" s="3"/>
     </row>
-    <row r="117" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="20:29" ht="14.1" customHeight="1">
       <c r="T117" s="3"/>
       <c r="U117" s="3"/>
       <c r="V117" s="3" t="s">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="AC117" s="3"/>
     </row>
-    <row r="118" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="20:29" ht="14.1" customHeight="1">
       <c r="T118" s="3"/>
       <c r="U118" s="3"/>
       <c r="V118" s="3" t="s">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="AC118" s="3"/>
     </row>
-    <row r="119" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="20:29" ht="14.1" customHeight="1">
       <c r="T119" s="3" t="s">
         <v>43</v>
       </c>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="AC119" s="3"/>
     </row>
-    <row r="120" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="20:29" ht="14.1" customHeight="1">
       <c r="T120" s="3"/>
       <c r="U120" s="3"/>
       <c r="V120" s="3" t="s">
@@ -23340,7 +23340,7 @@
       </c>
       <c r="AC120" s="3"/>
     </row>
-    <row r="121" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="20:29" ht="14.1" customHeight="1">
       <c r="T121" s="3"/>
       <c r="U121" s="3"/>
       <c r="V121" s="3" t="s">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="AC121" s="3"/>
     </row>
-    <row r="122" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="20:29" ht="14.1" customHeight="1">
       <c r="T122" s="3"/>
       <c r="U122" s="3"/>
       <c r="V122" s="3" t="s">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="AC122" s="3"/>
     </row>
-    <row r="123" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="20:29" ht="14.1" customHeight="1">
       <c r="T123" s="3"/>
       <c r="U123" s="3"/>
       <c r="V123" s="3" t="s">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AC123" s="3"/>
     </row>
-    <row r="124" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="20:29" ht="14.1" customHeight="1">
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
       <c r="V124" s="3" t="s">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="AC124" s="3"/>
     </row>
-    <row r="125" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="20:29" ht="14.1" customHeight="1">
       <c r="T125" s="3"/>
       <c r="U125" s="3"/>
       <c r="V125" s="3" t="s">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AC125" s="3"/>
     </row>
-    <row r="126" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="20:29" ht="14.1" customHeight="1">
       <c r="T126" s="3"/>
       <c r="U126" s="3"/>
       <c r="V126" s="3" t="s">
@@ -23484,7 +23484,7 @@
       </c>
       <c r="AC126" s="3"/>
     </row>
-    <row r="127" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="20:29" ht="14.1" customHeight="1">
       <c r="T127" s="3"/>
       <c r="U127" s="3"/>
       <c r="V127" s="3" t="s">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="AC127" s="3"/>
     </row>
-    <row r="128" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="20:29" ht="14.1" customHeight="1">
       <c r="T128" s="3"/>
       <c r="U128" s="3"/>
       <c r="V128" s="3" t="s">
@@ -23532,7 +23532,7 @@
       </c>
       <c r="AC128" s="3"/>
     </row>
-    <row r="129" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="20:29" ht="14.1" customHeight="1">
       <c r="T129" s="3"/>
       <c r="U129" s="3"/>
       <c r="V129" s="3" t="s">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="AC129" s="3"/>
     </row>
-    <row r="130" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="20:29" ht="14.1" customHeight="1">
       <c r="T130" s="3"/>
       <c r="U130" s="3"/>
       <c r="V130" s="3" t="s">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="AC130" s="3"/>
     </row>
-    <row r="131" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="20:29" ht="14.1" customHeight="1">
       <c r="T131" s="3"/>
       <c r="U131" s="3"/>
       <c r="V131" s="3" t="s">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="AC131" s="3"/>
     </row>
-    <row r="132" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="20:29" ht="14.1" customHeight="1">
       <c r="T132" s="3" t="s">
         <v>44</v>
       </c>
@@ -23630,7 +23630,7 @@
       </c>
       <c r="AC132" s="3"/>
     </row>
-    <row r="133" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="20:29" ht="14.1" customHeight="1">
       <c r="T133" s="3"/>
       <c r="U133" s="3"/>
       <c r="V133" s="3" t="s">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="AC133" s="3"/>
     </row>
-    <row r="134" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="20:29" ht="14.1" customHeight="1">
       <c r="T134" s="3"/>
       <c r="U134" s="3"/>
       <c r="V134" s="3" t="s">
@@ -23678,7 +23678,7 @@
       </c>
       <c r="AC134" s="3"/>
     </row>
-    <row r="135" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="20:29" ht="14.1" customHeight="1">
       <c r="T135" s="3"/>
       <c r="U135" s="3"/>
       <c r="V135" s="3" t="s">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AC135" s="3"/>
     </row>
-    <row r="136" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="20:29" ht="14.1" customHeight="1">
       <c r="T136" s="3"/>
       <c r="U136" s="3"/>
       <c r="V136" s="3" t="s">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="AC136" s="3"/>
     </row>
-    <row r="137" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="20:29" ht="14.1" customHeight="1">
       <c r="T137" s="3"/>
       <c r="U137" s="3"/>
       <c r="V137" s="3" t="s">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AC137" s="3"/>
     </row>
-    <row r="138" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="20:29" ht="14.1" customHeight="1">
       <c r="T138" s="3"/>
       <c r="U138" s="3"/>
       <c r="V138" s="3" t="s">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="AC138" s="3"/>
     </row>
-    <row r="139" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="20:29" ht="14.1" customHeight="1">
       <c r="T139" s="3"/>
       <c r="U139" s="3"/>
       <c r="V139" s="3" t="s">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="AC139" s="3"/>
     </row>
-    <row r="140" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="20:29" ht="14.1" customHeight="1">
       <c r="T140" s="3"/>
       <c r="U140" s="3"/>
       <c r="V140" s="3" t="s">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="AC140" s="3"/>
     </row>
-    <row r="141" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="20:29" ht="14.1" customHeight="1">
       <c r="T141" s="3"/>
       <c r="U141" s="3"/>
       <c r="V141" s="3" t="s">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="AC141" s="3"/>
     </row>
-    <row r="142" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="20:29" ht="14.1" customHeight="1">
       <c r="T142" s="3"/>
       <c r="U142" s="3"/>
       <c r="V142" s="3" t="s">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="AC142" s="3"/>
     </row>
-    <row r="143" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="20:29" ht="14.1" customHeight="1">
       <c r="T143" s="3"/>
       <c r="U143" s="3"/>
       <c r="V143" s="3" t="s">
@@ -23894,7 +23894,7 @@
       </c>
       <c r="AC143" s="3"/>
     </row>
-    <row r="144" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="20:29" ht="14.1" customHeight="1">
       <c r="T144" s="3" t="s">
         <v>45</v>
       </c>
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AC144" s="3"/>
     </row>
-    <row r="145" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="20:29" ht="14.1" customHeight="1">
       <c r="T145" s="3"/>
       <c r="U145" s="3"/>
       <c r="V145" s="3" t="s">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="AC145" s="3"/>
     </row>
-    <row r="146" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="20:29" ht="14.1" customHeight="1">
       <c r="T146" s="3"/>
       <c r="U146" s="3"/>
       <c r="V146" s="3" t="s">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="AC146" s="3"/>
     </row>
-    <row r="147" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="20:29" ht="14.1" customHeight="1">
       <c r="T147" s="3"/>
       <c r="U147" s="3"/>
       <c r="V147" s="3" t="s">
@@ -23992,7 +23992,7 @@
       </c>
       <c r="AC147" s="3"/>
     </row>
-    <row r="148" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="20:29" ht="14.1" customHeight="1">
       <c r="T148" s="3"/>
       <c r="U148" s="3"/>
       <c r="V148" s="3" t="s">
@@ -24016,7 +24016,7 @@
       </c>
       <c r="AC148" s="3"/>
     </row>
-    <row r="149" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="20:29" ht="14.1" customHeight="1">
       <c r="T149" s="3"/>
       <c r="U149" s="3"/>
       <c r="V149" s="3" t="s">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="AC149" s="3"/>
     </row>
-    <row r="150" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="20:29" ht="14.1" customHeight="1">
       <c r="T150" s="3"/>
       <c r="U150" s="3"/>
       <c r="V150" s="3" t="s">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="AC150" s="3"/>
     </row>
-    <row r="151" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="20:29" ht="14.1" customHeight="1">
       <c r="T151" s="3"/>
       <c r="U151" s="3"/>
       <c r="V151" s="3" t="s">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="AC151" s="3"/>
     </row>
-    <row r="152" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="20:29" ht="14.1" customHeight="1">
       <c r="T152" s="3"/>
       <c r="U152" s="3"/>
       <c r="V152" s="3" t="s">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="AC152" s="3"/>
     </row>
-    <row r="153" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="20:29" ht="14.1" customHeight="1">
       <c r="T153" s="3"/>
       <c r="U153" s="3"/>
       <c r="V153" s="3" t="s">
@@ -24136,7 +24136,7 @@
       </c>
       <c r="AC153" s="3"/>
     </row>
-    <row r="154" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="20:29" ht="14.1" customHeight="1">
       <c r="T154" s="3"/>
       <c r="U154" s="3"/>
       <c r="V154" s="3" t="s">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="AC154" s="3"/>
     </row>
-    <row r="155" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="20:29" ht="14.1" customHeight="1">
       <c r="T155" s="3" t="s">
         <v>48</v>
       </c>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="AC155" s="3"/>
     </row>
-    <row r="156" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="20:29" ht="14.1" customHeight="1">
       <c r="T156" s="3"/>
       <c r="U156" s="3"/>
       <c r="V156" s="3" t="s">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="AC156" s="3"/>
     </row>
-    <row r="157" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="20:29" ht="14.1" customHeight="1">
       <c r="T157" s="3"/>
       <c r="U157" s="3"/>
       <c r="V157" s="3" t="s">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="AC157" s="3"/>
     </row>
-    <row r="158" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="20:29" ht="14.1" customHeight="1">
       <c r="T158" s="3"/>
       <c r="U158" s="3"/>
       <c r="V158" s="3" t="s">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="AC158" s="3"/>
     </row>
-    <row r="159" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="20:29" ht="14.1" customHeight="1">
       <c r="T159" s="3"/>
       <c r="U159" s="3"/>
       <c r="V159" s="3" t="s">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="AC159" s="3"/>
     </row>
-    <row r="160" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="20:29" ht="14.1" customHeight="1">
       <c r="T160" s="3"/>
       <c r="U160" s="3"/>
       <c r="V160" s="3" t="s">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="AC160" s="3"/>
     </row>
-    <row r="161" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="20:29" ht="14.1" customHeight="1">
       <c r="T161" s="3"/>
       <c r="U161" s="3"/>
       <c r="V161" s="3" t="s">
@@ -24330,7 +24330,7 @@
       </c>
       <c r="AC161" s="3"/>
     </row>
-    <row r="162" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="20:29" ht="14.1" customHeight="1">
       <c r="T162" s="3"/>
       <c r="U162" s="3"/>
       <c r="V162" s="3" t="s">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="AC162" s="3"/>
     </row>
-    <row r="163" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="20:29" ht="14.1" customHeight="1">
       <c r="T163" s="3"/>
       <c r="U163" s="3"/>
       <c r="V163" s="3" t="s">
@@ -24378,7 +24378,7 @@
       </c>
       <c r="AC163" s="3"/>
     </row>
-    <row r="164" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="20:29" ht="14.1" customHeight="1">
       <c r="T164" s="3"/>
       <c r="U164" s="3"/>
       <c r="V164" s="3" t="s">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="AC164" s="3"/>
     </row>
-    <row r="165" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="20:29" ht="14.1" customHeight="1">
       <c r="T165" s="3" t="s">
         <v>49</v>
       </c>
@@ -24428,7 +24428,7 @@
       </c>
       <c r="AC165" s="3"/>
     </row>
-    <row r="166" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="20:29" ht="14.1" customHeight="1">
       <c r="T166" s="3"/>
       <c r="U166" s="3"/>
       <c r="V166" s="3" t="s">
@@ -24452,7 +24452,7 @@
       </c>
       <c r="AC166" s="3"/>
     </row>
-    <row r="167" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="20:29" ht="14.1" customHeight="1">
       <c r="T167" s="3"/>
       <c r="U167" s="3"/>
       <c r="V167" s="3" t="s">
@@ -24476,7 +24476,7 @@
       </c>
       <c r="AC167" s="3"/>
     </row>
-    <row r="168" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="20:29" ht="14.1" customHeight="1">
       <c r="T168" s="3"/>
       <c r="U168" s="3"/>
       <c r="V168" s="3" t="s">
@@ -24500,7 +24500,7 @@
       </c>
       <c r="AC168" s="3"/>
     </row>
-    <row r="169" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="20:29" ht="14.1" customHeight="1">
       <c r="T169" s="3"/>
       <c r="U169" s="3"/>
       <c r="V169" s="3" t="s">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="AC169" s="3"/>
     </row>
-    <row r="170" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="20:29" ht="14.1" customHeight="1">
       <c r="T170" s="3"/>
       <c r="U170" s="3"/>
       <c r="V170" s="3" t="s">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AC170" s="3"/>
     </row>
-    <row r="171" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="20:29" ht="14.1" customHeight="1">
       <c r="T171" s="3"/>
       <c r="U171" s="3"/>
       <c r="V171" s="3" t="s">
@@ -24572,7 +24572,7 @@
       </c>
       <c r="AC171" s="3"/>
     </row>
-    <row r="172" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="20:29" ht="14.1" customHeight="1">
       <c r="T172" s="3"/>
       <c r="U172" s="3"/>
       <c r="V172" s="3" t="s">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="AC172" s="3"/>
     </row>
-    <row r="173" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="20:29" ht="14.1" customHeight="1">
       <c r="T173" s="3"/>
       <c r="U173" s="3"/>
       <c r="V173" s="3" t="s">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="AC173" s="3"/>
     </row>
-    <row r="174" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="20:29" ht="14.1" customHeight="1">
       <c r="T174" s="3" t="s">
         <v>50</v>
       </c>
@@ -24646,7 +24646,7 @@
       </c>
       <c r="AC174" s="3"/>
     </row>
-    <row r="175" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="20:29" ht="14.1" customHeight="1">
       <c r="T175" s="3"/>
       <c r="U175" s="3"/>
       <c r="V175" s="3" t="s">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="AC175" s="3"/>
     </row>
-    <row r="176" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="20:29" ht="14.1" customHeight="1">
       <c r="T176" s="3"/>
       <c r="U176" s="3"/>
       <c r="V176" s="3" t="s">
@@ -24694,7 +24694,7 @@
       </c>
       <c r="AC176" s="3"/>
     </row>
-    <row r="177" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="20:29" ht="14.1" customHeight="1">
       <c r="T177" s="3"/>
       <c r="U177" s="3"/>
       <c r="V177" s="3" t="s">
@@ -24718,7 +24718,7 @@
       </c>
       <c r="AC177" s="3"/>
     </row>
-    <row r="178" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="20:29" ht="14.1" customHeight="1">
       <c r="T178" s="3"/>
       <c r="U178" s="3"/>
       <c r="V178" s="3" t="s">
@@ -24742,7 +24742,7 @@
       </c>
       <c r="AC178" s="3"/>
     </row>
-    <row r="179" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="20:29" ht="14.1" customHeight="1">
       <c r="T179" s="3"/>
       <c r="U179" s="3"/>
       <c r="V179" s="3" t="s">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="AC179" s="3"/>
     </row>
-    <row r="180" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="20:29" ht="14.1" customHeight="1">
       <c r="T180" s="3"/>
       <c r="U180" s="3"/>
       <c r="V180" s="3" t="s">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="AC180" s="3"/>
     </row>
-    <row r="181" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="20:29" ht="14.1" customHeight="1">
       <c r="T181" s="3"/>
       <c r="U181" s="3"/>
       <c r="V181" s="3" t="s">
@@ -24816,7 +24816,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="182" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="20:29" ht="14.1" customHeight="1">
       <c r="T182" s="3" t="s">
         <v>53</v>
       </c>
@@ -24842,7 +24842,7 @@
       </c>
       <c r="AC182" s="3"/>
     </row>
-    <row r="183" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="20:29" ht="14.1" customHeight="1">
       <c r="T183" s="3"/>
       <c r="U183" s="3"/>
       <c r="V183" s="3" t="s">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="AC183" s="3"/>
     </row>
-    <row r="184" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="20:29" ht="14.1" customHeight="1">
       <c r="T184" s="3"/>
       <c r="U184" s="3"/>
       <c r="V184" s="3" t="s">
@@ -24890,7 +24890,7 @@
       </c>
       <c r="AC184" s="3"/>
     </row>
-    <row r="185" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="20:29" ht="14.1" customHeight="1">
       <c r="T185" s="3"/>
       <c r="U185" s="3"/>
       <c r="V185" s="3" t="s">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="AC185" s="3"/>
     </row>
-    <row r="186" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="20:29" ht="14.1" customHeight="1">
       <c r="T186" s="3"/>
       <c r="U186" s="3"/>
       <c r="V186" s="3" t="s">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="AC186" s="3"/>
     </row>
-    <row r="187" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="20:29" ht="14.1" customHeight="1">
       <c r="T187" s="3"/>
       <c r="U187" s="3"/>
       <c r="V187" s="3" t="s">
@@ -24962,7 +24962,7 @@
       </c>
       <c r="AC187" s="3"/>
     </row>
-    <row r="188" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="20:29" ht="14.1" customHeight="1">
       <c r="T188" s="3"/>
       <c r="U188" s="3"/>
       <c r="V188" s="3" t="s">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="AC188" s="3"/>
     </row>
-    <row r="189" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="20:29" ht="14.1" customHeight="1">
       <c r="T189" s="3" t="s">
         <v>54</v>
       </c>
@@ -25012,7 +25012,7 @@
       </c>
       <c r="AC189" s="3"/>
     </row>
-    <row r="190" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="20:29" ht="14.1" customHeight="1">
       <c r="T190" s="3"/>
       <c r="U190" s="3"/>
       <c r="V190" s="3" t="s">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="AC190" s="3"/>
     </row>
-    <row r="191" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="20:29" ht="14.1" customHeight="1">
       <c r="T191" s="3"/>
       <c r="U191" s="3"/>
       <c r="V191" s="3" t="s">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="AC191" s="3"/>
     </row>
-    <row r="192" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="20:29" ht="14.1" customHeight="1">
       <c r="T192" s="3"/>
       <c r="U192" s="3"/>
       <c r="V192" s="3" t="s">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="AC192" s="3"/>
     </row>
-    <row r="193" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="20:29" ht="14.1" customHeight="1">
       <c r="T193" s="3"/>
       <c r="U193" s="3"/>
       <c r="V193" s="3" t="s">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="AC193" s="3"/>
     </row>
-    <row r="194" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="20:29" ht="14.1" customHeight="1">
       <c r="T194" s="3"/>
       <c r="U194" s="3"/>
       <c r="V194" s="3" t="s">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="AC194" s="3"/>
     </row>
-    <row r="195" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="20:29" ht="14.1" customHeight="1">
       <c r="T195" s="3" t="s">
         <v>55</v>
       </c>
@@ -25158,7 +25158,7 @@
       </c>
       <c r="AC195" s="3"/>
     </row>
-    <row r="196" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="20:29" ht="14.1" customHeight="1">
       <c r="T196" s="3"/>
       <c r="U196" s="3"/>
       <c r="V196" s="3" t="s">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="AC196" s="3"/>
     </row>
-    <row r="197" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="20:29" ht="14.1" customHeight="1">
       <c r="T197" s="3"/>
       <c r="U197" s="3"/>
       <c r="V197" s="3" t="s">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="AC197" s="3"/>
     </row>
-    <row r="198" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="20:29" ht="14.1" customHeight="1">
       <c r="T198" s="3"/>
       <c r="U198" s="3"/>
       <c r="V198" s="3" t="s">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="AC198" s="3"/>
     </row>
-    <row r="199" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="20:29" ht="14.1" customHeight="1">
       <c r="T199" s="3"/>
       <c r="U199" s="3"/>
       <c r="V199" s="3" t="s">
@@ -25256,7 +25256,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="200" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="20:29" ht="14.1" customHeight="1">
       <c r="T200" s="3" t="s">
         <v>56</v>
       </c>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="AC200" s="3"/>
     </row>
-    <row r="201" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="20:29" ht="14.1" customHeight="1">
       <c r="T201" s="3"/>
       <c r="U201" s="3"/>
       <c r="V201" s="3" t="s">
@@ -25306,7 +25306,7 @@
       </c>
       <c r="AC201" s="3"/>
     </row>
-    <row r="202" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="20:29" ht="14.1" customHeight="1">
       <c r="T202" s="3"/>
       <c r="U202" s="3"/>
       <c r="V202" s="3" t="s">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="AC202" s="3"/>
     </row>
-    <row r="203" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="20:29" ht="14.1" customHeight="1">
       <c r="T203" s="3"/>
       <c r="U203" s="3"/>
       <c r="V203" s="3" t="s">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="AC203" s="3"/>
     </row>
-    <row r="204" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="20:29" ht="14.1" customHeight="1">
       <c r="T204" s="3" t="s">
         <v>57</v>
       </c>
@@ -25380,7 +25380,7 @@
       </c>
       <c r="AC204" s="3"/>
     </row>
-    <row r="205" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="20:29" ht="14.1" customHeight="1">
       <c r="T205" s="3"/>
       <c r="U205" s="3"/>
       <c r="V205" s="3" t="s">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="AC205" s="3"/>
     </row>
-    <row r="206" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="20:29" ht="14.1" customHeight="1">
       <c r="T206" s="3"/>
       <c r="U206" s="3"/>
       <c r="V206" s="3" t="s">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="AC206" s="3"/>
     </row>
-    <row r="207" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="20:29" ht="14.1" customHeight="1">
       <c r="T207" s="3" t="s">
         <v>58</v>
       </c>
@@ -25454,7 +25454,7 @@
       </c>
       <c r="AC207" s="3"/>
     </row>
-    <row r="208" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="20:29" ht="14.1" customHeight="1">
       <c r="T208" s="3"/>
       <c r="U208" s="3"/>
       <c r="V208" s="3" t="s">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="AC208" s="3"/>
     </row>
-    <row r="209" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="20:29" ht="14.1" customHeight="1">
       <c r="T209" s="3" t="s">
         <v>59</v>
       </c>
@@ -25504,48 +25504,80 @@
       </c>
       <c r="AC209" s="3"/>
     </row>
-    <row r="210" spans="20:29" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="T210" s="143"/>
-      <c r="U210" s="143"/>
-      <c r="V210" s="143"/>
-      <c r="W210" s="143"/>
-      <c r="X210" s="143"/>
-      <c r="Y210" s="143"/>
-      <c r="Z210" s="143"/>
-      <c r="AA210" s="143"/>
-      <c r="AB210" s="143"/>
-      <c r="AC210" s="143"/>
-    </row>
-    <row r="211" spans="20:29" ht="14.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="T211" s="144" t="s">
+    <row r="210" spans="20:29" ht="14.1" customHeight="1" thickBot="1">
+      <c r="T210" s="125"/>
+      <c r="U210" s="125"/>
+      <c r="V210" s="125"/>
+      <c r="W210" s="125"/>
+      <c r="X210" s="125"/>
+      <c r="Y210" s="125"/>
+      <c r="Z210" s="125"/>
+      <c r="AA210" s="125"/>
+      <c r="AB210" s="125"/>
+      <c r="AC210" s="125"/>
+    </row>
+    <row r="211" spans="20:29" ht="14.1" customHeight="1" thickTop="1">
+      <c r="T211" s="126" t="s">
         <v>209</v>
       </c>
-      <c r="U211" s="144"/>
-      <c r="V211" s="144"/>
-      <c r="W211" s="144"/>
-      <c r="X211" s="144"/>
-      <c r="Y211" s="144"/>
-      <c r="Z211" s="144"/>
-      <c r="AA211" s="144"/>
-      <c r="AB211" s="144"/>
-      <c r="AC211" s="144"/>
-    </row>
-    <row r="212" spans="20:29" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="T212" s="145" t="s">
+      <c r="U211" s="126"/>
+      <c r="V211" s="126"/>
+      <c r="W211" s="126"/>
+      <c r="X211" s="126"/>
+      <c r="Y211" s="126"/>
+      <c r="Z211" s="126"/>
+      <c r="AA211" s="126"/>
+      <c r="AB211" s="126"/>
+      <c r="AC211" s="126"/>
+    </row>
+    <row r="212" spans="20:29" ht="14.1" customHeight="1">
+      <c r="T212" s="127" t="s">
         <v>210</v>
       </c>
-      <c r="U212" s="145"/>
-      <c r="V212" s="145"/>
-      <c r="W212" s="145"/>
-      <c r="X212" s="145"/>
-      <c r="Y212" s="145"/>
-      <c r="Z212" s="145"/>
-      <c r="AA212" s="145"/>
-      <c r="AB212" s="145"/>
-      <c r="AC212" s="145"/>
+      <c r="U212" s="127"/>
+      <c r="V212" s="127"/>
+      <c r="W212" s="127"/>
+      <c r="X212" s="127"/>
+      <c r="Y212" s="127"/>
+      <c r="Z212" s="127"/>
+      <c r="AA212" s="127"/>
+      <c r="AB212" s="127"/>
+      <c r="AC212" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="AE4:AK4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="U3:AD3"/>
+    <mergeCell ref="U4:Y4"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="AE5:AK5"/>
+    <mergeCell ref="AE6:AG7"/>
+    <mergeCell ref="AH6:AH7"/>
+    <mergeCell ref="AI6:AI7"/>
+    <mergeCell ref="AJ6:AK6"/>
+    <mergeCell ref="AE8:AE28"/>
+    <mergeCell ref="AF8:AF12"/>
+    <mergeCell ref="AF13:AF16"/>
+    <mergeCell ref="AF17:AF20"/>
+    <mergeCell ref="AF21:AF24"/>
+    <mergeCell ref="AF25:AF28"/>
+    <mergeCell ref="AE29:AE48"/>
+    <mergeCell ref="AF29:AF32"/>
+    <mergeCell ref="AF33:AF36"/>
+    <mergeCell ref="AF37:AF40"/>
+    <mergeCell ref="AF41:AF44"/>
+    <mergeCell ref="AF45:AF48"/>
+    <mergeCell ref="AE49:AE68"/>
+    <mergeCell ref="AF49:AF52"/>
+    <mergeCell ref="AF53:AF56"/>
+    <mergeCell ref="AF57:AF60"/>
+    <mergeCell ref="AF61:AF64"/>
+    <mergeCell ref="AF65:AF68"/>
     <mergeCell ref="T211:AC211"/>
     <mergeCell ref="T212:AC212"/>
     <mergeCell ref="AE69:AK69"/>
@@ -25554,38 +25586,6 @@
     <mergeCell ref="AE72:AK72"/>
     <mergeCell ref="AE73:AK73"/>
     <mergeCell ref="T210:AC210"/>
-    <mergeCell ref="AE49:AE68"/>
-    <mergeCell ref="AF49:AF52"/>
-    <mergeCell ref="AF53:AF56"/>
-    <mergeCell ref="AF57:AF60"/>
-    <mergeCell ref="AF61:AF64"/>
-    <mergeCell ref="AF65:AF68"/>
-    <mergeCell ref="AE29:AE48"/>
-    <mergeCell ref="AF29:AF32"/>
-    <mergeCell ref="AF33:AF36"/>
-    <mergeCell ref="AF37:AF40"/>
-    <mergeCell ref="AF41:AF44"/>
-    <mergeCell ref="AF45:AF48"/>
-    <mergeCell ref="AE8:AE28"/>
-    <mergeCell ref="AF8:AF12"/>
-    <mergeCell ref="AF13:AF16"/>
-    <mergeCell ref="AF17:AF20"/>
-    <mergeCell ref="AF21:AF24"/>
-    <mergeCell ref="AF25:AF28"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="AC5:AD5"/>
-    <mergeCell ref="AE5:AK5"/>
-    <mergeCell ref="AE6:AG7"/>
-    <mergeCell ref="AH6:AH7"/>
-    <mergeCell ref="AI6:AI7"/>
-    <mergeCell ref="AJ6:AK6"/>
-    <mergeCell ref="AE4:AK4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="U3:AD3"/>
-    <mergeCell ref="U4:Y4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AC4:AD4"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
